--- a/finance/_refresh_ola.xlsx
+++ b/finance/_refresh_ola.xlsx
@@ -45,8 +45,8 @@
     <definedName name="load_sel">'Assumptions'!$B$36</definedName>
     <definedName name="revleg_sel">'Assumptions'!$B$37</definedName>
     <definedName name="country_opex">'Country opex'!$A$4:$G$4</definedName>
-    <definedName name="som_floor_fleet">'Corridor economics'!$D$106</definedName>
-    <definedName name="som_floor_rev">'Corridor economics'!$E$106</definedName>
+    <definedName name="som_floor_fleet">'Corridor economics'!$D$114</definedName>
+    <definedName name="som_floor_rev">'Corridor economics'!$E$114</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1820,7 +1820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX109"/>
+  <dimension ref="A1:AX119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2539,7 +2539,7 @@
     <row r="6">
       <c r="A6" s="29" t="inlineStr">
         <is>
-          <t>India Andaman Ola</t>
+          <t>India Kolkata Ola</t>
         </is>
       </c>
       <c r="B6" s="29" t="inlineStr">
@@ -2549,25 +2549,17 @@
       </c>
       <c r="C6" s="30" t="inlineStr">
         <is>
-          <t>Marina Park → Aberdeen Jetty</t>
+          <t>Howrah Ferry Ghat → Fairlie Place Ferry</t>
         </is>
       </c>
       <c r="D6" s="31" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="E6" s="26" t="n">
-        <v>22</v>
-      </c>
-      <c r="F6" s="32" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="G6" s="32" t="inlineStr">
-        <is>
-          <t>med-low</t>
-        </is>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="F6" s="32" t="n"/>
+      <c r="G6" s="32" t="n"/>
       <c r="H6" s="19" t="n">
         <v>1</v>
       </c>
@@ -2668,18 +2660,10 @@
         <v/>
       </c>
       <c r="AG6" s="31" t="n">
-        <v>5000</v>
-      </c>
-      <c r="AH6" s="32" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="AI6" s="32" t="inlineStr">
-        <is>
-          <t>med-low</t>
-        </is>
-      </c>
+        <v>1600000</v>
+      </c>
+      <c r="AH6" s="32" t="n"/>
+      <c r="AI6" s="32" t="n"/>
       <c r="AJ6" s="39" t="n">
         <v>0.1</v>
       </c>
@@ -2721,14 +2705,10 @@
       </c>
       <c r="AW6" s="44" t="inlineStr">
         <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
-        </is>
-      </c>
-      <c r="AX6" s="44" t="inlineStr">
-        <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
-        </is>
-      </c>
+          <t xml:space="preserve">[LB-255 PREMIUM RE-FARE: subsidized comparable $2.5 lifted to premium on-demand floor $18.0] </t>
+        </is>
+      </c>
+      <c r="AX6" s="44" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="29" t="inlineStr">
@@ -2743,7 +2723,7 @@
       </c>
       <c r="C7" s="30" t="inlineStr">
         <is>
-          <t>Marina View Point → Aberdeen Jetty</t>
+          <t>Marina Park → Aberdeen Jetty</t>
         </is>
       </c>
       <c r="D7" s="31" t="n">
@@ -2937,11 +2917,11 @@
       </c>
       <c r="C8" s="30" t="inlineStr">
         <is>
-          <t>APARUPA SANDS MARINA → Office Of Assistant Engineer Civil, Andaman Lakshdweep Harbour Work Havelock</t>
+          <t>Marina View Point → Aberdeen Jetty</t>
         </is>
       </c>
       <c r="D8" s="31" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="E8" s="26" t="n">
         <v>22</v>
@@ -3121,7 +3101,7 @@
     <row r="9">
       <c r="A9" s="29" t="inlineStr">
         <is>
-          <t>India Andaman Ola</t>
+          <t>India Kolkata Ola</t>
         </is>
       </c>
       <c r="B9" s="29" t="inlineStr">
@@ -3131,25 +3111,17 @@
       </c>
       <c r="C9" s="30" t="inlineStr">
         <is>
-          <t>Marina Park → Marina View Point</t>
+          <t>Howrah Ferry Ghat → Millennium Park Jetty</t>
         </is>
       </c>
       <c r="D9" s="31" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="E9" s="26" t="n">
-        <v>22</v>
-      </c>
-      <c r="F9" s="32" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="G9" s="32" t="inlineStr">
-        <is>
-          <t>med-low</t>
-        </is>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="F9" s="32" t="n"/>
+      <c r="G9" s="32" t="n"/>
       <c r="H9" s="19" t="n">
         <v>1</v>
       </c>
@@ -3250,18 +3222,10 @@
         <v/>
       </c>
       <c r="AG9" s="31" t="n">
-        <v>5000</v>
-      </c>
-      <c r="AH9" s="32" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="AI9" s="32" t="inlineStr">
-        <is>
-          <t>med-low</t>
-        </is>
-      </c>
+        <v>1600000</v>
+      </c>
+      <c r="AH9" s="32" t="n"/>
+      <c r="AI9" s="32" t="n"/>
       <c r="AJ9" s="39" t="n">
         <v>0.1</v>
       </c>
@@ -3303,14 +3267,10 @@
       </c>
       <c r="AW9" s="44" t="inlineStr">
         <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
-        </is>
-      </c>
-      <c r="AX9" s="44" t="inlineStr">
-        <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
-        </is>
-      </c>
+          <t xml:space="preserve">[LB-255 PREMIUM RE-FARE: subsidized comparable $2.5 lifted to premium on-demand floor $18.0] </t>
+        </is>
+      </c>
+      <c r="AX9" s="44" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="29" t="inlineStr">
@@ -3325,11 +3285,11 @@
       </c>
       <c r="C10" s="30" t="inlineStr">
         <is>
-          <t>Game Fishing In Andaman | Bite Me Charter | Best Sport fishing in Andaman Islands → Port Blair</t>
+          <t>APARUPA SANDS MARINA → Office Of Assistant Engineer Civil, Andaman Lakshdweep Harbour Work Havelock</t>
         </is>
       </c>
       <c r="D10" s="31" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="E10" s="26" t="n">
         <v>22</v>
@@ -3509,7 +3469,7 @@
     <row r="11">
       <c r="A11" s="29" t="inlineStr">
         <is>
-          <t>India Andaman Ola</t>
+          <t>India Kolkata Ola</t>
         </is>
       </c>
       <c r="B11" s="29" t="inlineStr">
@@ -3519,25 +3479,17 @@
       </c>
       <c r="C11" s="30" t="inlineStr">
         <is>
-          <t>Fisheries Jetty → BookMyBoat Andaman Ferry Booking</t>
+          <t>Dakshineswar Ferry Ghat → Belur Math Ferry Ghat</t>
         </is>
       </c>
       <c r="D11" s="31" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="E11" s="26" t="n">
-        <v>22</v>
-      </c>
-      <c r="F11" s="32" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="G11" s="32" t="inlineStr">
-        <is>
-          <t>med-low</t>
-        </is>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="F11" s="32" t="n"/>
+      <c r="G11" s="32" t="n"/>
       <c r="H11" s="19" t="n">
         <v>1</v>
       </c>
@@ -3638,18 +3590,10 @@
         <v/>
       </c>
       <c r="AG11" s="31" t="n">
-        <v>5000</v>
-      </c>
-      <c r="AH11" s="32" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="AI11" s="32" t="inlineStr">
-        <is>
-          <t>med-low</t>
-        </is>
-      </c>
+        <v>1600000</v>
+      </c>
+      <c r="AH11" s="32" t="n"/>
+      <c r="AI11" s="32" t="n"/>
       <c r="AJ11" s="39" t="n">
         <v>0.1</v>
       </c>
@@ -3691,14 +3635,10 @@
       </c>
       <c r="AW11" s="44" t="inlineStr">
         <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
-        </is>
-      </c>
-      <c r="AX11" s="44" t="inlineStr">
-        <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
-        </is>
-      </c>
+          <t xml:space="preserve">[LB-255 PREMIUM RE-FARE: subsidized comparable $2.5 lifted to premium on-demand floor $18.0] </t>
+        </is>
+      </c>
+      <c r="AX11" s="44" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="29" t="inlineStr">
@@ -3713,11 +3653,11 @@
       </c>
       <c r="C12" s="30" t="inlineStr">
         <is>
-          <t>Fisheries Jetty → Gamefishing Asia</t>
+          <t>Marina Park → Marina View Point</t>
         </is>
       </c>
       <c r="D12" s="31" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="E12" s="26" t="n">
         <v>22</v>
@@ -3907,11 +3847,11 @@
       </c>
       <c r="C13" s="30" t="inlineStr">
         <is>
-          <t>Panighat Ferry Jetty → Chatham Harbour</t>
+          <t>Game Fishing In Andaman | Bite Me Charter | Best Sport fishing in Andaman Islands → Port Blair</t>
         </is>
       </c>
       <c r="D13" s="31" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="E13" s="26" t="n">
         <v>22</v>
@@ -4091,7 +4031,7 @@
     <row r="14">
       <c r="A14" s="29" t="inlineStr">
         <is>
-          <t>Ola Mumbai</t>
+          <t>India Kolkata Ola</t>
         </is>
       </c>
       <c r="B14" s="29" t="inlineStr">
@@ -4101,23 +4041,17 @@
       </c>
       <c r="C14" s="30" t="inlineStr">
         <is>
-          <t>Gateway of India → Mumbai Harbour</t>
+          <t>Fairlie Place Ferry → Bagbazar Ghat</t>
         </is>
       </c>
       <c r="D14" s="31" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="E14" s="26" t="n"/>
-      <c r="F14" s="32" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="G14" s="32" t="inlineStr">
-        <is>
-          <t>med-low</t>
-        </is>
-      </c>
+        <v>1.7</v>
+      </c>
+      <c r="E14" s="26" t="n">
+        <v>18</v>
+      </c>
+      <c r="F14" s="32" t="n"/>
+      <c r="G14" s="32" t="n"/>
       <c r="H14" s="19" t="n">
         <v>1</v>
       </c>
@@ -4218,18 +4152,10 @@
         <v/>
       </c>
       <c r="AG14" s="31" t="n">
-        <v>10909</v>
-      </c>
-      <c r="AH14" s="32" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="AI14" s="32" t="inlineStr">
-        <is>
-          <t>med-low</t>
-        </is>
-      </c>
+        <v>1600000</v>
+      </c>
+      <c r="AH14" s="32" t="n"/>
+      <c r="AI14" s="32" t="n"/>
       <c r="AJ14" s="39" t="n">
         <v>0.1</v>
       </c>
@@ -4255,11 +4181,7 @@
       </c>
       <c r="AP14" s="40" t="n"/>
       <c r="AQ14" s="41" t="n"/>
-      <c r="AR14" s="41" t="inlineStr">
-        <is>
-          <t>experience_upside</t>
-        </is>
-      </c>
+      <c r="AR14" s="41" t="n"/>
       <c r="AS14" s="42" t="n"/>
       <c r="AT14" s="43">
         <f>IF(((S14*pax_cap*load_thin*ROUND(K14*L14*revleg_thin,0))-(((battery/range_nm)*D14*ROUND(K14*L14*revleg_thin,0)*VLOOKUP(B14,country_opex,3,FALSE))+V14+W14+X14+Y14+Z14))&lt;=0,"",VLOOKUP(B14,country_opex,7,FALSE)/((S14*pax_cap*load_thin*ROUND(K14*L14*revleg_thin,0))-(((battery/range_nm)*D14*ROUND(K14*L14*revleg_thin,0)*VLOOKUP(B14,country_opex,3,FALSE))+V14+W14+X14+Y14+Z14)))</f>
@@ -4275,19 +4197,15 @@
       </c>
       <c r="AW14" s="44" t="inlineStr">
         <is>
-          <t>M2M Ferries published Mumbai Ferry Wharf/Bhaucha Dhakka ↔ Mandwa Ro-Pax fare floor: passenger fares from ₹400 onwards; motorcycle ₹210 onwards; 4-wheelers ₹1,020 onwards; buses ₹4,500 onwards; vehicle deck over 120 cars/two-wheelers/buses. Converted at ~INR85/USD: ₹400 ≈ $4.70. This is a direct fare floor/comparable, not a premium Navier fare claim.</t>
-        </is>
-      </c>
-      <c r="AX14" s="44" t="inlineStr">
-        <is>
-          <t>PR #58 Mumbai spine route-count split (11 sealed rows × anchor 120,000 pax/yr)</t>
-        </is>
-      </c>
+          <t xml:space="preserve">[LB-255 PREMIUM RE-FARE: subsidized comparable $2.5 lifted to premium on-demand floor $18.0] </t>
+        </is>
+      </c>
+      <c r="AX14" s="44" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="29" t="inlineStr">
         <is>
-          <t>India Goa Ola</t>
+          <t>India Andaman Ola</t>
         </is>
       </c>
       <c r="B15" s="29" t="inlineStr">
@@ -4297,14 +4215,14 @@
       </c>
       <c r="C15" s="30" t="inlineStr">
         <is>
-          <t>Panaji Jetty → Goa</t>
+          <t>Fisheries Jetty → BookMyBoat Andaman Ferry Booking</t>
         </is>
       </c>
       <c r="D15" s="31" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="E15" s="26" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="F15" s="32" t="inlineStr">
         <is>
@@ -4416,7 +4334,7 @@
         <v/>
       </c>
       <c r="AG15" s="31" t="n">
-        <v>11250</v>
+        <v>5000</v>
       </c>
       <c r="AH15" s="32" t="inlineStr">
         <is>
@@ -4469,19 +4387,19 @@
       </c>
       <c r="AW15" s="44" t="inlineStr">
         <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (goa)</t>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
         </is>
       </c>
       <c r="AX15" s="44" t="inlineStr">
         <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (goa)</t>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="29" t="inlineStr">
         <is>
-          <t>India Kerala Ola</t>
+          <t>India Andaman Ola</t>
         </is>
       </c>
       <c r="B16" s="29" t="inlineStr">
@@ -4491,14 +4409,14 @@
       </c>
       <c r="C16" s="30" t="inlineStr">
         <is>
-          <t>Marina One, Kochi → Harbour Roof Garden</t>
+          <t>Fisheries Jetty → Gamefishing Asia</t>
         </is>
       </c>
       <c r="D16" s="31" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="E16" s="26" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F16" s="32" t="inlineStr">
         <is>
@@ -4610,7 +4528,7 @@
         <v/>
       </c>
       <c r="AG16" s="31" t="n">
-        <v>29166</v>
+        <v>5000</v>
       </c>
       <c r="AH16" s="32" t="inlineStr">
         <is>
@@ -4663,19 +4581,19 @@
       </c>
       <c r="AW16" s="44" t="inlineStr">
         <is>
-          <t>[LB-255 PREMIUM RE-FARE: subsidized comparable $3.5 lifted to premium on-demand floor $18.0] handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (kerala)</t>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
         </is>
       </c>
       <c r="AX16" s="44" t="inlineStr">
         <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (kerala)</t>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="29" t="inlineStr">
         <is>
-          <t>India Kerala Ola</t>
+          <t>India Andaman Ola</t>
         </is>
       </c>
       <c r="B17" s="29" t="inlineStr">
@@ -4685,14 +4603,14 @@
       </c>
       <c r="C17" s="30" t="inlineStr">
         <is>
-          <t>Water Wolf Speed Boat - Boating Kadamakudy → Ferry Terminal</t>
+          <t>Panighat Ferry Jetty → Chatham Harbour</t>
         </is>
       </c>
       <c r="D17" s="31" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="E17" s="26" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F17" s="32" t="inlineStr">
         <is>
@@ -4804,7 +4722,7 @@
         <v/>
       </c>
       <c r="AG17" s="31" t="n">
-        <v>29166</v>
+        <v>5000</v>
       </c>
       <c r="AH17" s="32" t="inlineStr">
         <is>
@@ -4857,19 +4775,19 @@
       </c>
       <c r="AW17" s="44" t="inlineStr">
         <is>
-          <t>[LB-255 PREMIUM RE-FARE: subsidized comparable $3.5 lifted to premium on-demand floor $18.0] handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (kerala)</t>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
         </is>
       </c>
       <c r="AX17" s="44" t="inlineStr">
         <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (kerala)</t>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="29" t="inlineStr">
         <is>
-          <t>India Kerala Ola</t>
+          <t>Ola Mumbai</t>
         </is>
       </c>
       <c r="B18" s="29" t="inlineStr">
@@ -4879,15 +4797,13 @@
       </c>
       <c r="C18" s="30" t="inlineStr">
         <is>
-          <t>Willingdon Island → Kerala Backwaters &amp; Kochi</t>
+          <t>Gateway of India → Mumbai Harbour</t>
         </is>
       </c>
       <c r="D18" s="31" t="n">
         <v>2.1</v>
       </c>
-      <c r="E18" s="26" t="n">
-        <v>18</v>
-      </c>
+      <c r="E18" s="26" t="n"/>
       <c r="F18" s="32" t="inlineStr">
         <is>
           <t>T3</t>
@@ -4998,7 +4914,7 @@
         <v/>
       </c>
       <c r="AG18" s="31" t="n">
-        <v>29166</v>
+        <v>10909</v>
       </c>
       <c r="AH18" s="32" t="inlineStr">
         <is>
@@ -5035,7 +4951,11 @@
       </c>
       <c r="AP18" s="40" t="n"/>
       <c r="AQ18" s="41" t="n"/>
-      <c r="AR18" s="41" t="n"/>
+      <c r="AR18" s="41" t="inlineStr">
+        <is>
+          <t>experience_upside</t>
+        </is>
+      </c>
       <c r="AS18" s="42" t="n"/>
       <c r="AT18" s="43">
         <f>IF(((S18*pax_cap*load_thin*ROUND(K18*L18*revleg_thin,0))-(((battery/range_nm)*D18*ROUND(K18*L18*revleg_thin,0)*VLOOKUP(B18,country_opex,3,FALSE))+V18+W18+X18+Y18+Z18))&lt;=0,"",VLOOKUP(B18,country_opex,7,FALSE)/((S18*pax_cap*load_thin*ROUND(K18*L18*revleg_thin,0))-(((battery/range_nm)*D18*ROUND(K18*L18*revleg_thin,0)*VLOOKUP(B18,country_opex,3,FALSE))+V18+W18+X18+Y18+Z18)))</f>
@@ -5051,19 +4971,19 @@
       </c>
       <c r="AW18" s="44" t="inlineStr">
         <is>
-          <t>[LB-255 PREMIUM RE-FARE: subsidized comparable $3.5 lifted to premium on-demand floor $18.0] handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (kerala)</t>
+          <t>M2M Ferries published Mumbai Ferry Wharf/Bhaucha Dhakka ↔ Mandwa Ro-Pax fare floor: passenger fares from ₹400 onwards; motorcycle ₹210 onwards; 4-wheelers ₹1,020 onwards; buses ₹4,500 onwards; vehicle deck over 120 cars/two-wheelers/buses. Converted at ~INR85/USD: ₹400 ≈ $4.70. This is a direct fare floor/comparable, not a premium Navier fare claim.</t>
         </is>
       </c>
       <c r="AX18" s="44" t="inlineStr">
         <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (kerala)</t>
+          <t>PR #58 Mumbai spine route-count split (11 sealed rows × anchor 120,000 pax/yr)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="29" t="inlineStr">
         <is>
-          <t>India Kerala Ola</t>
+          <t>India Goa Ola</t>
         </is>
       </c>
       <c r="B19" s="29" t="inlineStr">
@@ -5073,14 +4993,14 @@
       </c>
       <c r="C19" s="30" t="inlineStr">
         <is>
-          <t>Kochi International Marina KTDC → Martins Harbour</t>
+          <t>Panaji Jetty → Goa</t>
         </is>
       </c>
       <c r="D19" s="31" t="n">
         <v>2.1</v>
       </c>
       <c r="E19" s="26" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F19" s="32" t="inlineStr">
         <is>
@@ -5192,7 +5112,7 @@
         <v/>
       </c>
       <c r="AG19" s="31" t="n">
-        <v>29166</v>
+        <v>11250</v>
       </c>
       <c r="AH19" s="32" t="inlineStr">
         <is>
@@ -5245,19 +5165,19 @@
       </c>
       <c r="AW19" s="44" t="inlineStr">
         <is>
-          <t>[LB-255 PREMIUM RE-FARE: subsidized comparable $3.5 lifted to premium on-demand floor $18.0] handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (kerala)</t>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (goa)</t>
         </is>
       </c>
       <c r="AX19" s="44" t="inlineStr">
         <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (kerala)</t>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (goa)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="29" t="inlineStr">
         <is>
-          <t>India Andaman Ola</t>
+          <t>India Kerala Ola</t>
         </is>
       </c>
       <c r="B20" s="29" t="inlineStr">
@@ -5267,14 +5187,14 @@
       </c>
       <c r="C20" s="30" t="inlineStr">
         <is>
-          <t>Game Fishing In Andaman | Bite Me Charter | Best Sport fishing in Andaman Islands → Junglighat Jetty</t>
+          <t>Marina One, Kochi → Harbour Roof Garden</t>
         </is>
       </c>
       <c r="D20" s="31" t="n">
         <v>2.1</v>
       </c>
       <c r="E20" s="26" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F20" s="32" t="inlineStr">
         <is>
@@ -5386,7 +5306,7 @@
         <v/>
       </c>
       <c r="AG20" s="31" t="n">
-        <v>5000</v>
+        <v>29166</v>
       </c>
       <c r="AH20" s="32" t="inlineStr">
         <is>
@@ -5439,19 +5359,19 @@
       </c>
       <c r="AW20" s="44" t="inlineStr">
         <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
+          <t>[LB-255 PREMIUM RE-FARE: subsidized comparable $3.5 lifted to premium on-demand floor $18.0] handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (kerala)</t>
         </is>
       </c>
       <c r="AX20" s="44" t="inlineStr">
         <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (kerala)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="29" t="inlineStr">
         <is>
-          <t>India Andaman Ola</t>
+          <t>India Kerala Ola</t>
         </is>
       </c>
       <c r="B21" s="29" t="inlineStr">
@@ -5461,14 +5381,14 @@
       </c>
       <c r="C21" s="30" t="inlineStr">
         <is>
-          <t>Andaman → Game Fishing In Andaman | Bite Me Charter | Best Sport fishing in Andaman Islands</t>
+          <t>Water Wolf Speed Boat - Boating Kadamakudy → Ferry Terminal</t>
         </is>
       </c>
       <c r="D21" s="31" t="n">
         <v>2.1</v>
       </c>
       <c r="E21" s="26" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F21" s="32" t="inlineStr">
         <is>
@@ -5580,7 +5500,7 @@
         <v/>
       </c>
       <c r="AG21" s="31" t="n">
-        <v>5000</v>
+        <v>29166</v>
       </c>
       <c r="AH21" s="32" t="inlineStr">
         <is>
@@ -5633,12 +5553,12 @@
       </c>
       <c r="AW21" s="44" t="inlineStr">
         <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
+          <t>[LB-255 PREMIUM RE-FARE: subsidized comparable $3.5 lifted to premium on-demand floor $18.0] handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (kerala)</t>
         </is>
       </c>
       <c r="AX21" s="44" t="inlineStr">
         <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (kerala)</t>
         </is>
       </c>
     </row>
@@ -5659,7 +5579,7 @@
         </is>
       </c>
       <c r="D22" s="31" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="E22" s="26" t="n">
         <v>18</v>
@@ -5839,7 +5759,7 @@
     <row r="23">
       <c r="A23" s="29" t="inlineStr">
         <is>
-          <t>India Andaman Ola</t>
+          <t>India Kerala Ola</t>
         </is>
       </c>
       <c r="B23" s="29" t="inlineStr">
@@ -5849,14 +5769,14 @@
       </c>
       <c r="C23" s="30" t="inlineStr">
         <is>
-          <t>Andaman → Marina Park</t>
+          <t>Kochi International Marina KTDC → Martins Harbour</t>
         </is>
       </c>
       <c r="D23" s="31" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="E23" s="26" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F23" s="32" t="inlineStr">
         <is>
@@ -5968,7 +5888,7 @@
         <v/>
       </c>
       <c r="AG23" s="31" t="n">
-        <v>5000</v>
+        <v>29166</v>
       </c>
       <c r="AH23" s="32" t="inlineStr">
         <is>
@@ -6021,12 +5941,12 @@
       </c>
       <c r="AW23" s="44" t="inlineStr">
         <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
+          <t>[LB-255 PREMIUM RE-FARE: subsidized comparable $3.5 lifted to premium on-demand floor $18.0] handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (kerala)</t>
         </is>
       </c>
       <c r="AX23" s="44" t="inlineStr">
         <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (kerala)</t>
         </is>
       </c>
     </row>
@@ -6043,11 +5963,11 @@
       </c>
       <c r="C24" s="30" t="inlineStr">
         <is>
-          <t>Panighat Ferry Jetty → Chatham Jetty</t>
+          <t>Game Fishing In Andaman | Bite Me Charter | Best Sport fishing in Andaman Islands → Junglighat Jetty</t>
         </is>
       </c>
       <c r="D24" s="31" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="E24" s="26" t="n">
         <v>22</v>
@@ -6227,7 +6147,7 @@
     <row r="25">
       <c r="A25" s="29" t="inlineStr">
         <is>
-          <t>India Goa Ola</t>
+          <t>India Andaman Ola</t>
         </is>
       </c>
       <c r="B25" s="29" t="inlineStr">
@@ -6237,14 +6157,14 @@
       </c>
       <c r="C25" s="30" t="inlineStr">
         <is>
-          <t>Chorao Ferry Terminal → Piedade Ferry Terminal</t>
+          <t>Andaman → Game Fishing In Andaman | Bite Me Charter | Best Sport fishing in Andaman Islands</t>
         </is>
       </c>
       <c r="D25" s="31" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="E25" s="26" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="F25" s="32" t="inlineStr">
         <is>
@@ -6356,7 +6276,7 @@
         <v/>
       </c>
       <c r="AG25" s="31" t="n">
-        <v>11250</v>
+        <v>5000</v>
       </c>
       <c r="AH25" s="32" t="inlineStr">
         <is>
@@ -6409,19 +6329,19 @@
       </c>
       <c r="AW25" s="44" t="inlineStr">
         <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (goa)</t>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
         </is>
       </c>
       <c r="AX25" s="44" t="inlineStr">
         <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (goa)</t>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="29" t="inlineStr">
         <is>
-          <t>India Andaman Ola</t>
+          <t>India Kerala Ola</t>
         </is>
       </c>
       <c r="B26" s="29" t="inlineStr">
@@ -6431,14 +6351,14 @@
       </c>
       <c r="C26" s="30" t="inlineStr">
         <is>
-          <t>Chatham Jetty → Chatham Harbour</t>
+          <t>Willingdon Island → Kerala Backwaters &amp; Kochi</t>
         </is>
       </c>
       <c r="D26" s="31" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="E26" s="26" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F26" s="32" t="inlineStr">
         <is>
@@ -6550,7 +6470,7 @@
         <v/>
       </c>
       <c r="AG26" s="31" t="n">
-        <v>5000</v>
+        <v>29166</v>
       </c>
       <c r="AH26" s="32" t="inlineStr">
         <is>
@@ -6603,12 +6523,12 @@
       </c>
       <c r="AW26" s="44" t="inlineStr">
         <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
+          <t>[LB-255 PREMIUM RE-FARE: subsidized comparable $3.5 lifted to premium on-demand floor $18.0] handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (kerala)</t>
         </is>
       </c>
       <c r="AX26" s="44" t="inlineStr">
         <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (kerala)</t>
         </is>
       </c>
     </row>
@@ -6625,11 +6545,11 @@
       </c>
       <c r="C27" s="30" t="inlineStr">
         <is>
-          <t>Andaman → Fisheries Jetty</t>
+          <t>Andaman → Marina Park</t>
         </is>
       </c>
       <c r="D27" s="31" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="E27" s="26" t="n">
         <v>22</v>
@@ -6809,7 +6729,7 @@
     <row r="28">
       <c r="A28" s="29" t="inlineStr">
         <is>
-          <t>India Mumbai Ola</t>
+          <t>India Andaman Ola</t>
         </is>
       </c>
       <c r="B28" s="29" t="inlineStr">
@@ -6819,14 +6739,14 @@
       </c>
       <c r="C28" s="30" t="inlineStr">
         <is>
-          <t>Bhaucha Dhakka → Cordelia Cruises</t>
+          <t>Panighat Ferry Jetty → Chatham Jetty</t>
         </is>
       </c>
       <c r="D28" s="31" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="E28" s="26" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F28" s="32" t="inlineStr">
         <is>
@@ -6991,19 +6911,19 @@
       </c>
       <c r="AW28" s="44" t="inlineStr">
         <is>
-          <t>[LB-255 PREMIUM RE-FARE: subsidized comparable $5.5 lifted to premium on-demand floor $18.0] handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (mumbai)</t>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
         </is>
       </c>
       <c r="AX28" s="44" t="inlineStr">
         <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (mumbai)</t>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="29" t="inlineStr">
         <is>
-          <t>India Mumbai Ola</t>
+          <t>India Goa Ola</t>
         </is>
       </c>
       <c r="B29" s="29" t="inlineStr">
@@ -7013,14 +6933,14 @@
       </c>
       <c r="C29" s="30" t="inlineStr">
         <is>
-          <t>Bhaucha Dhakka Ferry Boat Service → Cordelia Cruises</t>
+          <t>Chorao Ferry Terminal → Piedade Ferry Terminal</t>
         </is>
       </c>
       <c r="D29" s="31" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="E29" s="26" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F29" s="32" t="inlineStr">
         <is>
@@ -7132,7 +7052,7 @@
         <v/>
       </c>
       <c r="AG29" s="31" t="n">
-        <v>5000</v>
+        <v>11250</v>
       </c>
       <c r="AH29" s="32" t="inlineStr">
         <is>
@@ -7185,12 +7105,12 @@
       </c>
       <c r="AW29" s="44" t="inlineStr">
         <is>
-          <t>[LB-255 PREMIUM RE-FARE: subsidized comparable $5.5 lifted to premium on-demand floor $18.0] handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (mumbai)</t>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (goa)</t>
         </is>
       </c>
       <c r="AX29" s="44" t="inlineStr">
         <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (mumbai)</t>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (goa)</t>
         </is>
       </c>
     </row>
@@ -7207,11 +7127,11 @@
       </c>
       <c r="C30" s="30" t="inlineStr">
         <is>
-          <t>Haddo Jetty → Chatham Harbour</t>
+          <t>Chatham Jetty → Chatham Harbour</t>
         </is>
       </c>
       <c r="D30" s="31" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="E30" s="26" t="n">
         <v>22</v>
@@ -7401,11 +7321,11 @@
       </c>
       <c r="C31" s="30" t="inlineStr">
         <is>
-          <t>Gamefishing Asia → Haddo Jetty</t>
+          <t>Andaman → Fisheries Jetty</t>
         </is>
       </c>
       <c r="D31" s="31" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="E31" s="26" t="n">
         <v>22</v>
@@ -7595,11 +7515,11 @@
       </c>
       <c r="C32" s="30" t="inlineStr">
         <is>
-          <t>Bombay Harbour → Mora</t>
+          <t>Bhaucha Dhakka → Cordelia Cruises</t>
         </is>
       </c>
       <c r="D32" s="31" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="E32" s="26" t="n">
         <v>18</v>
@@ -7789,11 +7709,11 @@
       </c>
       <c r="C33" s="30" t="inlineStr">
         <is>
-          <t>Battle Harbour Design Studio → Cordelia Cruises</t>
+          <t>Bhaucha Dhakka Ferry Boat Service → Cordelia Cruises</t>
         </is>
       </c>
       <c r="D33" s="31" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="E33" s="26" t="n">
         <v>18</v>
@@ -7973,7 +7893,7 @@
     <row r="34">
       <c r="A34" s="29" t="inlineStr">
         <is>
-          <t>India Goa Ola</t>
+          <t>India Andaman Ola</t>
         </is>
       </c>
       <c r="B34" s="29" t="inlineStr">
@@ -7983,14 +7903,14 @@
       </c>
       <c r="C34" s="30" t="inlineStr">
         <is>
-          <t>Panaji Jetty → Goa</t>
+          <t>Haddo Jetty → Chatham Harbour</t>
         </is>
       </c>
       <c r="D34" s="31" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="E34" s="26" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="F34" s="32" t="inlineStr">
         <is>
@@ -8102,7 +8022,7 @@
         <v/>
       </c>
       <c r="AG34" s="31" t="n">
-        <v>11250</v>
+        <v>5000</v>
       </c>
       <c r="AH34" s="32" t="inlineStr">
         <is>
@@ -8155,19 +8075,19 @@
       </c>
       <c r="AW34" s="44" t="inlineStr">
         <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (goa)</t>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
         </is>
       </c>
       <c r="AX34" s="44" t="inlineStr">
         <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (goa)</t>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="29" t="inlineStr">
         <is>
-          <t>India Kerala Ola</t>
+          <t>India Andaman Ola</t>
         </is>
       </c>
       <c r="B35" s="29" t="inlineStr">
@@ -8177,14 +8097,14 @@
       </c>
       <c r="C35" s="30" t="inlineStr">
         <is>
-          <t>Palette MG Road Ernakulam formerly Harbour View Residency → BLUEMARINE Backwaters</t>
+          <t>Gamefishing Asia → Haddo Jetty</t>
         </is>
       </c>
       <c r="D35" s="31" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="E35" s="26" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F35" s="32" t="inlineStr">
         <is>
@@ -8296,7 +8216,7 @@
         <v/>
       </c>
       <c r="AG35" s="31" t="n">
-        <v>29166</v>
+        <v>5000</v>
       </c>
       <c r="AH35" s="32" t="inlineStr">
         <is>
@@ -8349,19 +8269,19 @@
       </c>
       <c r="AW35" s="44" t="inlineStr">
         <is>
-          <t>[LB-255 PREMIUM RE-FARE: subsidized comparable $3.5 lifted to premium on-demand floor $18.0] handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (kerala)</t>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
         </is>
       </c>
       <c r="AX35" s="44" t="inlineStr">
         <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (kerala)</t>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="29" t="inlineStr">
         <is>
-          <t>India Andaman Ola</t>
+          <t>India Mumbai Ola</t>
         </is>
       </c>
       <c r="B36" s="29" t="inlineStr">
@@ -8371,14 +8291,14 @@
       </c>
       <c r="C36" s="30" t="inlineStr">
         <is>
-          <t>Haddo Jetty → Chatham Jetty</t>
+          <t>Bombay Harbour → Mora</t>
         </is>
       </c>
       <c r="D36" s="31" t="n">
         <v>2.6</v>
       </c>
       <c r="E36" s="26" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F36" s="32" t="inlineStr">
         <is>
@@ -8543,12 +8463,12 @@
       </c>
       <c r="AW36" s="44" t="inlineStr">
         <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
+          <t>[LB-255 PREMIUM RE-FARE: subsidized comparable $5.5 lifted to premium on-demand floor $18.0] handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (mumbai)</t>
         </is>
       </c>
       <c r="AX36" s="44" t="inlineStr">
         <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (mumbai)</t>
         </is>
       </c>
     </row>
@@ -8565,11 +8485,11 @@
       </c>
       <c r="C37" s="30" t="inlineStr">
         <is>
-          <t>Bhaucha Dhakka Ferry Boat Service → Bombay Harbour</t>
+          <t>Battle Harbour Design Studio → Cordelia Cruises</t>
         </is>
       </c>
       <c r="D37" s="31" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="E37" s="26" t="n">
         <v>18</v>
@@ -8759,11 +8679,11 @@
       </c>
       <c r="C38" s="30" t="inlineStr">
         <is>
-          <t>Chorao Ferry Terminal → Pomburpa Ferry Terminal</t>
+          <t>Panaji Jetty → Goa</t>
         </is>
       </c>
       <c r="D38" s="31" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="E38" s="26" t="n">
         <v>8</v>
@@ -8943,7 +8863,7 @@
     <row r="39">
       <c r="A39" s="29" t="inlineStr">
         <is>
-          <t>India Goa Ola</t>
+          <t>India Kerala Ola</t>
         </is>
       </c>
       <c r="B39" s="29" t="inlineStr">
@@ -8953,14 +8873,14 @@
       </c>
       <c r="C39" s="30" t="inlineStr">
         <is>
-          <t>Goveia Marina → Camurlim Ferry Terminal</t>
+          <t>Palette MG Road Ernakulam formerly Harbour View Residency → BLUEMARINE Backwaters</t>
         </is>
       </c>
       <c r="D39" s="31" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="E39" s="26" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F39" s="32" t="inlineStr">
         <is>
@@ -9072,7 +8992,7 @@
         <v/>
       </c>
       <c r="AG39" s="31" t="n">
-        <v>11250</v>
+        <v>29166</v>
       </c>
       <c r="AH39" s="32" t="inlineStr">
         <is>
@@ -9125,19 +9045,19 @@
       </c>
       <c r="AW39" s="44" t="inlineStr">
         <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (goa)</t>
+          <t>[LB-255 PREMIUM RE-FARE: subsidized comparable $3.5 lifted to premium on-demand floor $18.0] handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (kerala)</t>
         </is>
       </c>
       <c r="AX39" s="44" t="inlineStr">
         <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (goa)</t>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (kerala)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="29" t="inlineStr">
         <is>
-          <t>India Kerala Ola</t>
+          <t>India Andaman Ola</t>
         </is>
       </c>
       <c r="B40" s="29" t="inlineStr">
@@ -9147,14 +9067,14 @@
       </c>
       <c r="C40" s="30" t="inlineStr">
         <is>
-          <t>BLUEMARINE Backwaters → Sailing Club House</t>
+          <t>Haddo Jetty → Chatham Jetty</t>
         </is>
       </c>
       <c r="D40" s="31" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="E40" s="26" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F40" s="32" t="inlineStr">
         <is>
@@ -9266,7 +9186,7 @@
         <v/>
       </c>
       <c r="AG40" s="31" t="n">
-        <v>29166</v>
+        <v>5000</v>
       </c>
       <c r="AH40" s="32" t="inlineStr">
         <is>
@@ -9319,19 +9239,19 @@
       </c>
       <c r="AW40" s="44" t="inlineStr">
         <is>
-          <t>[LB-255 PREMIUM RE-FARE: subsidized comparable $3.5 lifted to premium on-demand floor $18.0] handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (kerala)</t>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
         </is>
       </c>
       <c r="AX40" s="44" t="inlineStr">
         <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (kerala)</t>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="29" t="inlineStr">
         <is>
-          <t>India Andaman Ola</t>
+          <t>India Mumbai Ola</t>
         </is>
       </c>
       <c r="B41" s="29" t="inlineStr">
@@ -9341,14 +9261,14 @@
       </c>
       <c r="C41" s="30" t="inlineStr">
         <is>
-          <t>Gamefishing Asia → Chatham Jetty</t>
+          <t>Bhaucha Dhakka Ferry Boat Service → Bombay Harbour</t>
         </is>
       </c>
       <c r="D41" s="31" t="n">
         <v>2.7</v>
       </c>
       <c r="E41" s="26" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F41" s="32" t="inlineStr">
         <is>
@@ -9513,19 +9433,19 @@
       </c>
       <c r="AW41" s="44" t="inlineStr">
         <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
+          <t>[LB-255 PREMIUM RE-FARE: subsidized comparable $5.5 lifted to premium on-demand floor $18.0] handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (mumbai)</t>
         </is>
       </c>
       <c r="AX41" s="44" t="inlineStr">
         <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (mumbai)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="29" t="inlineStr">
         <is>
-          <t>India Mumbai Ola</t>
+          <t>India Goa Ola</t>
         </is>
       </c>
       <c r="B42" s="29" t="inlineStr">
@@ -9535,14 +9455,14 @@
       </c>
       <c r="C42" s="30" t="inlineStr">
         <is>
-          <t>Bhaucha Dhakka → Bombay Harbour</t>
+          <t>Chorao Ferry Terminal → Pomburpa Ferry Terminal</t>
         </is>
       </c>
       <c r="D42" s="31" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="E42" s="26" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F42" s="32" t="inlineStr">
         <is>
@@ -9654,7 +9574,7 @@
         <v/>
       </c>
       <c r="AG42" s="31" t="n">
-        <v>5000</v>
+        <v>11250</v>
       </c>
       <c r="AH42" s="32" t="inlineStr">
         <is>
@@ -9707,12 +9627,12 @@
       </c>
       <c r="AW42" s="44" t="inlineStr">
         <is>
-          <t>[LB-255 PREMIUM RE-FARE: subsidized comparable $5.5 lifted to premium on-demand floor $18.0] handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (mumbai)</t>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (goa)</t>
         </is>
       </c>
       <c r="AX42" s="44" t="inlineStr">
         <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (mumbai)</t>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (goa)</t>
         </is>
       </c>
     </row>
@@ -9729,11 +9649,11 @@
       </c>
       <c r="C43" s="30" t="inlineStr">
         <is>
-          <t>Goveia Marina → Tuem Ferry Terminal</t>
+          <t>Goveia Marina → Camurlim Ferry Terminal</t>
         </is>
       </c>
       <c r="D43" s="31" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="E43" s="26" t="n">
         <v>8</v>
@@ -9913,7 +9833,7 @@
     <row r="44">
       <c r="A44" s="29" t="inlineStr">
         <is>
-          <t>India Goa Ola</t>
+          <t>India Kerala Ola</t>
         </is>
       </c>
       <c r="B44" s="29" t="inlineStr">
@@ -9923,14 +9843,14 @@
       </c>
       <c r="C44" s="30" t="inlineStr">
         <is>
-          <t>Ribandar Ferry → Piedade Ferry Terminal</t>
+          <t>BLUEMARINE Backwaters → Sailing Club House</t>
         </is>
       </c>
       <c r="D44" s="31" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="E44" s="26" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F44" s="32" t="inlineStr">
         <is>
@@ -10042,7 +9962,7 @@
         <v/>
       </c>
       <c r="AG44" s="31" t="n">
-        <v>11250</v>
+        <v>29166</v>
       </c>
       <c r="AH44" s="32" t="inlineStr">
         <is>
@@ -10095,19 +10015,19 @@
       </c>
       <c r="AW44" s="44" t="inlineStr">
         <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (goa)</t>
+          <t>[LB-255 PREMIUM RE-FARE: subsidized comparable $3.5 lifted to premium on-demand floor $18.0] handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (kerala)</t>
         </is>
       </c>
       <c r="AX44" s="44" t="inlineStr">
         <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (goa)</t>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (kerala)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="29" t="inlineStr">
         <is>
-          <t>India Kerala Ola</t>
+          <t>India Andaman Ola</t>
         </is>
       </c>
       <c r="B45" s="29" t="inlineStr">
@@ -10117,14 +10037,14 @@
       </c>
       <c r="C45" s="30" t="inlineStr">
         <is>
-          <t>Keltron Ferry → Sailing Club House</t>
+          <t>Gamefishing Asia → Chatham Jetty</t>
         </is>
       </c>
       <c r="D45" s="31" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="E45" s="26" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F45" s="32" t="inlineStr">
         <is>
@@ -10236,7 +10156,7 @@
         <v/>
       </c>
       <c r="AG45" s="31" t="n">
-        <v>29166</v>
+        <v>5000</v>
       </c>
       <c r="AH45" s="32" t="inlineStr">
         <is>
@@ -10289,19 +10209,19 @@
       </c>
       <c r="AW45" s="44" t="inlineStr">
         <is>
-          <t>[LB-255 PREMIUM RE-FARE: subsidized comparable $3.5 lifted to premium on-demand floor $18.0] handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (kerala)</t>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
         </is>
       </c>
       <c r="AX45" s="44" t="inlineStr">
         <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (kerala)</t>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="29" t="inlineStr">
         <is>
-          <t>India Andaman Ola</t>
+          <t>India Mumbai Ola</t>
         </is>
       </c>
       <c r="B46" s="29" t="inlineStr">
@@ -10311,14 +10231,14 @@
       </c>
       <c r="C46" s="30" t="inlineStr">
         <is>
-          <t>Andaman → Andaman &amp; Nicobar Islands</t>
+          <t>Bhaucha Dhakka → Bombay Harbour</t>
         </is>
       </c>
       <c r="D46" s="31" t="n">
         <v>2.8</v>
       </c>
       <c r="E46" s="26" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F46" s="32" t="inlineStr">
         <is>
@@ -10483,19 +10403,19 @@
       </c>
       <c r="AW46" s="44" t="inlineStr">
         <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
+          <t>[LB-255 PREMIUM RE-FARE: subsidized comparable $5.5 lifted to premium on-demand floor $18.0] handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (mumbai)</t>
         </is>
       </c>
       <c r="AX46" s="44" t="inlineStr">
         <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (mumbai)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="29" t="inlineStr">
         <is>
-          <t>India Andaman Ola</t>
+          <t>India Goa Ola</t>
         </is>
       </c>
       <c r="B47" s="29" t="inlineStr">
@@ -10505,14 +10425,14 @@
       </c>
       <c r="C47" s="30" t="inlineStr">
         <is>
-          <t>Andaman → BookMyBoat Andaman Ferry Booking</t>
+          <t>Goveia Marina → Tuem Ferry Terminal</t>
         </is>
       </c>
       <c r="D47" s="31" t="n">
         <v>2.8</v>
       </c>
       <c r="E47" s="26" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="F47" s="32" t="inlineStr">
         <is>
@@ -10624,7 +10544,7 @@
         <v/>
       </c>
       <c r="AG47" s="31" t="n">
-        <v>5000</v>
+        <v>11250</v>
       </c>
       <c r="AH47" s="32" t="inlineStr">
         <is>
@@ -10677,19 +10597,19 @@
       </c>
       <c r="AW47" s="44" t="inlineStr">
         <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (goa)</t>
         </is>
       </c>
       <c r="AX47" s="44" t="inlineStr">
         <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (goa)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="29" t="inlineStr">
         <is>
-          <t>India Andaman Ola</t>
+          <t>India Goa Ola</t>
         </is>
       </c>
       <c r="B48" s="29" t="inlineStr">
@@ -10699,14 +10619,14 @@
       </c>
       <c r="C48" s="30" t="inlineStr">
         <is>
-          <t>Port Blair → BookMyBoat Andaman Ferry Booking</t>
+          <t>Ribandar Ferry → Piedade Ferry Terminal</t>
         </is>
       </c>
       <c r="D48" s="31" t="n">
         <v>2.8</v>
       </c>
       <c r="E48" s="26" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="F48" s="32" t="inlineStr">
         <is>
@@ -10818,7 +10738,7 @@
         <v/>
       </c>
       <c r="AG48" s="31" t="n">
-        <v>5000</v>
+        <v>11250</v>
       </c>
       <c r="AH48" s="32" t="inlineStr">
         <is>
@@ -10871,19 +10791,19 @@
       </c>
       <c r="AW48" s="44" t="inlineStr">
         <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (goa)</t>
         </is>
       </c>
       <c r="AX48" s="44" t="inlineStr">
         <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (goa)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="29" t="inlineStr">
         <is>
-          <t>India Andaman Ola</t>
+          <t>India Kerala Ola</t>
         </is>
       </c>
       <c r="B49" s="29" t="inlineStr">
@@ -10893,14 +10813,14 @@
       </c>
       <c r="C49" s="30" t="inlineStr">
         <is>
-          <t>Junglighat Jetty → BookMyBoat Andaman Ferry Booking</t>
+          <t>Keltron Ferry → Sailing Club House</t>
         </is>
       </c>
       <c r="D49" s="31" t="n">
         <v>2.8</v>
       </c>
       <c r="E49" s="26" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F49" s="32" t="inlineStr">
         <is>
@@ -11012,7 +10932,7 @@
         <v/>
       </c>
       <c r="AG49" s="31" t="n">
-        <v>5000</v>
+        <v>29166</v>
       </c>
       <c r="AH49" s="32" t="inlineStr">
         <is>
@@ -11065,19 +10985,19 @@
       </c>
       <c r="AW49" s="44" t="inlineStr">
         <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
+          <t>[LB-255 PREMIUM RE-FARE: subsidized comparable $3.5 lifted to premium on-demand floor $18.0] handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (kerala)</t>
         </is>
       </c>
       <c r="AX49" s="44" t="inlineStr">
         <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (kerala)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="29" t="inlineStr">
         <is>
-          <t>India Mumbai Ola</t>
+          <t>India Andaman Ola</t>
         </is>
       </c>
       <c r="B50" s="29" t="inlineStr">
@@ -11087,14 +11007,14 @@
       </c>
       <c r="C50" s="30" t="inlineStr">
         <is>
-          <t>Pirpau Jetty → JNPT Ferry Service</t>
+          <t>Andaman → Andaman &amp; Nicobar Islands</t>
         </is>
       </c>
       <c r="D50" s="31" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="E50" s="26" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F50" s="32" t="inlineStr">
         <is>
@@ -11259,12 +11179,12 @@
       </c>
       <c r="AW50" s="44" t="inlineStr">
         <is>
-          <t>[LB-255 PREMIUM RE-FARE: subsidized comparable $5.5 lifted to premium on-demand floor $18.0] handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (mumbai)</t>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
         </is>
       </c>
       <c r="AX50" s="44" t="inlineStr">
         <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (mumbai)</t>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
         </is>
       </c>
     </row>
@@ -11281,11 +11201,11 @@
       </c>
       <c r="C51" s="30" t="inlineStr">
         <is>
-          <t>Bambooflat Jetty → Panighat Ferry Jetty</t>
+          <t>Andaman → BookMyBoat Andaman Ferry Booking</t>
         </is>
       </c>
       <c r="D51" s="31" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="E51" s="26" t="n">
         <v>22</v>
@@ -11465,7 +11385,7 @@
     <row r="52">
       <c r="A52" s="29" t="inlineStr">
         <is>
-          <t>India Goa Ola</t>
+          <t>India Andaman Ola</t>
         </is>
       </c>
       <c r="B52" s="29" t="inlineStr">
@@ -11475,14 +11395,14 @@
       </c>
       <c r="C52" s="30" t="inlineStr">
         <is>
-          <t>Yacht Life Goa → Camurlim Ferry Terminal</t>
+          <t>Port Blair → BookMyBoat Andaman Ferry Booking</t>
         </is>
       </c>
       <c r="D52" s="31" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="E52" s="26" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="F52" s="32" t="inlineStr">
         <is>
@@ -11594,7 +11514,7 @@
         <v/>
       </c>
       <c r="AG52" s="31" t="n">
-        <v>11250</v>
+        <v>5000</v>
       </c>
       <c r="AH52" s="32" t="inlineStr">
         <is>
@@ -11647,19 +11567,19 @@
       </c>
       <c r="AW52" s="44" t="inlineStr">
         <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (goa)</t>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
         </is>
       </c>
       <c r="AX52" s="44" t="inlineStr">
         <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (goa)</t>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="29" t="inlineStr">
         <is>
-          <t>India Goa Ola</t>
+          <t>India Andaman Ola</t>
         </is>
       </c>
       <c r="B53" s="29" t="inlineStr">
@@ -11669,14 +11589,14 @@
       </c>
       <c r="C53" s="30" t="inlineStr">
         <is>
-          <t>Yacht Life Goa → Tuem Ferry Terminal</t>
+          <t>Junglighat Jetty → BookMyBoat Andaman Ferry Booking</t>
         </is>
       </c>
       <c r="D53" s="31" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="E53" s="26" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="F53" s="32" t="inlineStr">
         <is>
@@ -11788,7 +11708,7 @@
         <v/>
       </c>
       <c r="AG53" s="31" t="n">
-        <v>11250</v>
+        <v>5000</v>
       </c>
       <c r="AH53" s="32" t="inlineStr">
         <is>
@@ -11841,19 +11761,19 @@
       </c>
       <c r="AW53" s="44" t="inlineStr">
         <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (goa)</t>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
         </is>
       </c>
       <c r="AX53" s="44" t="inlineStr">
         <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (goa)</t>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="29" t="inlineStr">
         <is>
-          <t>India Goa Ola</t>
+          <t>India Mumbai Ola</t>
         </is>
       </c>
       <c r="B54" s="29" t="inlineStr">
@@ -11863,14 +11783,14 @@
       </c>
       <c r="C54" s="30" t="inlineStr">
         <is>
-          <t>Panaji Jetty → Goa</t>
+          <t>Pirpau Jetty → JNPT Ferry Service</t>
         </is>
       </c>
       <c r="D54" s="31" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="E54" s="26" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F54" s="32" t="inlineStr">
         <is>
@@ -11982,7 +11902,7 @@
         <v/>
       </c>
       <c r="AG54" s="31" t="n">
-        <v>11250</v>
+        <v>5000</v>
       </c>
       <c r="AH54" s="32" t="inlineStr">
         <is>
@@ -12035,19 +11955,19 @@
       </c>
       <c r="AW54" s="44" t="inlineStr">
         <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (goa)</t>
+          <t>[LB-255 PREMIUM RE-FARE: subsidized comparable $5.5 lifted to premium on-demand floor $18.0] handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (mumbai)</t>
         </is>
       </c>
       <c r="AX54" s="44" t="inlineStr">
         <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (goa)</t>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (mumbai)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="29" t="inlineStr">
         <is>
-          <t>India Kerala Ola</t>
+          <t>India Andaman Ola</t>
         </is>
       </c>
       <c r="B55" s="29" t="inlineStr">
@@ -12057,14 +11977,14 @@
       </c>
       <c r="C55" s="30" t="inlineStr">
         <is>
-          <t>Martins Harbour → Kakkanad Ferry Terminal</t>
+          <t>Bambooflat Jetty → Panighat Ferry Jetty</t>
         </is>
       </c>
       <c r="D55" s="31" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="E55" s="26" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F55" s="32" t="inlineStr">
         <is>
@@ -12176,7 +12096,7 @@
         <v/>
       </c>
       <c r="AG55" s="31" t="n">
-        <v>29166</v>
+        <v>5000</v>
       </c>
       <c r="AH55" s="32" t="inlineStr">
         <is>
@@ -12229,19 +12149,19 @@
       </c>
       <c r="AW55" s="44" t="inlineStr">
         <is>
-          <t>[LB-255 PREMIUM RE-FARE: subsidized comparable $3.5 lifted to premium on-demand floor $18.0] handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (kerala)</t>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
         </is>
       </c>
       <c r="AX55" s="44" t="inlineStr">
         <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (kerala)</t>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="29" t="inlineStr">
         <is>
-          <t>India Mumbai Ola</t>
+          <t>India Goa Ola</t>
         </is>
       </c>
       <c r="B56" s="29" t="inlineStr">
@@ -12251,14 +12171,14 @@
       </c>
       <c r="C56" s="30" t="inlineStr">
         <is>
-          <t>Bombay Harbour → Elephanta Caves</t>
+          <t>Yacht Life Goa → Camurlim Ferry Terminal</t>
         </is>
       </c>
       <c r="D56" s="31" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="E56" s="26" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F56" s="32" t="inlineStr">
         <is>
@@ -12370,7 +12290,7 @@
         <v/>
       </c>
       <c r="AG56" s="31" t="n">
-        <v>5000</v>
+        <v>11250</v>
       </c>
       <c r="AH56" s="32" t="inlineStr">
         <is>
@@ -12423,12 +12343,12 @@
       </c>
       <c r="AW56" s="44" t="inlineStr">
         <is>
-          <t>[LB-255 PREMIUM RE-FARE: subsidized comparable $5.5 lifted to premium on-demand floor $18.0] handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (mumbai)</t>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (goa)</t>
         </is>
       </c>
       <c r="AX56" s="44" t="inlineStr">
         <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (mumbai)</t>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (goa)</t>
         </is>
       </c>
     </row>
@@ -12445,11 +12365,11 @@
       </c>
       <c r="C57" s="30" t="inlineStr">
         <is>
-          <t>Ribandar Ferry → Pomburpa Ferry Terminal</t>
+          <t>Yacht Life Goa → Tuem Ferry Terminal</t>
         </is>
       </c>
       <c r="D57" s="31" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="E57" s="26" t="n">
         <v>8</v>
@@ -12629,7 +12549,7 @@
     <row r="58">
       <c r="A58" s="29" t="inlineStr">
         <is>
-          <t>India Kerala Ola</t>
+          <t>India Goa Ola</t>
         </is>
       </c>
       <c r="B58" s="29" t="inlineStr">
@@ -12639,14 +12559,14 @@
       </c>
       <c r="C58" s="30" t="inlineStr">
         <is>
-          <t>Thevara Ferry → Sailing Club House</t>
+          <t>Panaji Jetty → Goa</t>
         </is>
       </c>
       <c r="D58" s="31" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="E58" s="26" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F58" s="32" t="inlineStr">
         <is>
@@ -12758,7 +12678,7 @@
         <v/>
       </c>
       <c r="AG58" s="31" t="n">
-        <v>29166</v>
+        <v>11250</v>
       </c>
       <c r="AH58" s="32" t="inlineStr">
         <is>
@@ -12811,19 +12731,19 @@
       </c>
       <c r="AW58" s="44" t="inlineStr">
         <is>
-          <t>[LB-255 PREMIUM RE-FARE: subsidized comparable $3.5 lifted to premium on-demand floor $18.0] handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (kerala)</t>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (goa)</t>
         </is>
       </c>
       <c r="AX58" s="44" t="inlineStr">
         <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (kerala)</t>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (goa)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="29" t="inlineStr">
         <is>
-          <t>India Andaman Ola</t>
+          <t>India Kerala Ola</t>
         </is>
       </c>
       <c r="B59" s="29" t="inlineStr">
@@ -12833,14 +12753,14 @@
       </c>
       <c r="C59" s="30" t="inlineStr">
         <is>
-          <t>Andaman → Panighat Ferry Jetty</t>
+          <t>Martins Harbour → Kakkanad Ferry Terminal</t>
         </is>
       </c>
       <c r="D59" s="31" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="E59" s="26" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F59" s="32" t="inlineStr">
         <is>
@@ -12952,7 +12872,7 @@
         <v/>
       </c>
       <c r="AG59" s="31" t="n">
-        <v>5000</v>
+        <v>29166</v>
       </c>
       <c r="AH59" s="32" t="inlineStr">
         <is>
@@ -13005,19 +12925,19 @@
       </c>
       <c r="AW59" s="44" t="inlineStr">
         <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
+          <t>[LB-255 PREMIUM RE-FARE: subsidized comparable $3.5 lifted to premium on-demand floor $18.0] handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (kerala)</t>
         </is>
       </c>
       <c r="AX59" s="44" t="inlineStr">
         <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (kerala)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="29" t="inlineStr">
         <is>
-          <t>India Andaman Ola</t>
+          <t>India Mumbai Ola</t>
         </is>
       </c>
       <c r="B60" s="29" t="inlineStr">
@@ -13027,14 +12947,14 @@
       </c>
       <c r="C60" s="30" t="inlineStr">
         <is>
-          <t>Andaman → Chatham Harbour</t>
+          <t>Bombay Harbour → Elephanta Caves</t>
         </is>
       </c>
       <c r="D60" s="31" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="E60" s="26" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F60" s="32" t="inlineStr">
         <is>
@@ -13199,19 +13119,19 @@
       </c>
       <c r="AW60" s="44" t="inlineStr">
         <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
+          <t>[LB-255 PREMIUM RE-FARE: subsidized comparable $5.5 lifted to premium on-demand floor $18.0] handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (mumbai)</t>
         </is>
       </c>
       <c r="AX60" s="44" t="inlineStr">
         <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (mumbai)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="29" t="inlineStr">
         <is>
-          <t>India Andaman Ola</t>
+          <t>India Goa Ola</t>
         </is>
       </c>
       <c r="B61" s="29" t="inlineStr">
@@ -13221,14 +13141,14 @@
       </c>
       <c r="C61" s="30" t="inlineStr">
         <is>
-          <t>Andaman → Haddo Jetty</t>
+          <t>Ribandar Ferry → Pomburpa Ferry Terminal</t>
         </is>
       </c>
       <c r="D61" s="31" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="E61" s="26" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="F61" s="32" t="inlineStr">
         <is>
@@ -13340,7 +13260,7 @@
         <v/>
       </c>
       <c r="AG61" s="31" t="n">
-        <v>5000</v>
+        <v>11250</v>
       </c>
       <c r="AH61" s="32" t="inlineStr">
         <is>
@@ -13393,19 +13313,19 @@
       </c>
       <c r="AW61" s="44" t="inlineStr">
         <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (goa)</t>
         </is>
       </c>
       <c r="AX61" s="44" t="inlineStr">
         <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (goa)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="29" t="inlineStr">
         <is>
-          <t>India Andaman Ola</t>
+          <t>India Kerala Ola</t>
         </is>
       </c>
       <c r="B62" s="29" t="inlineStr">
@@ -13415,14 +13335,14 @@
       </c>
       <c r="C62" s="30" t="inlineStr">
         <is>
-          <t>Bambooflat Jetty → Chatham Jetty</t>
+          <t>Thevara Ferry → Sailing Club House</t>
         </is>
       </c>
       <c r="D62" s="31" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="E62" s="26" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F62" s="32" t="inlineStr">
         <is>
@@ -13534,7 +13454,7 @@
         <v/>
       </c>
       <c r="AG62" s="31" t="n">
-        <v>5000</v>
+        <v>29166</v>
       </c>
       <c r="AH62" s="32" t="inlineStr">
         <is>
@@ -13587,19 +13507,19 @@
       </c>
       <c r="AW62" s="44" t="inlineStr">
         <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
+          <t>[LB-255 PREMIUM RE-FARE: subsidized comparable $3.5 lifted to premium on-demand floor $18.0] handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (kerala)</t>
         </is>
       </c>
       <c r="AX62" s="44" t="inlineStr">
         <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (kerala)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="29" t="inlineStr">
         <is>
-          <t>Ola Mumbai</t>
+          <t>India Andaman Ola</t>
         </is>
       </c>
       <c r="B63" s="29" t="inlineStr">
@@ -13609,13 +13529,15 @@
       </c>
       <c r="C63" s="30" t="inlineStr">
         <is>
-          <t>Gateway of India → Mumbai Harbour</t>
+          <t>Andaman → Panighat Ferry Jetty</t>
         </is>
       </c>
       <c r="D63" s="31" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="E63" s="26" t="n"/>
+        <v>3.2</v>
+      </c>
+      <c r="E63" s="26" t="n">
+        <v>22</v>
+      </c>
       <c r="F63" s="32" t="inlineStr">
         <is>
           <t>T3</t>
@@ -13726,7 +13648,7 @@
         <v/>
       </c>
       <c r="AG63" s="31" t="n">
-        <v>10909</v>
+        <v>5000</v>
       </c>
       <c r="AH63" s="32" t="inlineStr">
         <is>
@@ -13763,11 +13685,7 @@
       </c>
       <c r="AP63" s="40" t="n"/>
       <c r="AQ63" s="41" t="n"/>
-      <c r="AR63" s="41" t="inlineStr">
-        <is>
-          <t>experience_upside</t>
-        </is>
-      </c>
+      <c r="AR63" s="41" t="n"/>
       <c r="AS63" s="42" t="n"/>
       <c r="AT63" s="43">
         <f>IF(((S63*pax_cap*load_thin*ROUND(K63*L63*revleg_thin,0))-(((battery/range_nm)*D63*ROUND(K63*L63*revleg_thin,0)*VLOOKUP(B63,country_opex,3,FALSE))+V63+W63+X63+Y63+Z63))&lt;=0,"",VLOOKUP(B63,country_opex,7,FALSE)/((S63*pax_cap*load_thin*ROUND(K63*L63*revleg_thin,0))-(((battery/range_nm)*D63*ROUND(K63*L63*revleg_thin,0)*VLOOKUP(B63,country_opex,3,FALSE))+V63+W63+X63+Y63+Z63)))</f>
@@ -13783,19 +13701,19 @@
       </c>
       <c r="AW63" s="44" t="inlineStr">
         <is>
-          <t>M2M Ferries published Mumbai Ferry Wharf/Bhaucha Dhakka ↔ Mandwa Ro-Pax fare floor: passenger fares from ₹400 onwards; motorcycle ₹210 onwards; 4-wheelers ₹1,020 onwards; buses ₹4,500 onwards; vehicle deck over 120 cars/two-wheelers/buses. Converted at ~INR85/USD: ₹400 ≈ $4.70. This is a direct fare floor/comparable, not a premium Navier fare claim.</t>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
         </is>
       </c>
       <c r="AX63" s="44" t="inlineStr">
         <is>
-          <t>PR #58 Mumbai spine route-count split (11 sealed rows × anchor 120,000 pax/yr)</t>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="29" t="inlineStr">
         <is>
-          <t>India Mumbai Ola</t>
+          <t>India Chennai Ola</t>
         </is>
       </c>
       <c r="B64" s="29" t="inlineStr">
@@ -13805,25 +13723,17 @@
       </c>
       <c r="C64" s="30" t="inlineStr">
         <is>
-          <t>Bombay Harbour → Pirpau Jetty</t>
+          <t>Chennai Port WQIV Cruise Terminal → Marina Beach Waterfront</t>
         </is>
       </c>
       <c r="D64" s="31" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="E64" s="26" t="n">
-        <v>18</v>
-      </c>
-      <c r="F64" s="32" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="G64" s="32" t="inlineStr">
-        <is>
-          <t>med-low</t>
-        </is>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="F64" s="32" t="n"/>
+      <c r="G64" s="32" t="n"/>
       <c r="H64" s="19" t="n">
         <v>1</v>
       </c>
@@ -13924,18 +13834,10 @@
         <v/>
       </c>
       <c r="AG64" s="31" t="n">
-        <v>5000</v>
-      </c>
-      <c r="AH64" s="32" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="AI64" s="32" t="inlineStr">
-        <is>
-          <t>med-low</t>
-        </is>
-      </c>
+        <v>400000</v>
+      </c>
+      <c r="AH64" s="32" t="n"/>
+      <c r="AI64" s="32" t="n"/>
       <c r="AJ64" s="39" t="n">
         <v>0.1</v>
       </c>
@@ -13975,21 +13877,13 @@
         <f>IF(((S64*pax_cap*load_full*ROUND(K64*L64*revleg_full,0))-(((battery/range_nm)*D64*ROUND(K64*L64*revleg_full,0)*VLOOKUP(B64,country_opex,3,FALSE))+V64+W64+X64+Y64+Z64))&lt;=0,"",VLOOKUP(B64,country_opex,7,FALSE)/((S64*pax_cap*load_full*ROUND(K64*L64*revleg_full,0))-(((battery/range_nm)*D64*ROUND(K64*L64*revleg_full,0)*VLOOKUP(B64,country_opex,3,FALSE))+V64+W64+X64+Y64+Z64)))</f>
         <v/>
       </c>
-      <c r="AW64" s="44" t="inlineStr">
-        <is>
-          <t>[LB-255 PREMIUM RE-FARE: subsidized comparable $5.5 lifted to premium on-demand floor $18.0] handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (mumbai)</t>
-        </is>
-      </c>
-      <c r="AX64" s="44" t="inlineStr">
-        <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (mumbai)</t>
-        </is>
-      </c>
+      <c r="AW64" s="44" t="n"/>
+      <c r="AX64" s="44" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="29" t="inlineStr">
         <is>
-          <t>Ola Mumbai</t>
+          <t>India Andaman Ola</t>
         </is>
       </c>
       <c r="B65" s="29" t="inlineStr">
@@ -13999,13 +13893,15 @@
       </c>
       <c r="C65" s="30" t="inlineStr">
         <is>
-          <t>Gateway of India → Mumbai Harbour</t>
+          <t>Andaman → Chatham Harbour</t>
         </is>
       </c>
       <c r="D65" s="31" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E65" s="26" t="n"/>
+        <v>3.3</v>
+      </c>
+      <c r="E65" s="26" t="n">
+        <v>22</v>
+      </c>
       <c r="F65" s="32" t="inlineStr">
         <is>
           <t>T3</t>
@@ -14116,7 +14012,7 @@
         <v/>
       </c>
       <c r="AG65" s="31" t="n">
-        <v>10909</v>
+        <v>5000</v>
       </c>
       <c r="AH65" s="32" t="inlineStr">
         <is>
@@ -14153,11 +14049,7 @@
       </c>
       <c r="AP65" s="40" t="n"/>
       <c r="AQ65" s="41" t="n"/>
-      <c r="AR65" s="41" t="inlineStr">
-        <is>
-          <t>experience_upside</t>
-        </is>
-      </c>
+      <c r="AR65" s="41" t="n"/>
       <c r="AS65" s="42" t="n"/>
       <c r="AT65" s="43">
         <f>IF(((S65*pax_cap*load_thin*ROUND(K65*L65*revleg_thin,0))-(((battery/range_nm)*D65*ROUND(K65*L65*revleg_thin,0)*VLOOKUP(B65,country_opex,3,FALSE))+V65+W65+X65+Y65+Z65))&lt;=0,"",VLOOKUP(B65,country_opex,7,FALSE)/((S65*pax_cap*load_thin*ROUND(K65*L65*revleg_thin,0))-(((battery/range_nm)*D65*ROUND(K65*L65*revleg_thin,0)*VLOOKUP(B65,country_opex,3,FALSE))+V65+W65+X65+Y65+Z65)))</f>
@@ -14173,12 +14065,12 @@
       </c>
       <c r="AW65" s="44" t="inlineStr">
         <is>
-          <t>M2M Ferries published Mumbai Ferry Wharf/Bhaucha Dhakka ↔ Mandwa Ro-Pax fare floor: passenger fares from ₹400 onwards; motorcycle ₹210 onwards; 4-wheelers ₹1,020 onwards; buses ₹4,500 onwards; vehicle deck over 120 cars/two-wheelers/buses. Converted at ~INR85/USD: ₹400 ≈ $4.70. This is a direct fare floor/comparable, not a premium Navier fare claim.</t>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
         </is>
       </c>
       <c r="AX65" s="44" t="inlineStr">
         <is>
-          <t>PR #58 Mumbai spine route-count split (11 sealed rows × anchor 120,000 pax/yr)</t>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
         </is>
       </c>
     </row>
@@ -14195,11 +14087,11 @@
       </c>
       <c r="C66" s="30" t="inlineStr">
         <is>
-          <t>Andaman → Chatham Jetty</t>
+          <t>Andaman → Haddo Jetty</t>
         </is>
       </c>
       <c r="D66" s="31" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="E66" s="26" t="n">
         <v>22</v>
@@ -14389,11 +14281,11 @@
       </c>
       <c r="C67" s="30" t="inlineStr">
         <is>
-          <t>Middle Strait Jetty → NK Cruise Terminal</t>
+          <t>Bambooflat Jetty → Chatham Jetty</t>
         </is>
       </c>
       <c r="D67" s="31" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="E67" s="26" t="n">
         <v>22</v>
@@ -14573,7 +14465,7 @@
     <row r="68">
       <c r="A68" s="29" t="inlineStr">
         <is>
-          <t>India Mumbai Ola</t>
+          <t>Ola Mumbai</t>
         </is>
       </c>
       <c r="B68" s="29" t="inlineStr">
@@ -14583,15 +14475,13 @@
       </c>
       <c r="C68" s="30" t="inlineStr">
         <is>
-          <t>Mora → Elephanta Caves</t>
+          <t>Gateway of India → Mumbai Harbour</t>
         </is>
       </c>
       <c r="D68" s="31" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="E68" s="26" t="n">
-        <v>18</v>
-      </c>
+        <v>3.4</v>
+      </c>
+      <c r="E68" s="26" t="n"/>
       <c r="F68" s="32" t="inlineStr">
         <is>
           <t>T3</t>
@@ -14702,7 +14592,7 @@
         <v/>
       </c>
       <c r="AG68" s="31" t="n">
-        <v>5000</v>
+        <v>10909</v>
       </c>
       <c r="AH68" s="32" t="inlineStr">
         <is>
@@ -14739,7 +14629,11 @@
       </c>
       <c r="AP68" s="40" t="n"/>
       <c r="AQ68" s="41" t="n"/>
-      <c r="AR68" s="41" t="n"/>
+      <c r="AR68" s="41" t="inlineStr">
+        <is>
+          <t>experience_upside</t>
+        </is>
+      </c>
       <c r="AS68" s="42" t="n"/>
       <c r="AT68" s="43">
         <f>IF(((S68*pax_cap*load_thin*ROUND(K68*L68*revleg_thin,0))-(((battery/range_nm)*D68*ROUND(K68*L68*revleg_thin,0)*VLOOKUP(B68,country_opex,3,FALSE))+V68+W68+X68+Y68+Z68))&lt;=0,"",VLOOKUP(B68,country_opex,7,FALSE)/((S68*pax_cap*load_thin*ROUND(K68*L68*revleg_thin,0))-(((battery/range_nm)*D68*ROUND(K68*L68*revleg_thin,0)*VLOOKUP(B68,country_opex,3,FALSE))+V68+W68+X68+Y68+Z68)))</f>
@@ -14755,19 +14649,19 @@
       </c>
       <c r="AW68" s="44" t="inlineStr">
         <is>
-          <t>[LB-255 PREMIUM RE-FARE: subsidized comparable $5.5 lifted to premium on-demand floor $18.0] handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (mumbai)</t>
+          <t>M2M Ferries published Mumbai Ferry Wharf/Bhaucha Dhakka ↔ Mandwa Ro-Pax fare floor: passenger fares from ₹400 onwards; motorcycle ₹210 onwards; 4-wheelers ₹1,020 onwards; buses ₹4,500 onwards; vehicle deck over 120 cars/two-wheelers/buses. Converted at ~INR85/USD: ₹400 ≈ $4.70. This is a direct fare floor/comparable, not a premium Navier fare claim.</t>
         </is>
       </c>
       <c r="AX68" s="44" t="inlineStr">
         <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (mumbai)</t>
+          <t>PR #58 Mumbai spine route-count split (11 sealed rows × anchor 120,000 pax/yr)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="29" t="inlineStr">
         <is>
-          <t>India Andaman Ola</t>
+          <t>India Mumbai Ola</t>
         </is>
       </c>
       <c r="B69" s="29" t="inlineStr">
@@ -14777,14 +14671,14 @@
       </c>
       <c r="C69" s="30" t="inlineStr">
         <is>
-          <t>Andaman → Andaman &amp; Nicobar Islands</t>
+          <t>Bombay Harbour → Pirpau Jetty</t>
         </is>
       </c>
       <c r="D69" s="31" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="E69" s="26" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F69" s="32" t="inlineStr">
         <is>
@@ -14949,19 +14843,19 @@
       </c>
       <c r="AW69" s="44" t="inlineStr">
         <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
+          <t>[LB-255 PREMIUM RE-FARE: subsidized comparable $5.5 lifted to premium on-demand floor $18.0] handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (mumbai)</t>
         </is>
       </c>
       <c r="AX69" s="44" t="inlineStr">
         <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (mumbai)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="29" t="inlineStr">
         <is>
-          <t>India Andaman Ola</t>
+          <t>Ola Mumbai</t>
         </is>
       </c>
       <c r="B70" s="29" t="inlineStr">
@@ -14971,15 +14865,13 @@
       </c>
       <c r="C70" s="30" t="inlineStr">
         <is>
-          <t>Andaman → Bambooflat Jetty</t>
+          <t>Gateway of India → Mumbai Harbour</t>
         </is>
       </c>
       <c r="D70" s="31" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="E70" s="26" t="n">
-        <v>22</v>
-      </c>
+        <v>3.5</v>
+      </c>
+      <c r="E70" s="26" t="n"/>
       <c r="F70" s="32" t="inlineStr">
         <is>
           <t>T3</t>
@@ -15090,7 +14982,7 @@
         <v/>
       </c>
       <c r="AG70" s="31" t="n">
-        <v>5000</v>
+        <v>10909</v>
       </c>
       <c r="AH70" s="32" t="inlineStr">
         <is>
@@ -15127,7 +15019,11 @@
       </c>
       <c r="AP70" s="40" t="n"/>
       <c r="AQ70" s="41" t="n"/>
-      <c r="AR70" s="41" t="n"/>
+      <c r="AR70" s="41" t="inlineStr">
+        <is>
+          <t>experience_upside</t>
+        </is>
+      </c>
       <c r="AS70" s="42" t="n"/>
       <c r="AT70" s="43">
         <f>IF(((S70*pax_cap*load_thin*ROUND(K70*L70*revleg_thin,0))-(((battery/range_nm)*D70*ROUND(K70*L70*revleg_thin,0)*VLOOKUP(B70,country_opex,3,FALSE))+V70+W70+X70+Y70+Z70))&lt;=0,"",VLOOKUP(B70,country_opex,7,FALSE)/((S70*pax_cap*load_thin*ROUND(K70*L70*revleg_thin,0))-(((battery/range_nm)*D70*ROUND(K70*L70*revleg_thin,0)*VLOOKUP(B70,country_opex,3,FALSE))+V70+W70+X70+Y70+Z70)))</f>
@@ -15143,19 +15039,19 @@
       </c>
       <c r="AW70" s="44" t="inlineStr">
         <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
+          <t>M2M Ferries published Mumbai Ferry Wharf/Bhaucha Dhakka ↔ Mandwa Ro-Pax fare floor: passenger fares from ₹400 onwards; motorcycle ₹210 onwards; 4-wheelers ₹1,020 onwards; buses ₹4,500 onwards; vehicle deck over 120 cars/two-wheelers/buses. Converted at ~INR85/USD: ₹400 ≈ $4.70. This is a direct fare floor/comparable, not a premium Navier fare claim.</t>
         </is>
       </c>
       <c r="AX70" s="44" t="inlineStr">
         <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
+          <t>PR #58 Mumbai spine route-count split (11 sealed rows × anchor 120,000 pax/yr)</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="29" t="inlineStr">
         <is>
-          <t>Ola Mumbai</t>
+          <t>India Andaman Ola</t>
         </is>
       </c>
       <c r="B71" s="29" t="inlineStr">
@@ -15165,13 +15061,15 @@
       </c>
       <c r="C71" s="30" t="inlineStr">
         <is>
-          <t>BSA Mandwa → Marina Bay Bistro @KARANJA Fishing Dock</t>
+          <t>Andaman → Chatham Jetty</t>
         </is>
       </c>
       <c r="D71" s="31" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="E71" s="26" t="n"/>
+        <v>3.5</v>
+      </c>
+      <c r="E71" s="26" t="n">
+        <v>22</v>
+      </c>
       <c r="F71" s="32" t="inlineStr">
         <is>
           <t>T3</t>
@@ -15282,7 +15180,7 @@
         <v/>
       </c>
       <c r="AG71" s="31" t="n">
-        <v>10909</v>
+        <v>5000</v>
       </c>
       <c r="AH71" s="32" t="inlineStr">
         <is>
@@ -15319,11 +15217,7 @@
       </c>
       <c r="AP71" s="40" t="n"/>
       <c r="AQ71" s="41" t="n"/>
-      <c r="AR71" s="41" t="inlineStr">
-        <is>
-          <t>experience_upside</t>
-        </is>
-      </c>
+      <c r="AR71" s="41" t="n"/>
       <c r="AS71" s="42" t="n"/>
       <c r="AT71" s="43">
         <f>IF(((S71*pax_cap*load_thin*ROUND(K71*L71*revleg_thin,0))-(((battery/range_nm)*D71*ROUND(K71*L71*revleg_thin,0)*VLOOKUP(B71,country_opex,3,FALSE))+V71+W71+X71+Y71+Z71))&lt;=0,"",VLOOKUP(B71,country_opex,7,FALSE)/((S71*pax_cap*load_thin*ROUND(K71*L71*revleg_thin,0))-(((battery/range_nm)*D71*ROUND(K71*L71*revleg_thin,0)*VLOOKUP(B71,country_opex,3,FALSE))+V71+W71+X71+Y71+Z71)))</f>
@@ -15339,19 +15233,19 @@
       </c>
       <c r="AW71" s="44" t="inlineStr">
         <is>
-          <t>M2M Ferries published Mumbai Ferry Wharf/Bhaucha Dhakka ↔ Mandwa Ro-Pax fare floor: passenger fares from ₹400 onwards; motorcycle ₹210 onwards; 4-wheelers ₹1,020 onwards; buses ₹4,500 onwards; vehicle deck over 120 cars/two-wheelers/buses. Converted at ~INR85/USD: ₹400 ≈ $4.70. This is a direct fare floor/comparable, not a premium Navier fare claim.</t>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
         </is>
       </c>
       <c r="AX71" s="44" t="inlineStr">
         <is>
-          <t>PR #58 Mumbai spine route-count split (11 sealed rows × anchor 120,000 pax/yr)</t>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="29" t="inlineStr">
         <is>
-          <t>Ola Mumbai</t>
+          <t>India Andaman Ola</t>
         </is>
       </c>
       <c r="B72" s="29" t="inlineStr">
@@ -15361,13 +15255,15 @@
       </c>
       <c r="C72" s="30" t="inlineStr">
         <is>
-          <t>Mandwa Jetty → Mumbai Harbour</t>
+          <t>Middle Strait Jetty → NK Cruise Terminal</t>
         </is>
       </c>
       <c r="D72" s="31" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="E72" s="26" t="n"/>
+        <v>3.7</v>
+      </c>
+      <c r="E72" s="26" t="n">
+        <v>22</v>
+      </c>
       <c r="F72" s="32" t="inlineStr">
         <is>
           <t>T3</t>
@@ -15478,7 +15374,7 @@
         <v/>
       </c>
       <c r="AG72" s="31" t="n">
-        <v>10909</v>
+        <v>5000</v>
       </c>
       <c r="AH72" s="32" t="inlineStr">
         <is>
@@ -15515,11 +15411,7 @@
       </c>
       <c r="AP72" s="40" t="n"/>
       <c r="AQ72" s="41" t="n"/>
-      <c r="AR72" s="41" t="inlineStr">
-        <is>
-          <t>experience_upside</t>
-        </is>
-      </c>
+      <c r="AR72" s="41" t="n"/>
       <c r="AS72" s="42" t="n"/>
       <c r="AT72" s="43">
         <f>IF(((S72*pax_cap*load_thin*ROUND(K72*L72*revleg_thin,0))-(((battery/range_nm)*D72*ROUND(K72*L72*revleg_thin,0)*VLOOKUP(B72,country_opex,3,FALSE))+V72+W72+X72+Y72+Z72))&lt;=0,"",VLOOKUP(B72,country_opex,7,FALSE)/((S72*pax_cap*load_thin*ROUND(K72*L72*revleg_thin,0))-(((battery/range_nm)*D72*ROUND(K72*L72*revleg_thin,0)*VLOOKUP(B72,country_opex,3,FALSE))+V72+W72+X72+Y72+Z72)))</f>
@@ -15535,19 +15427,19 @@
       </c>
       <c r="AW72" s="44" t="inlineStr">
         <is>
-          <t>M2M Ferries published Mumbai Ferry Wharf/Bhaucha Dhakka ↔ Mandwa Ro-Pax fare floor: passenger fares from ₹400 onwards; motorcycle ₹210 onwards; 4-wheelers ₹1,020 onwards; buses ₹4,500 onwards; vehicle deck over 120 cars/two-wheelers/buses. Converted at ~INR85/USD: ₹400 ≈ $4.70. This is a direct fare floor/comparable, not a premium Navier fare claim.</t>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
         </is>
       </c>
       <c r="AX72" s="44" t="inlineStr">
         <is>
-          <t>PR #58 Mumbai spine route-count split (11 sealed rows × anchor 120,000 pax/yr)</t>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="29" t="inlineStr">
         <is>
-          <t>India Goa Ola</t>
+          <t>India Mumbai Ola</t>
         </is>
       </c>
       <c r="B73" s="29" t="inlineStr">
@@ -15557,14 +15449,14 @@
       </c>
       <c r="C73" s="30" t="inlineStr">
         <is>
-          <t>Villa Marina → Mole</t>
+          <t>Mora → Elephanta Caves</t>
         </is>
       </c>
       <c r="D73" s="31" t="n">
-        <v>4.9</v>
+        <v>3.8</v>
       </c>
       <c r="E73" s="26" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F73" s="32" t="inlineStr">
         <is>
@@ -15676,7 +15568,7 @@
         <v/>
       </c>
       <c r="AG73" s="31" t="n">
-        <v>11250</v>
+        <v>5000</v>
       </c>
       <c r="AH73" s="32" t="inlineStr">
         <is>
@@ -15729,19 +15621,19 @@
       </c>
       <c r="AW73" s="44" t="inlineStr">
         <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (goa)</t>
+          <t>[LB-255 PREMIUM RE-FARE: subsidized comparable $5.5 lifted to premium on-demand floor $18.0] handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (mumbai)</t>
         </is>
       </c>
       <c r="AX73" s="44" t="inlineStr">
         <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (goa)</t>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (mumbai)</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="29" t="inlineStr">
         <is>
-          <t>India Mumbai Ola</t>
+          <t>India Andaman Ola</t>
         </is>
       </c>
       <c r="B74" s="29" t="inlineStr">
@@ -15751,14 +15643,14 @@
       </c>
       <c r="C74" s="30" t="inlineStr">
         <is>
-          <t>Marina Bay Bistro @KARANJA Fishing Dock → Harbour view villa by 29 bungalow</t>
+          <t>Andaman → Andaman &amp; Nicobar Islands</t>
         </is>
       </c>
       <c r="D74" s="31" t="n">
-        <v>5.4</v>
+        <v>3.8</v>
       </c>
       <c r="E74" s="26" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F74" s="32" t="inlineStr">
         <is>
@@ -15923,19 +15815,19 @@
       </c>
       <c r="AW74" s="44" t="inlineStr">
         <is>
-          <t>[LB-255 PREMIUM RE-FARE: subsidized comparable $5.5 lifted to premium on-demand floor $18.0] handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (mumbai)</t>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
         </is>
       </c>
       <c r="AX74" s="44" t="inlineStr">
         <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (mumbai)</t>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="29" t="inlineStr">
         <is>
-          <t>Ola Mumbai</t>
+          <t>India Andaman Ola</t>
         </is>
       </c>
       <c r="B75" s="29" t="inlineStr">
@@ -15945,13 +15837,15 @@
       </c>
       <c r="C75" s="30" t="inlineStr">
         <is>
-          <t>Elephanta Caves → Mumbai Trans-Harbour Navi Mumbai Toll Plaza</t>
+          <t>Andaman → Bambooflat Jetty</t>
         </is>
       </c>
       <c r="D75" s="31" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="E75" s="26" t="n"/>
+        <v>4.2</v>
+      </c>
+      <c r="E75" s="26" t="n">
+        <v>22</v>
+      </c>
       <c r="F75" s="32" t="inlineStr">
         <is>
           <t>T3</t>
@@ -16062,7 +15956,7 @@
         <v/>
       </c>
       <c r="AG75" s="31" t="n">
-        <v>10909</v>
+        <v>5000</v>
       </c>
       <c r="AH75" s="32" t="inlineStr">
         <is>
@@ -16099,11 +15993,7 @@
       </c>
       <c r="AP75" s="40" t="n"/>
       <c r="AQ75" s="41" t="n"/>
-      <c r="AR75" s="41" t="inlineStr">
-        <is>
-          <t>experience_upside</t>
-        </is>
-      </c>
+      <c r="AR75" s="41" t="n"/>
       <c r="AS75" s="42" t="n"/>
       <c r="AT75" s="43">
         <f>IF(((S75*pax_cap*load_thin*ROUND(K75*L75*revleg_thin,0))-(((battery/range_nm)*D75*ROUND(K75*L75*revleg_thin,0)*VLOOKUP(B75,country_opex,3,FALSE))+V75+W75+X75+Y75+Z75))&lt;=0,"",VLOOKUP(B75,country_opex,7,FALSE)/((S75*pax_cap*load_thin*ROUND(K75*L75*revleg_thin,0))-(((battery/range_nm)*D75*ROUND(K75*L75*revleg_thin,0)*VLOOKUP(B75,country_opex,3,FALSE))+V75+W75+X75+Y75+Z75)))</f>
@@ -16119,19 +16009,19 @@
       </c>
       <c r="AW75" s="44" t="inlineStr">
         <is>
-          <t>M2M Ferries published Mumbai Ferry Wharf/Bhaucha Dhakka ↔ Mandwa Ro-Pax fare floor: passenger fares from ₹400 onwards; motorcycle ₹210 onwards; 4-wheelers ₹1,020 onwards; buses ₹4,500 onwards; vehicle deck over 120 cars/two-wheelers/buses. Converted at ~INR85/USD: ₹400 ≈ $4.70. This is a direct fare floor/comparable, not a premium Navier fare claim.</t>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
         </is>
       </c>
       <c r="AX75" s="44" t="inlineStr">
         <is>
-          <t>PR #58 Mumbai spine route-count split (11 sealed rows × anchor 120,000 pax/yr)</t>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="29" t="inlineStr">
         <is>
-          <t>India Goa Ola</t>
+          <t>Ola Mumbai</t>
         </is>
       </c>
       <c r="B76" s="29" t="inlineStr">
@@ -16141,15 +16031,13 @@
       </c>
       <c r="C76" s="30" t="inlineStr">
         <is>
-          <t>Goveia Marina → LifeOnYachts Goa</t>
+          <t>BSA Mandwa → Marina Bay Bistro @KARANJA Fishing Dock</t>
         </is>
       </c>
       <c r="D76" s="31" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="E76" s="26" t="n">
-        <v>8</v>
-      </c>
+        <v>4.5</v>
+      </c>
+      <c r="E76" s="26" t="n"/>
       <c r="F76" s="32" t="inlineStr">
         <is>
           <t>T3</t>
@@ -16260,7 +16148,7 @@
         <v/>
       </c>
       <c r="AG76" s="31" t="n">
-        <v>11250</v>
+        <v>10909</v>
       </c>
       <c r="AH76" s="32" t="inlineStr">
         <is>
@@ -16297,7 +16185,11 @@
       </c>
       <c r="AP76" s="40" t="n"/>
       <c r="AQ76" s="41" t="n"/>
-      <c r="AR76" s="41" t="n"/>
+      <c r="AR76" s="41" t="inlineStr">
+        <is>
+          <t>experience_upside</t>
+        </is>
+      </c>
       <c r="AS76" s="42" t="n"/>
       <c r="AT76" s="43">
         <f>IF(((S76*pax_cap*load_thin*ROUND(K76*L76*revleg_thin,0))-(((battery/range_nm)*D76*ROUND(K76*L76*revleg_thin,0)*VLOOKUP(B76,country_opex,3,FALSE))+V76+W76+X76+Y76+Z76))&lt;=0,"",VLOOKUP(B76,country_opex,7,FALSE)/((S76*pax_cap*load_thin*ROUND(K76*L76*revleg_thin,0))-(((battery/range_nm)*D76*ROUND(K76*L76*revleg_thin,0)*VLOOKUP(B76,country_opex,3,FALSE))+V76+W76+X76+Y76+Z76)))</f>
@@ -16313,19 +16205,19 @@
       </c>
       <c r="AW76" s="44" t="inlineStr">
         <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (goa)</t>
+          <t>M2M Ferries published Mumbai Ferry Wharf/Bhaucha Dhakka ↔ Mandwa Ro-Pax fare floor: passenger fares from ₹400 onwards; motorcycle ₹210 onwards; 4-wheelers ₹1,020 onwards; buses ₹4,500 onwards; vehicle deck over 120 cars/two-wheelers/buses. Converted at ~INR85/USD: ₹400 ≈ $4.70. This is a direct fare floor/comparable, not a premium Navier fare claim.</t>
         </is>
       </c>
       <c r="AX76" s="44" t="inlineStr">
         <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (goa)</t>
+          <t>PR #58 Mumbai spine route-count split (11 sealed rows × anchor 120,000 pax/yr)</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="29" t="inlineStr">
         <is>
-          <t>India Kerala Ola</t>
+          <t>Ola Mumbai</t>
         </is>
       </c>
       <c r="B77" s="29" t="inlineStr">
@@ -16335,15 +16227,13 @@
       </c>
       <c r="C77" s="30" t="inlineStr">
         <is>
-          <t>Keltron Ferry → Chellanam Harbour Kochi</t>
+          <t>Mandwa Jetty → Mumbai Harbour</t>
         </is>
       </c>
       <c r="D77" s="31" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="E77" s="26" t="n">
-        <v>18</v>
-      </c>
+        <v>4.6</v>
+      </c>
+      <c r="E77" s="26" t="n"/>
       <c r="F77" s="32" t="inlineStr">
         <is>
           <t>T3</t>
@@ -16454,7 +16344,7 @@
         <v/>
       </c>
       <c r="AG77" s="31" t="n">
-        <v>29166</v>
+        <v>10909</v>
       </c>
       <c r="AH77" s="32" t="inlineStr">
         <is>
@@ -16491,7 +16381,11 @@
       </c>
       <c r="AP77" s="40" t="n"/>
       <c r="AQ77" s="41" t="n"/>
-      <c r="AR77" s="41" t="n"/>
+      <c r="AR77" s="41" t="inlineStr">
+        <is>
+          <t>experience_upside</t>
+        </is>
+      </c>
       <c r="AS77" s="42" t="n"/>
       <c r="AT77" s="43">
         <f>IF(((S77*pax_cap*load_thin*ROUND(K77*L77*revleg_thin,0))-(((battery/range_nm)*D77*ROUND(K77*L77*revleg_thin,0)*VLOOKUP(B77,country_opex,3,FALSE))+V77+W77+X77+Y77+Z77))&lt;=0,"",VLOOKUP(B77,country_opex,7,FALSE)/((S77*pax_cap*load_thin*ROUND(K77*L77*revleg_thin,0))-(((battery/range_nm)*D77*ROUND(K77*L77*revleg_thin,0)*VLOOKUP(B77,country_opex,3,FALSE))+V77+W77+X77+Y77+Z77)))</f>
@@ -16507,19 +16401,19 @@
       </c>
       <c r="AW77" s="44" t="inlineStr">
         <is>
-          <t>[LB-255 PREMIUM RE-FARE: subsidized comparable $3.5 lifted to premium on-demand floor $18.0] handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (kerala)</t>
+          <t>M2M Ferries published Mumbai Ferry Wharf/Bhaucha Dhakka ↔ Mandwa Ro-Pax fare floor: passenger fares from ₹400 onwards; motorcycle ₹210 onwards; 4-wheelers ₹1,020 onwards; buses ₹4,500 onwards; vehicle deck over 120 cars/two-wheelers/buses. Converted at ~INR85/USD: ₹400 ≈ $4.70. This is a direct fare floor/comparable, not a premium Navier fare claim.</t>
         </is>
       </c>
       <c r="AX77" s="44" t="inlineStr">
         <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (kerala)</t>
+          <t>PR #58 Mumbai spine route-count split (11 sealed rows × anchor 120,000 pax/yr)</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="29" t="inlineStr">
         <is>
-          <t>Ola Mumbai</t>
+          <t>India Goa Ola</t>
         </is>
       </c>
       <c r="B78" s="29" t="inlineStr">
@@ -16529,13 +16423,15 @@
       </c>
       <c r="C78" s="30" t="inlineStr">
         <is>
-          <t>JNPT Ferry Service → Mumbai Trans-Harbour Navi Mumbai Toll Plaza</t>
+          <t>Villa Marina → Mole</t>
         </is>
       </c>
       <c r="D78" s="31" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="E78" s="26" t="n"/>
+        <v>4.9</v>
+      </c>
+      <c r="E78" s="26" t="n">
+        <v>8</v>
+      </c>
       <c r="F78" s="32" t="inlineStr">
         <is>
           <t>T3</t>
@@ -16646,7 +16542,7 @@
         <v/>
       </c>
       <c r="AG78" s="31" t="n">
-        <v>10909</v>
+        <v>11250</v>
       </c>
       <c r="AH78" s="32" t="inlineStr">
         <is>
@@ -16683,11 +16579,7 @@
       </c>
       <c r="AP78" s="40" t="n"/>
       <c r="AQ78" s="41" t="n"/>
-      <c r="AR78" s="41" t="inlineStr">
-        <is>
-          <t>experience_upside</t>
-        </is>
-      </c>
+      <c r="AR78" s="41" t="n"/>
       <c r="AS78" s="42" t="n"/>
       <c r="AT78" s="43">
         <f>IF(((S78*pax_cap*load_thin*ROUND(K78*L78*revleg_thin,0))-(((battery/range_nm)*D78*ROUND(K78*L78*revleg_thin,0)*VLOOKUP(B78,country_opex,3,FALSE))+V78+W78+X78+Y78+Z78))&lt;=0,"",VLOOKUP(B78,country_opex,7,FALSE)/((S78*pax_cap*load_thin*ROUND(K78*L78*revleg_thin,0))-(((battery/range_nm)*D78*ROUND(K78*L78*revleg_thin,0)*VLOOKUP(B78,country_opex,3,FALSE))+V78+W78+X78+Y78+Z78)))</f>
@@ -16703,19 +16595,19 @@
       </c>
       <c r="AW78" s="44" t="inlineStr">
         <is>
-          <t>M2M Ferries published Mumbai Ferry Wharf/Bhaucha Dhakka ↔ Mandwa Ro-Pax fare floor: passenger fares from ₹400 onwards; motorcycle ₹210 onwards; 4-wheelers ₹1,020 onwards; buses ₹4,500 onwards; vehicle deck over 120 cars/two-wheelers/buses. Converted at ~INR85/USD: ₹400 ≈ $4.70. This is a direct fare floor/comparable, not a premium Navier fare claim.</t>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (goa)</t>
         </is>
       </c>
       <c r="AX78" s="44" t="inlineStr">
         <is>
-          <t>PR #58 Mumbai spine route-count split (11 sealed rows × anchor 120,000 pax/yr)</t>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (goa)</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="29" t="inlineStr">
         <is>
-          <t>India Goa Ola</t>
+          <t>India Mumbai Ola</t>
         </is>
       </c>
       <c r="B79" s="29" t="inlineStr">
@@ -16725,14 +16617,14 @@
       </c>
       <c r="C79" s="30" t="inlineStr">
         <is>
-          <t>Panaji Jetty → Goa</t>
+          <t>Marina Bay Bistro @KARANJA Fishing Dock → Harbour view villa by 29 bungalow</t>
         </is>
       </c>
       <c r="D79" s="31" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="E79" s="26" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F79" s="32" t="inlineStr">
         <is>
@@ -16844,7 +16736,7 @@
         <v/>
       </c>
       <c r="AG79" s="31" t="n">
-        <v>11250</v>
+        <v>5000</v>
       </c>
       <c r="AH79" s="32" t="inlineStr">
         <is>
@@ -16897,12 +16789,12 @@
       </c>
       <c r="AW79" s="44" t="inlineStr">
         <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (goa)</t>
+          <t>[LB-255 PREMIUM RE-FARE: subsidized comparable $5.5 lifted to premium on-demand floor $18.0] handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (mumbai)</t>
         </is>
       </c>
       <c r="AX79" s="44" t="inlineStr">
         <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (goa)</t>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (mumbai)</t>
         </is>
       </c>
     </row>
@@ -16919,11 +16811,11 @@
       </c>
       <c r="C80" s="30" t="inlineStr">
         <is>
-          <t>Pirpau Jetty → Mumbai Trans-Harbour Navi Mumbai Toll Plaza</t>
+          <t>Elephanta Caves → Mumbai Trans-Harbour Navi Mumbai Toll Plaza</t>
         </is>
       </c>
       <c r="D80" s="31" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="E80" s="26" t="n"/>
       <c r="F80" s="32" t="inlineStr">
@@ -17105,7 +16997,7 @@
     <row r="81">
       <c r="A81" s="29" t="inlineStr">
         <is>
-          <t>India Mumbai Ola</t>
+          <t>India Goa Ola</t>
         </is>
       </c>
       <c r="B81" s="29" t="inlineStr">
@@ -17115,14 +17007,14 @@
       </c>
       <c r="C81" s="30" t="inlineStr">
         <is>
-          <t>Mora → Marina Bay Bistro @KARANJA Fishing Dock</t>
+          <t>Goveia Marina → LifeOnYachts Goa</t>
         </is>
       </c>
       <c r="D81" s="31" t="n">
-        <v>6.7</v>
+        <v>5.8</v>
       </c>
       <c r="E81" s="26" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F81" s="32" t="inlineStr">
         <is>
@@ -17234,7 +17126,7 @@
         <v/>
       </c>
       <c r="AG81" s="31" t="n">
-        <v>5000</v>
+        <v>11250</v>
       </c>
       <c r="AH81" s="32" t="inlineStr">
         <is>
@@ -17287,19 +17179,19 @@
       </c>
       <c r="AW81" s="44" t="inlineStr">
         <is>
-          <t>[LB-255 PREMIUM RE-FARE: subsidized comparable $5.5 lifted to premium on-demand floor $18.0] handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (mumbai)</t>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (goa)</t>
         </is>
       </c>
       <c r="AX81" s="44" t="inlineStr">
         <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (mumbai)</t>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (goa)</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="29" t="inlineStr">
         <is>
-          <t>India Goa Ola</t>
+          <t>India Kerala Ola</t>
         </is>
       </c>
       <c r="B82" s="29" t="inlineStr">
@@ -17309,14 +17201,14 @@
       </c>
       <c r="C82" s="30" t="inlineStr">
         <is>
-          <t>Villa Marina → Marina Russian B2B Thai Spa Service near me</t>
+          <t>Keltron Ferry → Chellanam Harbour Kochi</t>
         </is>
       </c>
       <c r="D82" s="31" t="n">
-        <v>6.7</v>
+        <v>5.8</v>
       </c>
       <c r="E82" s="26" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F82" s="32" t="inlineStr">
         <is>
@@ -17428,7 +17320,7 @@
         <v/>
       </c>
       <c r="AG82" s="31" t="n">
-        <v>11250</v>
+        <v>29166</v>
       </c>
       <c r="AH82" s="32" t="inlineStr">
         <is>
@@ -17481,19 +17373,19 @@
       </c>
       <c r="AW82" s="44" t="inlineStr">
         <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (goa)</t>
+          <t>[LB-255 PREMIUM RE-FARE: subsidized comparable $3.5 lifted to premium on-demand floor $18.0] handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (kerala)</t>
         </is>
       </c>
       <c r="AX82" s="44" t="inlineStr">
         <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (goa)</t>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (kerala)</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="29" t="inlineStr">
         <is>
-          <t>India Kerala Ola</t>
+          <t>Ola Mumbai</t>
         </is>
       </c>
       <c r="B83" s="29" t="inlineStr">
@@ -17503,15 +17395,13 @@
       </c>
       <c r="C83" s="30" t="inlineStr">
         <is>
-          <t>Willingdon Island → Kerala Backwaters &amp; Kochi</t>
+          <t>JNPT Ferry Service → Mumbai Trans-Harbour Navi Mumbai Toll Plaza</t>
         </is>
       </c>
       <c r="D83" s="31" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="E83" s="26" t="n">
-        <v>18</v>
-      </c>
+        <v>5.9</v>
+      </c>
+      <c r="E83" s="26" t="n"/>
       <c r="F83" s="32" t="inlineStr">
         <is>
           <t>T3</t>
@@ -17622,7 +17512,7 @@
         <v/>
       </c>
       <c r="AG83" s="31" t="n">
-        <v>29166</v>
+        <v>10909</v>
       </c>
       <c r="AH83" s="32" t="inlineStr">
         <is>
@@ -17659,7 +17549,11 @@
       </c>
       <c r="AP83" s="40" t="n"/>
       <c r="AQ83" s="41" t="n"/>
-      <c r="AR83" s="41" t="n"/>
+      <c r="AR83" s="41" t="inlineStr">
+        <is>
+          <t>experience_upside</t>
+        </is>
+      </c>
       <c r="AS83" s="42" t="n"/>
       <c r="AT83" s="43">
         <f>IF(((S83*pax_cap*load_thin*ROUND(K83*L83*revleg_thin,0))-(((battery/range_nm)*D83*ROUND(K83*L83*revleg_thin,0)*VLOOKUP(B83,country_opex,3,FALSE))+V83+W83+X83+Y83+Z83))&lt;=0,"",VLOOKUP(B83,country_opex,7,FALSE)/((S83*pax_cap*load_thin*ROUND(K83*L83*revleg_thin,0))-(((battery/range_nm)*D83*ROUND(K83*L83*revleg_thin,0)*VLOOKUP(B83,country_opex,3,FALSE))+V83+W83+X83+Y83+Z83)))</f>
@@ -17675,12 +17569,12 @@
       </c>
       <c r="AW83" s="44" t="inlineStr">
         <is>
-          <t>[LB-255 PREMIUM RE-FARE: subsidized comparable $3.5 lifted to premium on-demand floor $18.0] handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (kerala)</t>
+          <t>M2M Ferries published Mumbai Ferry Wharf/Bhaucha Dhakka ↔ Mandwa Ro-Pax fare floor: passenger fares from ₹400 onwards; motorcycle ₹210 onwards; 4-wheelers ₹1,020 onwards; buses ₹4,500 onwards; vehicle deck over 120 cars/two-wheelers/buses. Converted at ~INR85/USD: ₹400 ≈ $4.70. This is a direct fare floor/comparable, not a premium Navier fare claim.</t>
         </is>
       </c>
       <c r="AX83" s="44" t="inlineStr">
         <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (kerala)</t>
+          <t>PR #58 Mumbai spine route-count split (11 sealed rows × anchor 120,000 pax/yr)</t>
         </is>
       </c>
     </row>
@@ -17697,11 +17591,11 @@
       </c>
       <c r="C84" s="30" t="inlineStr">
         <is>
-          <t>Marina Russian B2B Thai Spa Service near me → Goveia Marina</t>
+          <t>Panaji Jetty → Goa</t>
         </is>
       </c>
       <c r="D84" s="31" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="E84" s="26" t="n">
         <v>8</v>
@@ -17891,11 +17785,11 @@
       </c>
       <c r="C85" s="30" t="inlineStr">
         <is>
-          <t>Mandwa Jetty → Mumbai Harbour</t>
+          <t>Pirpau Jetty → Mumbai Trans-Harbour Navi Mumbai Toll Plaza</t>
         </is>
       </c>
       <c r="D85" s="31" t="n">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
       <c r="E85" s="26" t="n"/>
       <c r="F85" s="32" t="inlineStr">
@@ -18077,7 +17971,7 @@
     <row r="86">
       <c r="A86" s="29" t="inlineStr">
         <is>
-          <t>Ola Mumbai</t>
+          <t>India Mumbai Ola</t>
         </is>
       </c>
       <c r="B86" s="29" t="inlineStr">
@@ -18087,13 +17981,15 @@
       </c>
       <c r="C86" s="30" t="inlineStr">
         <is>
-          <t>Mumbai Harbour → Mandwa Jetty</t>
+          <t>Mora → Marina Bay Bistro @KARANJA Fishing Dock</t>
         </is>
       </c>
       <c r="D86" s="31" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="E86" s="26" t="n"/>
+        <v>6.7</v>
+      </c>
+      <c r="E86" s="26" t="n">
+        <v>18</v>
+      </c>
       <c r="F86" s="32" t="inlineStr">
         <is>
           <t>T3</t>
@@ -18204,7 +18100,7 @@
         <v/>
       </c>
       <c r="AG86" s="31" t="n">
-        <v>10909</v>
+        <v>5000</v>
       </c>
       <c r="AH86" s="32" t="inlineStr">
         <is>
@@ -18241,11 +18137,7 @@
       </c>
       <c r="AP86" s="40" t="n"/>
       <c r="AQ86" s="41" t="n"/>
-      <c r="AR86" s="41" t="inlineStr">
-        <is>
-          <t>experience_upside</t>
-        </is>
-      </c>
+      <c r="AR86" s="41" t="n"/>
       <c r="AS86" s="42" t="n"/>
       <c r="AT86" s="43">
         <f>IF(((S86*pax_cap*load_thin*ROUND(K86*L86*revleg_thin,0))-(((battery/range_nm)*D86*ROUND(K86*L86*revleg_thin,0)*VLOOKUP(B86,country_opex,3,FALSE))+V86+W86+X86+Y86+Z86))&lt;=0,"",VLOOKUP(B86,country_opex,7,FALSE)/((S86*pax_cap*load_thin*ROUND(K86*L86*revleg_thin,0))-(((battery/range_nm)*D86*ROUND(K86*L86*revleg_thin,0)*VLOOKUP(B86,country_opex,3,FALSE))+V86+W86+X86+Y86+Z86)))</f>
@@ -18261,19 +18153,19 @@
       </c>
       <c r="AW86" s="44" t="inlineStr">
         <is>
-          <t>M2M Ferries published Mumbai Ferry Wharf/Bhaucha Dhakka ↔ Mandwa Ro-Pax fare floor: passenger fares from ₹400 onwards; motorcycle ₹210 onwards; 4-wheelers ₹1,020 onwards; buses ₹4,500 onwards; vehicle deck over 120 cars/two-wheelers/buses. Converted at ~INR85/USD: ₹400 ≈ $4.70. This is a direct fare floor/comparable, not a premium Navier fare claim.</t>
+          <t>[LB-255 PREMIUM RE-FARE: subsidized comparable $5.5 lifted to premium on-demand floor $18.0] handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (mumbai)</t>
         </is>
       </c>
       <c r="AX86" s="44" t="inlineStr">
         <is>
-          <t>PR #58 Mumbai spine route-count split (11 sealed rows × anchor 120,000 pax/yr)</t>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (mumbai)</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="29" t="inlineStr">
         <is>
-          <t>India Andaman Ola</t>
+          <t>India Goa Ola</t>
         </is>
       </c>
       <c r="B87" s="29" t="inlineStr">
@@ -18283,14 +18175,14 @@
       </c>
       <c r="C87" s="30" t="inlineStr">
         <is>
-          <t>Bambooflat Jetty → Game Fishing In Andaman | Bite Me Charter | Best Sport fishing in Andaman Islands</t>
+          <t>Villa Marina → Marina Russian B2B Thai Spa Service near me</t>
         </is>
       </c>
       <c r="D87" s="31" t="n">
-        <v>8.4</v>
+        <v>6.7</v>
       </c>
       <c r="E87" s="26" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="F87" s="32" t="inlineStr">
         <is>
@@ -18402,7 +18294,7 @@
         <v/>
       </c>
       <c r="AG87" s="31" t="n">
-        <v>5000</v>
+        <v>11250</v>
       </c>
       <c r="AH87" s="32" t="inlineStr">
         <is>
@@ -18455,19 +18347,19 @@
       </c>
       <c r="AW87" s="44" t="inlineStr">
         <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (goa)</t>
         </is>
       </c>
       <c r="AX87" s="44" t="inlineStr">
         <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (goa)</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="29" t="inlineStr">
         <is>
-          <t>India Mumbai Ola</t>
+          <t>India Kerala Ola</t>
         </is>
       </c>
       <c r="B88" s="29" t="inlineStr">
@@ -18477,11 +18369,11 @@
       </c>
       <c r="C88" s="30" t="inlineStr">
         <is>
-          <t>Cordelia Cruises → OLD HARBOR TEA &amp; COFFEE</t>
+          <t>Willingdon Island → Kerala Backwaters &amp; Kochi</t>
         </is>
       </c>
       <c r="D88" s="31" t="n">
-        <v>8.5</v>
+        <v>6.8</v>
       </c>
       <c r="E88" s="26" t="n">
         <v>18</v>
@@ -18596,7 +18488,7 @@
         <v/>
       </c>
       <c r="AG88" s="31" t="n">
-        <v>5000</v>
+        <v>29166</v>
       </c>
       <c r="AH88" s="32" t="inlineStr">
         <is>
@@ -18649,19 +18541,19 @@
       </c>
       <c r="AW88" s="44" t="inlineStr">
         <is>
-          <t>[LB-255 PREMIUM RE-FARE: subsidized comparable $5.5 lifted to premium on-demand floor $18.0] handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (mumbai)</t>
+          <t>[LB-255 PREMIUM RE-FARE: subsidized comparable $3.5 lifted to premium on-demand floor $18.0] handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (kerala)</t>
         </is>
       </c>
       <c r="AX88" s="44" t="inlineStr">
         <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (mumbai)</t>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (kerala)</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="29" t="inlineStr">
         <is>
-          <t>Ola Mumbai</t>
+          <t>India Goa Ola</t>
         </is>
       </c>
       <c r="B89" s="29" t="inlineStr">
@@ -18671,13 +18563,15 @@
       </c>
       <c r="C89" s="30" t="inlineStr">
         <is>
-          <t>Versova Ferry Wharf → Gateway of India</t>
+          <t>Marina Russian B2B Thai Spa Service near me → Goveia Marina</t>
         </is>
       </c>
       <c r="D89" s="31" t="n">
-        <v>12.43</v>
-      </c>
-      <c r="E89" s="26" t="n"/>
+        <v>7.5</v>
+      </c>
+      <c r="E89" s="26" t="n">
+        <v>8</v>
+      </c>
       <c r="F89" s="32" t="inlineStr">
         <is>
           <t>T3</t>
@@ -18788,7 +18682,7 @@
         <v/>
       </c>
       <c r="AG89" s="31" t="n">
-        <v>10909</v>
+        <v>11250</v>
       </c>
       <c r="AH89" s="32" t="inlineStr">
         <is>
@@ -18825,11 +18719,7 @@
       </c>
       <c r="AP89" s="40" t="n"/>
       <c r="AQ89" s="41" t="n"/>
-      <c r="AR89" s="41" t="inlineStr">
-        <is>
-          <t>experience_upside</t>
-        </is>
-      </c>
+      <c r="AR89" s="41" t="n"/>
       <c r="AS89" s="42" t="n"/>
       <c r="AT89" s="43">
         <f>IF(((S89*pax_cap*load_thin*ROUND(K89*L89*revleg_thin,0))-(((battery/range_nm)*D89*ROUND(K89*L89*revleg_thin,0)*VLOOKUP(B89,country_opex,3,FALSE))+V89+W89+X89+Y89+Z89))&lt;=0,"",VLOOKUP(B89,country_opex,7,FALSE)/((S89*pax_cap*load_thin*ROUND(K89*L89*revleg_thin,0))-(((battery/range_nm)*D89*ROUND(K89*L89*revleg_thin,0)*VLOOKUP(B89,country_opex,3,FALSE))+V89+W89+X89+Y89+Z89)))</f>
@@ -18845,19 +18735,19 @@
       </c>
       <c r="AW89" s="44" t="inlineStr">
         <is>
-          <t>M2M Ferries published Mumbai Ferry Wharf/Bhaucha Dhakka ↔ Mandwa Ro-Pax fare floor: passenger fares from ₹400 onwards; motorcycle ₹210 onwards; 4-wheelers ₹1,020 onwards; buses ₹4,500 onwards; vehicle deck over 120 cars/two-wheelers/buses. Converted at ~INR85/USD: ₹400 ≈ $4.70. This is a direct fare floor/comparable, not a premium Navier fare claim.</t>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (goa)</t>
         </is>
       </c>
       <c r="AX89" s="44" t="inlineStr">
         <is>
-          <t>PR #58 Mumbai spine route-count split (11 sealed rows × anchor 120,000 pax/yr)</t>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (goa)</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="29" t="inlineStr">
         <is>
-          <t>India Mumbai Ola</t>
+          <t>Ola Mumbai</t>
         </is>
       </c>
       <c r="B90" s="29" t="inlineStr">
@@ -18867,15 +18757,13 @@
       </c>
       <c r="C90" s="30" t="inlineStr">
         <is>
-          <t>Gorai / Marve Jetty → Nariman Point Water-Taxi Jetty</t>
+          <t>Mandwa Jetty → Mumbai Harbour</t>
         </is>
       </c>
       <c r="D90" s="31" t="n">
-        <v>13.45</v>
-      </c>
-      <c r="E90" s="26" t="n">
-        <v>18</v>
-      </c>
+        <v>7.8</v>
+      </c>
+      <c r="E90" s="26" t="n"/>
       <c r="F90" s="32" t="inlineStr">
         <is>
           <t>T3</t>
@@ -18986,7 +18874,7 @@
         <v/>
       </c>
       <c r="AG90" s="31" t="n">
-        <v>5000</v>
+        <v>10909</v>
       </c>
       <c r="AH90" s="32" t="inlineStr">
         <is>
@@ -19023,7 +18911,11 @@
       </c>
       <c r="AP90" s="40" t="n"/>
       <c r="AQ90" s="41" t="n"/>
-      <c r="AR90" s="41" t="n"/>
+      <c r="AR90" s="41" t="inlineStr">
+        <is>
+          <t>experience_upside</t>
+        </is>
+      </c>
       <c r="AS90" s="42" t="n"/>
       <c r="AT90" s="43">
         <f>IF(((S90*pax_cap*load_thin*ROUND(K90*L90*revleg_thin,0))-(((battery/range_nm)*D90*ROUND(K90*L90*revleg_thin,0)*VLOOKUP(B90,country_opex,3,FALSE))+V90+W90+X90+Y90+Z90))&lt;=0,"",VLOOKUP(B90,country_opex,7,FALSE)/((S90*pax_cap*load_thin*ROUND(K90*L90*revleg_thin,0))-(((battery/range_nm)*D90*ROUND(K90*L90*revleg_thin,0)*VLOOKUP(B90,country_opex,3,FALSE))+V90+W90+X90+Y90+Z90)))</f>
@@ -19039,19 +18931,19 @@
       </c>
       <c r="AW90" s="44" t="inlineStr">
         <is>
-          <t>[LB-255 PREMIUM RE-FARE: subsidized comparable $5.5 lifted to premium on-demand floor $18.0] handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (mumbai)</t>
+          <t>M2M Ferries published Mumbai Ferry Wharf/Bhaucha Dhakka ↔ Mandwa Ro-Pax fare floor: passenger fares from ₹400 onwards; motorcycle ₹210 onwards; 4-wheelers ₹1,020 onwards; buses ₹4,500 onwards; vehicle deck over 120 cars/two-wheelers/buses. Converted at ~INR85/USD: ₹400 ≈ $4.70. This is a direct fare floor/comparable, not a premium Navier fare claim.</t>
         </is>
       </c>
       <c r="AX90" s="44" t="inlineStr">
         <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (mumbai)</t>
+          <t>PR #58 Mumbai spine route-count split (11 sealed rows × anchor 120,000 pax/yr)</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="29" t="inlineStr">
         <is>
-          <t>India Andaman Ola</t>
+          <t>Ola Mumbai</t>
         </is>
       </c>
       <c r="B91" s="29" t="inlineStr">
@@ -19061,15 +18953,13 @@
       </c>
       <c r="C91" s="30" t="inlineStr">
         <is>
-          <t>APARUPA SANDS MARINA → Shaheed Dweep Jetty</t>
+          <t>Mumbai Harbour → Mandwa Jetty</t>
         </is>
       </c>
       <c r="D91" s="31" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="E91" s="26" t="n">
-        <v>22</v>
-      </c>
+        <v>7.9</v>
+      </c>
+      <c r="E91" s="26" t="n"/>
       <c r="F91" s="32" t="inlineStr">
         <is>
           <t>T3</t>
@@ -19180,7 +19070,7 @@
         <v/>
       </c>
       <c r="AG91" s="31" t="n">
-        <v>5000</v>
+        <v>10909</v>
       </c>
       <c r="AH91" s="32" t="inlineStr">
         <is>
@@ -19217,7 +19107,11 @@
       </c>
       <c r="AP91" s="40" t="n"/>
       <c r="AQ91" s="41" t="n"/>
-      <c r="AR91" s="41" t="n"/>
+      <c r="AR91" s="41" t="inlineStr">
+        <is>
+          <t>experience_upside</t>
+        </is>
+      </c>
       <c r="AS91" s="42" t="n"/>
       <c r="AT91" s="43">
         <f>IF(((S91*pax_cap*load_thin*ROUND(K91*L91*revleg_thin,0))-(((battery/range_nm)*D91*ROUND(K91*L91*revleg_thin,0)*VLOOKUP(B91,country_opex,3,FALSE))+V91+W91+X91+Y91+Z91))&lt;=0,"",VLOOKUP(B91,country_opex,7,FALSE)/((S91*pax_cap*load_thin*ROUND(K91*L91*revleg_thin,0))-(((battery/range_nm)*D91*ROUND(K91*L91*revleg_thin,0)*VLOOKUP(B91,country_opex,3,FALSE))+V91+W91+X91+Y91+Z91)))</f>
@@ -19233,12 +19127,12 @@
       </c>
       <c r="AW91" s="44" t="inlineStr">
         <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
+          <t>M2M Ferries published Mumbai Ferry Wharf/Bhaucha Dhakka ↔ Mandwa Ro-Pax fare floor: passenger fares from ₹400 onwards; motorcycle ₹210 onwards; 4-wheelers ₹1,020 onwards; buses ₹4,500 onwards; vehicle deck over 120 cars/two-wheelers/buses. Converted at ~INR85/USD: ₹400 ≈ $4.70. This is a direct fare floor/comparable, not a premium Navier fare claim.</t>
         </is>
       </c>
       <c r="AX91" s="44" t="inlineStr">
         <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
+          <t>PR #58 Mumbai spine route-count split (11 sealed rows × anchor 120,000 pax/yr)</t>
         </is>
       </c>
     </row>
@@ -19255,11 +19149,11 @@
       </c>
       <c r="C92" s="30" t="inlineStr">
         <is>
-          <t>Office Of Assistant Engineer Civil, Andaman Lakshdweep Harbour Work Havelock → Shaheed Dweep Jetty</t>
+          <t>Bambooflat Jetty → Game Fishing In Andaman | Bite Me Charter | Best Sport fishing in Andaman Islands</t>
         </is>
       </c>
       <c r="D92" s="31" t="n">
-        <v>14.6</v>
+        <v>8.4</v>
       </c>
       <c r="E92" s="26" t="n">
         <v>22</v>
@@ -19439,7 +19333,7 @@
     <row r="93">
       <c r="A93" s="29" t="inlineStr">
         <is>
-          <t>India Andaman Ola</t>
+          <t>India Mumbai Ola</t>
         </is>
       </c>
       <c r="B93" s="29" t="inlineStr">
@@ -19449,14 +19343,14 @@
       </c>
       <c r="C93" s="30" t="inlineStr">
         <is>
-          <t>Office Of Assistant Engineer Civil, Andaman Lakshdweep Harbour Work Havelock → Shaheed Dweep Jetty</t>
+          <t>Cordelia Cruises → OLD HARBOR TEA &amp; COFFEE</t>
         </is>
       </c>
       <c r="D93" s="31" t="n">
-        <v>15.2</v>
+        <v>8.5</v>
       </c>
       <c r="E93" s="26" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F93" s="32" t="inlineStr">
         <is>
@@ -19621,19 +19515,19 @@
       </c>
       <c r="AW93" s="44" t="inlineStr">
         <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
+          <t>[LB-255 PREMIUM RE-FARE: subsidized comparable $5.5 lifted to premium on-demand floor $18.0] handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (mumbai)</t>
         </is>
       </c>
       <c r="AX93" s="44" t="inlineStr">
         <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (mumbai)</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="29" t="inlineStr">
         <is>
-          <t>India Andaman Ola</t>
+          <t>Ola Mumbai</t>
         </is>
       </c>
       <c r="B94" s="29" t="inlineStr">
@@ -19643,15 +19537,13 @@
       </c>
       <c r="C94" s="30" t="inlineStr">
         <is>
-          <t>Bambooflat Jetty → Shaheed Dweep Jetty</t>
+          <t>Versova Ferry Wharf → Gateway of India</t>
         </is>
       </c>
       <c r="D94" s="31" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="E94" s="26" t="n">
-        <v>22</v>
-      </c>
+        <v>12.43</v>
+      </c>
+      <c r="E94" s="26" t="n"/>
       <c r="F94" s="32" t="inlineStr">
         <is>
           <t>T3</t>
@@ -19762,7 +19654,7 @@
         <v/>
       </c>
       <c r="AG94" s="31" t="n">
-        <v>5000</v>
+        <v>10909</v>
       </c>
       <c r="AH94" s="32" t="inlineStr">
         <is>
@@ -19799,7 +19691,11 @@
       </c>
       <c r="AP94" s="40" t="n"/>
       <c r="AQ94" s="41" t="n"/>
-      <c r="AR94" s="41" t="n"/>
+      <c r="AR94" s="41" t="inlineStr">
+        <is>
+          <t>experience_upside</t>
+        </is>
+      </c>
       <c r="AS94" s="42" t="n"/>
       <c r="AT94" s="43">
         <f>IF(((S94*pax_cap*load_thin*ROUND(K94*L94*revleg_thin,0))-(((battery/range_nm)*D94*ROUND(K94*L94*revleg_thin,0)*VLOOKUP(B94,country_opex,3,FALSE))+V94+W94+X94+Y94+Z94))&lt;=0,"",VLOOKUP(B94,country_opex,7,FALSE)/((S94*pax_cap*load_thin*ROUND(K94*L94*revleg_thin,0))-(((battery/range_nm)*D94*ROUND(K94*L94*revleg_thin,0)*VLOOKUP(B94,country_opex,3,FALSE))+V94+W94+X94+Y94+Z94)))</f>
@@ -19815,19 +19711,19 @@
       </c>
       <c r="AW94" s="44" t="inlineStr">
         <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
+          <t>M2M Ferries published Mumbai Ferry Wharf/Bhaucha Dhakka ↔ Mandwa Ro-Pax fare floor: passenger fares from ₹400 onwards; motorcycle ₹210 onwards; 4-wheelers ₹1,020 onwards; buses ₹4,500 onwards; vehicle deck over 120 cars/two-wheelers/buses. Converted at ~INR85/USD: ₹400 ≈ $4.70. This is a direct fare floor/comparable, not a premium Navier fare claim.</t>
         </is>
       </c>
       <c r="AX94" s="44" t="inlineStr">
         <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
+          <t>PR #58 Mumbai spine route-count split (11 sealed rows × anchor 120,000 pax/yr)</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="29" t="inlineStr">
         <is>
-          <t>India Andaman Ola</t>
+          <t>India Mumbai Ola</t>
         </is>
       </c>
       <c r="B95" s="29" t="inlineStr">
@@ -19837,14 +19733,14 @@
       </c>
       <c r="C95" s="30" t="inlineStr">
         <is>
-          <t>Andaman → Office Of Assistant Engineer Civil, Andaman Lakshdweep Harbour Work Havelock</t>
+          <t>Gorai / Marve Jetty → Nariman Point Water-Taxi Jetty</t>
         </is>
       </c>
       <c r="D95" s="31" t="n">
-        <v>28.2</v>
+        <v>13.45</v>
       </c>
       <c r="E95" s="26" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F95" s="32" t="inlineStr">
         <is>
@@ -20009,12 +19905,12 @@
       </c>
       <c r="AW95" s="44" t="inlineStr">
         <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
+          <t>[LB-255 PREMIUM RE-FARE: subsidized comparable $5.5 lifted to premium on-demand floor $18.0] handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (mumbai)</t>
         </is>
       </c>
       <c r="AX95" s="44" t="inlineStr">
         <is>
-          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (mumbai)</t>
         </is>
       </c>
     </row>
@@ -20031,11 +19927,11 @@
       </c>
       <c r="C96" s="30" t="inlineStr">
         <is>
-          <t>Andaman → APARUPA SANDS MARINA</t>
+          <t>APARUPA SANDS MARINA → Shaheed Dweep Jetty</t>
         </is>
       </c>
       <c r="D96" s="31" t="n">
-        <v>29.4</v>
+        <v>13.9</v>
       </c>
       <c r="E96" s="26" t="n">
         <v>22</v>
@@ -20213,232 +20109,1438 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="45" t="inlineStr">
-        <is>
-          <t>TOTAL / median</t>
-        </is>
-      </c>
-      <c r="T97" s="46">
-        <f>SUM(T4:T96)</f>
-        <v/>
-      </c>
-      <c r="AC97" s="46">
-        <f>SUM(AC4:AC96)</f>
-        <v/>
-      </c>
-      <c r="AD97" s="47">
+      <c r="A97" s="29" t="inlineStr">
+        <is>
+          <t>India Andaman Ola</t>
+        </is>
+      </c>
+      <c r="B97" s="29" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C97" s="30" t="inlineStr">
+        <is>
+          <t>Office Of Assistant Engineer Civil, Andaman Lakshdweep Harbour Work Havelock → Shaheed Dweep Jetty</t>
+        </is>
+      </c>
+      <c r="D97" s="31" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="E97" s="26" t="n">
+        <v>22</v>
+      </c>
+      <c r="F97" s="32" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="G97" s="32" t="inlineStr">
+        <is>
+          <t>med-low</t>
+        </is>
+      </c>
+      <c r="H97" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I97" s="33">
+        <f>60*D97/cruise_kt</f>
+        <v/>
+      </c>
+      <c r="J97" s="33">
+        <f>I97+turn_min+dwell_min</f>
+        <v/>
+      </c>
+      <c r="K97" s="34">
+        <f>MIN(10,FLOOR(60*service_hr/J97,1))</f>
+        <v/>
+      </c>
+      <c r="L97" s="34">
+        <f>ROUND(365*mech_uptime*H97,0)</f>
+        <v/>
+      </c>
+      <c r="M97" s="35">
+        <f>mech_uptime</f>
+        <v/>
+      </c>
+      <c r="N97" s="35">
+        <f>revleg_sel</f>
+        <v/>
+      </c>
+      <c r="O97" s="34">
+        <f>ROUND(K97*L97*revleg_sel,0)</f>
+        <v/>
+      </c>
+      <c r="P97" s="36">
+        <f>load_sel</f>
+        <v/>
+      </c>
+      <c r="Q97" s="36">
+        <f>pax_cap*P97</f>
+        <v/>
+      </c>
+      <c r="R97" s="34">
+        <f>Q97*O97</f>
+        <v/>
+      </c>
+      <c r="S97" s="37">
+        <f>E97*discount</f>
+        <v/>
+      </c>
+      <c r="T97" s="38">
+        <f>S97*R97</f>
+        <v/>
+      </c>
+      <c r="U97" s="38">
+        <f>(battery/range_nm)*D97*O97*VLOOKUP(B97,country_opex,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="V97" s="38">
+        <f>VLOOKUP(B97,country_opex,2,FALSE)*crew_factor</f>
+        <v/>
+      </c>
+      <c r="W97" s="38">
+        <f>VLOOKUP(B97,country_opex,5,FALSE)</f>
+        <v/>
+      </c>
+      <c r="X97" s="38">
+        <f>maint</f>
+        <v/>
+      </c>
+      <c r="Y97" s="38">
+        <f>VLOOKUP(B97,country_opex,7,FALSE)*ins_pct</f>
+        <v/>
+      </c>
+      <c r="Z97" s="38">
+        <f>charge_berth</f>
+        <v/>
+      </c>
+      <c r="AA97" s="38">
+        <f>U97+V97+W97+X97+Y97+Z97</f>
+        <v/>
+      </c>
+      <c r="AB97" s="38">
+        <f>VLOOKUP(B97,country_opex,7,FALSE)/dep_years</f>
+        <v/>
+      </c>
+      <c r="AC97" s="38">
+        <f>T97-AA97</f>
+        <v/>
+      </c>
+      <c r="AD97" s="35">
         <f>IF(T97=0,"",AC97/T97)</f>
         <v/>
       </c>
-      <c r="AL97" s="48">
-        <f>SUM(AL4:AL96)</f>
-        <v/>
-      </c>
-      <c r="AM97" s="46">
-        <f>SUM(AM4:AM96)</f>
-        <v/>
+      <c r="AE97" s="36">
+        <f>IF(AC97&lt;=0,"",VLOOKUP(B97,country_opex,7,FALSE)/AC97)</f>
+        <v/>
+      </c>
+      <c r="AF97" s="33">
+        <f>((D97*O97/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D97*O97*VLOOKUP(B97,country_opex,4,FALSE))/1000</f>
+        <v/>
+      </c>
+      <c r="AG97" s="31" t="n">
+        <v>5000</v>
+      </c>
+      <c r="AH97" s="32" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="AI97" s="32" t="inlineStr">
+        <is>
+          <t>med-low</t>
+        </is>
+      </c>
+      <c r="AJ97" s="39" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AK97" s="34">
+        <f>IF(AG97="","",AG97*AJ97)</f>
+        <v/>
+      </c>
+      <c r="AL97" s="34">
+        <f>IF(OR(AG97="",R97=0),"",MIN(IF(AS97="",9.9E+99,AS97),FLOOR(AK97/R97,1)))</f>
+        <v/>
+      </c>
+      <c r="AM97" s="38">
+        <f>IF(AL97="","",AL97*T97)</f>
+        <v/>
+      </c>
+      <c r="AN97" s="36">
+        <f>IF(OR(AG97="",R97=0),"",MIN(IF(AS97="",9.9E+99,AS97),AK97/R97))</f>
+        <v/>
+      </c>
+      <c r="AO97" s="38">
+        <f>IF(AN97="","",AN97*T97)</f>
+        <v/>
+      </c>
+      <c r="AP97" s="40" t="n"/>
+      <c r="AQ97" s="41" t="n"/>
+      <c r="AR97" s="41" t="n"/>
+      <c r="AS97" s="42" t="n"/>
+      <c r="AT97" s="43">
+        <f>IF(((S97*pax_cap*load_thin*ROUND(K97*L97*revleg_thin,0))-(((battery/range_nm)*D97*ROUND(K97*L97*revleg_thin,0)*VLOOKUP(B97,country_opex,3,FALSE))+V97+W97+X97+Y97+Z97))&lt;=0,"",VLOOKUP(B97,country_opex,7,FALSE)/((S97*pax_cap*load_thin*ROUND(K97*L97*revleg_thin,0))-(((battery/range_nm)*D97*ROUND(K97*L97*revleg_thin,0)*VLOOKUP(B97,country_opex,3,FALSE))+V97+W97+X97+Y97+Z97)))</f>
+        <v/>
+      </c>
+      <c r="AU97" s="43">
+        <f>IF(((S97*pax_cap*load_mid*ROUND(K97*L97*revleg_mid,0))-(((battery/range_nm)*D97*ROUND(K97*L97*revleg_mid,0)*VLOOKUP(B97,country_opex,3,FALSE))+V97+W97+X97+Y97+Z97))&lt;=0,"",VLOOKUP(B97,country_opex,7,FALSE)/((S97*pax_cap*load_mid*ROUND(K97*L97*revleg_mid,0))-(((battery/range_nm)*D97*ROUND(K97*L97*revleg_mid,0)*VLOOKUP(B97,country_opex,3,FALSE))+V97+W97+X97+Y97+Z97)))</f>
+        <v/>
+      </c>
+      <c r="AV97" s="43">
+        <f>IF(((S97*pax_cap*load_full*ROUND(K97*L97*revleg_full,0))-(((battery/range_nm)*D97*ROUND(K97*L97*revleg_full,0)*VLOOKUP(B97,country_opex,3,FALSE))+V97+W97+X97+Y97+Z97))&lt;=0,"",VLOOKUP(B97,country_opex,7,FALSE)/((S97*pax_cap*load_full*ROUND(K97*L97*revleg_full,0))-(((battery/range_nm)*D97*ROUND(K97*L97*revleg_full,0)*VLOOKUP(B97,country_opex,3,FALSE))+V97+W97+X97+Y97+Z97)))</f>
+        <v/>
+      </c>
+      <c r="AW97" s="44" t="inlineStr">
+        <is>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
+        </is>
+      </c>
+      <c r="AX97" s="44" t="inlineStr">
+        <is>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="29" t="inlineStr">
+        <is>
+          <t>India Andaman Ola</t>
+        </is>
+      </c>
+      <c r="B98" s="29" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C98" s="30" t="inlineStr">
+        <is>
+          <t>Office Of Assistant Engineer Civil, Andaman Lakshdweep Harbour Work Havelock → Shaheed Dweep Jetty</t>
+        </is>
+      </c>
+      <c r="D98" s="31" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="E98" s="26" t="n">
+        <v>22</v>
+      </c>
+      <c r="F98" s="32" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="G98" s="32" t="inlineStr">
+        <is>
+          <t>med-low</t>
+        </is>
+      </c>
+      <c r="H98" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I98" s="33">
+        <f>60*D98/cruise_kt</f>
+        <v/>
+      </c>
+      <c r="J98" s="33">
+        <f>I98+turn_min+dwell_min</f>
+        <v/>
+      </c>
+      <c r="K98" s="34">
+        <f>MIN(10,FLOOR(60*service_hr/J98,1))</f>
+        <v/>
+      </c>
+      <c r="L98" s="34">
+        <f>ROUND(365*mech_uptime*H98,0)</f>
+        <v/>
+      </c>
+      <c r="M98" s="35">
+        <f>mech_uptime</f>
+        <v/>
+      </c>
+      <c r="N98" s="35">
+        <f>revleg_sel</f>
+        <v/>
+      </c>
+      <c r="O98" s="34">
+        <f>ROUND(K98*L98*revleg_sel,0)</f>
+        <v/>
+      </c>
+      <c r="P98" s="36">
+        <f>load_sel</f>
+        <v/>
+      </c>
+      <c r="Q98" s="36">
+        <f>pax_cap*P98</f>
+        <v/>
+      </c>
+      <c r="R98" s="34">
+        <f>Q98*O98</f>
+        <v/>
+      </c>
+      <c r="S98" s="37">
+        <f>E98*discount</f>
+        <v/>
+      </c>
+      <c r="T98" s="38">
+        <f>S98*R98</f>
+        <v/>
+      </c>
+      <c r="U98" s="38">
+        <f>(battery/range_nm)*D98*O98*VLOOKUP(B98,country_opex,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="V98" s="38">
+        <f>VLOOKUP(B98,country_opex,2,FALSE)*crew_factor</f>
+        <v/>
+      </c>
+      <c r="W98" s="38">
+        <f>VLOOKUP(B98,country_opex,5,FALSE)</f>
+        <v/>
+      </c>
+      <c r="X98" s="38">
+        <f>maint</f>
+        <v/>
+      </c>
+      <c r="Y98" s="38">
+        <f>VLOOKUP(B98,country_opex,7,FALSE)*ins_pct</f>
+        <v/>
+      </c>
+      <c r="Z98" s="38">
+        <f>charge_berth</f>
+        <v/>
+      </c>
+      <c r="AA98" s="38">
+        <f>U98+V98+W98+X98+Y98+Z98</f>
+        <v/>
+      </c>
+      <c r="AB98" s="38">
+        <f>VLOOKUP(B98,country_opex,7,FALSE)/dep_years</f>
+        <v/>
+      </c>
+      <c r="AC98" s="38">
+        <f>T98-AA98</f>
+        <v/>
+      </c>
+      <c r="AD98" s="35">
+        <f>IF(T98=0,"",AC98/T98)</f>
+        <v/>
+      </c>
+      <c r="AE98" s="36">
+        <f>IF(AC98&lt;=0,"",VLOOKUP(B98,country_opex,7,FALSE)/AC98)</f>
+        <v/>
+      </c>
+      <c r="AF98" s="33">
+        <f>((D98*O98/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D98*O98*VLOOKUP(B98,country_opex,4,FALSE))/1000</f>
+        <v/>
+      </c>
+      <c r="AG98" s="31" t="n">
+        <v>5000</v>
+      </c>
+      <c r="AH98" s="32" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="AI98" s="32" t="inlineStr">
+        <is>
+          <t>med-low</t>
+        </is>
+      </c>
+      <c r="AJ98" s="39" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AK98" s="34">
+        <f>IF(AG98="","",AG98*AJ98)</f>
+        <v/>
+      </c>
+      <c r="AL98" s="34">
+        <f>IF(OR(AG98="",R98=0),"",MIN(IF(AS98="",9.9E+99,AS98),FLOOR(AK98/R98,1)))</f>
+        <v/>
+      </c>
+      <c r="AM98" s="38">
+        <f>IF(AL98="","",AL98*T98)</f>
+        <v/>
+      </c>
+      <c r="AN98" s="36">
+        <f>IF(OR(AG98="",R98=0),"",MIN(IF(AS98="",9.9E+99,AS98),AK98/R98))</f>
+        <v/>
+      </c>
+      <c r="AO98" s="38">
+        <f>IF(AN98="","",AN98*T98)</f>
+        <v/>
+      </c>
+      <c r="AP98" s="40" t="n"/>
+      <c r="AQ98" s="41" t="n"/>
+      <c r="AR98" s="41" t="n"/>
+      <c r="AS98" s="42" t="n"/>
+      <c r="AT98" s="43">
+        <f>IF(((S98*pax_cap*load_thin*ROUND(K98*L98*revleg_thin,0))-(((battery/range_nm)*D98*ROUND(K98*L98*revleg_thin,0)*VLOOKUP(B98,country_opex,3,FALSE))+V98+W98+X98+Y98+Z98))&lt;=0,"",VLOOKUP(B98,country_opex,7,FALSE)/((S98*pax_cap*load_thin*ROUND(K98*L98*revleg_thin,0))-(((battery/range_nm)*D98*ROUND(K98*L98*revleg_thin,0)*VLOOKUP(B98,country_opex,3,FALSE))+V98+W98+X98+Y98+Z98)))</f>
+        <v/>
+      </c>
+      <c r="AU98" s="43">
+        <f>IF(((S98*pax_cap*load_mid*ROUND(K98*L98*revleg_mid,0))-(((battery/range_nm)*D98*ROUND(K98*L98*revleg_mid,0)*VLOOKUP(B98,country_opex,3,FALSE))+V98+W98+X98+Y98+Z98))&lt;=0,"",VLOOKUP(B98,country_opex,7,FALSE)/((S98*pax_cap*load_mid*ROUND(K98*L98*revleg_mid,0))-(((battery/range_nm)*D98*ROUND(K98*L98*revleg_mid,0)*VLOOKUP(B98,country_opex,3,FALSE))+V98+W98+X98+Y98+Z98)))</f>
+        <v/>
+      </c>
+      <c r="AV98" s="43">
+        <f>IF(((S98*pax_cap*load_full*ROUND(K98*L98*revleg_full,0))-(((battery/range_nm)*D98*ROUND(K98*L98*revleg_full,0)*VLOOKUP(B98,country_opex,3,FALSE))+V98+W98+X98+Y98+Z98))&lt;=0,"",VLOOKUP(B98,country_opex,7,FALSE)/((S98*pax_cap*load_full*ROUND(K98*L98*revleg_full,0))-(((battery/range_nm)*D98*ROUND(K98*L98*revleg_full,0)*VLOOKUP(B98,country_opex,3,FALSE))+V98+W98+X98+Y98+Z98)))</f>
+        <v/>
+      </c>
+      <c r="AW98" s="44" t="inlineStr">
+        <is>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
+        </is>
+      </c>
+      <c r="AX98" s="44" t="inlineStr">
+        <is>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
+        </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="8" t="inlineStr">
-        <is>
-          <t>Market fleet build-up — grounded floor (network-sum of raw vessel fractions per market, rounded once; subset slices excluded; legacy per-corridor-floor totals above kept for reference)</t>
-        </is>
-      </c>
+      <c r="A99" s="29" t="inlineStr">
+        <is>
+          <t>India Kolkata Ola</t>
+        </is>
+      </c>
+      <c r="B99" s="29" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C99" s="30" t="inlineStr">
+        <is>
+          <t>Millennium Park Jetty → Chandannagar Riverfront</t>
+        </is>
+      </c>
+      <c r="D99" s="31" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="E99" s="26" t="n">
+        <v>18</v>
+      </c>
+      <c r="F99" s="32" t="n"/>
+      <c r="G99" s="32" t="n"/>
+      <c r="H99" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I99" s="33">
+        <f>60*D99/cruise_kt</f>
+        <v/>
+      </c>
+      <c r="J99" s="33">
+        <f>I99+turn_min+dwell_min</f>
+        <v/>
+      </c>
+      <c r="K99" s="34">
+        <f>MIN(10,FLOOR(60*service_hr/J99,1))</f>
+        <v/>
+      </c>
+      <c r="L99" s="34">
+        <f>ROUND(365*mech_uptime*H99,0)</f>
+        <v/>
+      </c>
+      <c r="M99" s="35">
+        <f>mech_uptime</f>
+        <v/>
+      </c>
+      <c r="N99" s="35">
+        <f>revleg_sel</f>
+        <v/>
+      </c>
+      <c r="O99" s="34">
+        <f>ROUND(K99*L99*revleg_sel,0)</f>
+        <v/>
+      </c>
+      <c r="P99" s="36">
+        <f>load_sel</f>
+        <v/>
+      </c>
+      <c r="Q99" s="36">
+        <f>pax_cap*P99</f>
+        <v/>
+      </c>
+      <c r="R99" s="34">
+        <f>Q99*O99</f>
+        <v/>
+      </c>
+      <c r="S99" s="37">
+        <f>E99*discount</f>
+        <v/>
+      </c>
+      <c r="T99" s="38">
+        <f>S99*R99</f>
+        <v/>
+      </c>
+      <c r="U99" s="38">
+        <f>(battery/range_nm)*D99*O99*VLOOKUP(B99,country_opex,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="V99" s="38">
+        <f>VLOOKUP(B99,country_opex,2,FALSE)*crew_factor</f>
+        <v/>
+      </c>
+      <c r="W99" s="38">
+        <f>VLOOKUP(B99,country_opex,5,FALSE)</f>
+        <v/>
+      </c>
+      <c r="X99" s="38">
+        <f>maint</f>
+        <v/>
+      </c>
+      <c r="Y99" s="38">
+        <f>VLOOKUP(B99,country_opex,7,FALSE)*ins_pct</f>
+        <v/>
+      </c>
+      <c r="Z99" s="38">
+        <f>charge_berth</f>
+        <v/>
+      </c>
+      <c r="AA99" s="38">
+        <f>U99+V99+W99+X99+Y99+Z99</f>
+        <v/>
+      </c>
+      <c r="AB99" s="38">
+        <f>VLOOKUP(B99,country_opex,7,FALSE)/dep_years</f>
+        <v/>
+      </c>
+      <c r="AC99" s="38">
+        <f>T99-AA99</f>
+        <v/>
+      </c>
+      <c r="AD99" s="35">
+        <f>IF(T99=0,"",AC99/T99)</f>
+        <v/>
+      </c>
+      <c r="AE99" s="36">
+        <f>IF(AC99&lt;=0,"",VLOOKUP(B99,country_opex,7,FALSE)/AC99)</f>
+        <v/>
+      </c>
+      <c r="AF99" s="33">
+        <f>((D99*O99/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D99*O99*VLOOKUP(B99,country_opex,4,FALSE))/1000</f>
+        <v/>
+      </c>
+      <c r="AG99" s="31" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="AH99" s="32" t="n"/>
+      <c r="AI99" s="32" t="n"/>
+      <c r="AJ99" s="39" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AK99" s="34">
+        <f>IF(AG99="","",AG99*AJ99)</f>
+        <v/>
+      </c>
+      <c r="AL99" s="34">
+        <f>IF(OR(AG99="",R99=0),"",MIN(IF(AS99="",9.9E+99,AS99),FLOOR(AK99/R99,1)))</f>
+        <v/>
+      </c>
+      <c r="AM99" s="38">
+        <f>IF(AL99="","",AL99*T99)</f>
+        <v/>
+      </c>
+      <c r="AN99" s="36">
+        <f>IF(OR(AG99="",R99=0),"",MIN(IF(AS99="",9.9E+99,AS99),AK99/R99))</f>
+        <v/>
+      </c>
+      <c r="AO99" s="38">
+        <f>IF(AN99="","",AN99*T99)</f>
+        <v/>
+      </c>
+      <c r="AP99" s="40" t="n"/>
+      <c r="AQ99" s="41" t="n"/>
+      <c r="AR99" s="41" t="n"/>
+      <c r="AS99" s="42" t="n"/>
+      <c r="AT99" s="43">
+        <f>IF(((S99*pax_cap*load_thin*ROUND(K99*L99*revleg_thin,0))-(((battery/range_nm)*D99*ROUND(K99*L99*revleg_thin,0)*VLOOKUP(B99,country_opex,3,FALSE))+V99+W99+X99+Y99+Z99))&lt;=0,"",VLOOKUP(B99,country_opex,7,FALSE)/((S99*pax_cap*load_thin*ROUND(K99*L99*revleg_thin,0))-(((battery/range_nm)*D99*ROUND(K99*L99*revleg_thin,0)*VLOOKUP(B99,country_opex,3,FALSE))+V99+W99+X99+Y99+Z99)))</f>
+        <v/>
+      </c>
+      <c r="AU99" s="43">
+        <f>IF(((S99*pax_cap*load_mid*ROUND(K99*L99*revleg_mid,0))-(((battery/range_nm)*D99*ROUND(K99*L99*revleg_mid,0)*VLOOKUP(B99,country_opex,3,FALSE))+V99+W99+X99+Y99+Z99))&lt;=0,"",VLOOKUP(B99,country_opex,7,FALSE)/((S99*pax_cap*load_mid*ROUND(K99*L99*revleg_mid,0))-(((battery/range_nm)*D99*ROUND(K99*L99*revleg_mid,0)*VLOOKUP(B99,country_opex,3,FALSE))+V99+W99+X99+Y99+Z99)))</f>
+        <v/>
+      </c>
+      <c r="AV99" s="43">
+        <f>IF(((S99*pax_cap*load_full*ROUND(K99*L99*revleg_full,0))-(((battery/range_nm)*D99*ROUND(K99*L99*revleg_full,0)*VLOOKUP(B99,country_opex,3,FALSE))+V99+W99+X99+Y99+Z99))&lt;=0,"",VLOOKUP(B99,country_opex,7,FALSE)/((S99*pax_cap*load_full*ROUND(K99*L99*revleg_full,0))-(((battery/range_nm)*D99*ROUND(K99*L99*revleg_full,0)*VLOOKUP(B99,country_opex,3,FALSE))+V99+W99+X99+Y99+Z99)))</f>
+        <v/>
+      </c>
+      <c r="AW99" s="44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[LB-255 PREMIUM RE-FARE: subsidized comparable $2.5 lifted to premium on-demand floor $18.0] </t>
+        </is>
+      </c>
+      <c r="AX99" s="44" t="n"/>
     </row>
     <row r="100">
-      <c r="A100" s="24" t="inlineStr">
-        <is>
-          <t>Market</t>
-        </is>
-      </c>
-      <c r="B100" s="24" t="inlineStr">
-        <is>
-          <t>Fleet basis</t>
-        </is>
-      </c>
-      <c r="C100" s="24" t="inlineStr">
-        <is>
-          <t>Raw vessels (sum)</t>
-        </is>
-      </c>
-      <c r="D100" s="24" t="inlineStr">
-        <is>
-          <t>Fleet (rounded once)</t>
-        </is>
-      </c>
-      <c r="E100" s="24" t="inlineStr">
-        <is>
-          <t>Market rev/yr (raw sum)</t>
+      <c r="A100" s="29" t="inlineStr">
+        <is>
+          <t>India Andaman Ola</t>
+        </is>
+      </c>
+      <c r="B100" s="29" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C100" s="30" t="inlineStr">
+        <is>
+          <t>Bambooflat Jetty → Shaheed Dweep Jetty</t>
+        </is>
+      </c>
+      <c r="D100" s="31" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="E100" s="26" t="n">
+        <v>22</v>
+      </c>
+      <c r="F100" s="32" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="G100" s="32" t="inlineStr">
+        <is>
+          <t>med-low</t>
+        </is>
+      </c>
+      <c r="H100" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I100" s="33">
+        <f>60*D100/cruise_kt</f>
+        <v/>
+      </c>
+      <c r="J100" s="33">
+        <f>I100+turn_min+dwell_min</f>
+        <v/>
+      </c>
+      <c r="K100" s="34">
+        <f>MIN(10,FLOOR(60*service_hr/J100,1))</f>
+        <v/>
+      </c>
+      <c r="L100" s="34">
+        <f>ROUND(365*mech_uptime*H100,0)</f>
+        <v/>
+      </c>
+      <c r="M100" s="35">
+        <f>mech_uptime</f>
+        <v/>
+      </c>
+      <c r="N100" s="35">
+        <f>revleg_sel</f>
+        <v/>
+      </c>
+      <c r="O100" s="34">
+        <f>ROUND(K100*L100*revleg_sel,0)</f>
+        <v/>
+      </c>
+      <c r="P100" s="36">
+        <f>load_sel</f>
+        <v/>
+      </c>
+      <c r="Q100" s="36">
+        <f>pax_cap*P100</f>
+        <v/>
+      </c>
+      <c r="R100" s="34">
+        <f>Q100*O100</f>
+        <v/>
+      </c>
+      <c r="S100" s="37">
+        <f>E100*discount</f>
+        <v/>
+      </c>
+      <c r="T100" s="38">
+        <f>S100*R100</f>
+        <v/>
+      </c>
+      <c r="U100" s="38">
+        <f>(battery/range_nm)*D100*O100*VLOOKUP(B100,country_opex,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="V100" s="38">
+        <f>VLOOKUP(B100,country_opex,2,FALSE)*crew_factor</f>
+        <v/>
+      </c>
+      <c r="W100" s="38">
+        <f>VLOOKUP(B100,country_opex,5,FALSE)</f>
+        <v/>
+      </c>
+      <c r="X100" s="38">
+        <f>maint</f>
+        <v/>
+      </c>
+      <c r="Y100" s="38">
+        <f>VLOOKUP(B100,country_opex,7,FALSE)*ins_pct</f>
+        <v/>
+      </c>
+      <c r="Z100" s="38">
+        <f>charge_berth</f>
+        <v/>
+      </c>
+      <c r="AA100" s="38">
+        <f>U100+V100+W100+X100+Y100+Z100</f>
+        <v/>
+      </c>
+      <c r="AB100" s="38">
+        <f>VLOOKUP(B100,country_opex,7,FALSE)/dep_years</f>
+        <v/>
+      </c>
+      <c r="AC100" s="38">
+        <f>T100-AA100</f>
+        <v/>
+      </c>
+      <c r="AD100" s="35">
+        <f>IF(T100=0,"",AC100/T100)</f>
+        <v/>
+      </c>
+      <c r="AE100" s="36">
+        <f>IF(AC100&lt;=0,"",VLOOKUP(B100,country_opex,7,FALSE)/AC100)</f>
+        <v/>
+      </c>
+      <c r="AF100" s="33">
+        <f>((D100*O100/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D100*O100*VLOOKUP(B100,country_opex,4,FALSE))/1000</f>
+        <v/>
+      </c>
+      <c r="AG100" s="31" t="n">
+        <v>5000</v>
+      </c>
+      <c r="AH100" s="32" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="AI100" s="32" t="inlineStr">
+        <is>
+          <t>med-low</t>
+        </is>
+      </c>
+      <c r="AJ100" s="39" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AK100" s="34">
+        <f>IF(AG100="","",AG100*AJ100)</f>
+        <v/>
+      </c>
+      <c r="AL100" s="34">
+        <f>IF(OR(AG100="",R100=0),"",MIN(IF(AS100="",9.9E+99,AS100),FLOOR(AK100/R100,1)))</f>
+        <v/>
+      </c>
+      <c r="AM100" s="38">
+        <f>IF(AL100="","",AL100*T100)</f>
+        <v/>
+      </c>
+      <c r="AN100" s="36">
+        <f>IF(OR(AG100="",R100=0),"",MIN(IF(AS100="",9.9E+99,AS100),AK100/R100))</f>
+        <v/>
+      </c>
+      <c r="AO100" s="38">
+        <f>IF(AN100="","",AN100*T100)</f>
+        <v/>
+      </c>
+      <c r="AP100" s="40" t="n"/>
+      <c r="AQ100" s="41" t="n"/>
+      <c r="AR100" s="41" t="n"/>
+      <c r="AS100" s="42" t="n"/>
+      <c r="AT100" s="43">
+        <f>IF(((S100*pax_cap*load_thin*ROUND(K100*L100*revleg_thin,0))-(((battery/range_nm)*D100*ROUND(K100*L100*revleg_thin,0)*VLOOKUP(B100,country_opex,3,FALSE))+V100+W100+X100+Y100+Z100))&lt;=0,"",VLOOKUP(B100,country_opex,7,FALSE)/((S100*pax_cap*load_thin*ROUND(K100*L100*revleg_thin,0))-(((battery/range_nm)*D100*ROUND(K100*L100*revleg_thin,0)*VLOOKUP(B100,country_opex,3,FALSE))+V100+W100+X100+Y100+Z100)))</f>
+        <v/>
+      </c>
+      <c r="AU100" s="43">
+        <f>IF(((S100*pax_cap*load_mid*ROUND(K100*L100*revleg_mid,0))-(((battery/range_nm)*D100*ROUND(K100*L100*revleg_mid,0)*VLOOKUP(B100,country_opex,3,FALSE))+V100+W100+X100+Y100+Z100))&lt;=0,"",VLOOKUP(B100,country_opex,7,FALSE)/((S100*pax_cap*load_mid*ROUND(K100*L100*revleg_mid,0))-(((battery/range_nm)*D100*ROUND(K100*L100*revleg_mid,0)*VLOOKUP(B100,country_opex,3,FALSE))+V100+W100+X100+Y100+Z100)))</f>
+        <v/>
+      </c>
+      <c r="AV100" s="43">
+        <f>IF(((S100*pax_cap*load_full*ROUND(K100*L100*revleg_full,0))-(((battery/range_nm)*D100*ROUND(K100*L100*revleg_full,0)*VLOOKUP(B100,country_opex,3,FALSE))+V100+W100+X100+Y100+Z100))&lt;=0,"",VLOOKUP(B100,country_opex,7,FALSE)/((S100*pax_cap*load_full*ROUND(K100*L100*revleg_full,0))-(((battery/range_nm)*D100*ROUND(K100*L100*revleg_full,0)*VLOOKUP(B100,country_opex,3,FALSE))+V100+W100+X100+Y100+Z100)))</f>
+        <v/>
+      </c>
+      <c r="AW100" s="44" t="inlineStr">
+        <is>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
+        </is>
+      </c>
+      <c r="AX100" s="44" t="inlineStr">
+        <is>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="25" t="inlineStr">
+      <c r="A101" s="29" t="inlineStr">
         <is>
           <t>India Andaman Ola</t>
         </is>
       </c>
-      <c r="B101" s="13" t="inlineStr">
-        <is>
-          <t>network_sum / ceil</t>
-        </is>
-      </c>
-      <c r="C101" s="23">
-        <f>SUMIFS(AN4:AN96,A4:A96,"India Andaman Ola",AP4:AP96,"=",AQ4:AQ96,"=",AR4:AR96,"=")</f>
-        <v/>
-      </c>
-      <c r="D101" s="49">
-        <f>IF(C101=0,0,CEILING(C101,1))</f>
-        <v/>
-      </c>
-      <c r="E101" s="50">
-        <f>SUMIFS(AO4:AO96,A4:A96,"India Andaman Ola",AP4:AP96,"=",AQ4:AQ96,"=",AR4:AR96,"=")</f>
-        <v/>
+      <c r="B101" s="29" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C101" s="30" t="inlineStr">
+        <is>
+          <t>Andaman → Office Of Assistant Engineer Civil, Andaman Lakshdweep Harbour Work Havelock</t>
+        </is>
+      </c>
+      <c r="D101" s="31" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="E101" s="26" t="n">
+        <v>22</v>
+      </c>
+      <c r="F101" s="32" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="G101" s="32" t="inlineStr">
+        <is>
+          <t>med-low</t>
+        </is>
+      </c>
+      <c r="H101" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I101" s="33">
+        <f>60*D101/cruise_kt</f>
+        <v/>
+      </c>
+      <c r="J101" s="33">
+        <f>I101+turn_min+dwell_min</f>
+        <v/>
+      </c>
+      <c r="K101" s="34">
+        <f>MIN(10,FLOOR(60*service_hr/J101,1))</f>
+        <v/>
+      </c>
+      <c r="L101" s="34">
+        <f>ROUND(365*mech_uptime*H101,0)</f>
+        <v/>
+      </c>
+      <c r="M101" s="35">
+        <f>mech_uptime</f>
+        <v/>
+      </c>
+      <c r="N101" s="35">
+        <f>revleg_sel</f>
+        <v/>
+      </c>
+      <c r="O101" s="34">
+        <f>ROUND(K101*L101*revleg_sel,0)</f>
+        <v/>
+      </c>
+      <c r="P101" s="36">
+        <f>load_sel</f>
+        <v/>
+      </c>
+      <c r="Q101" s="36">
+        <f>pax_cap*P101</f>
+        <v/>
+      </c>
+      <c r="R101" s="34">
+        <f>Q101*O101</f>
+        <v/>
+      </c>
+      <c r="S101" s="37">
+        <f>E101*discount</f>
+        <v/>
+      </c>
+      <c r="T101" s="38">
+        <f>S101*R101</f>
+        <v/>
+      </c>
+      <c r="U101" s="38">
+        <f>(battery/range_nm)*D101*O101*VLOOKUP(B101,country_opex,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="V101" s="38">
+        <f>VLOOKUP(B101,country_opex,2,FALSE)*crew_factor</f>
+        <v/>
+      </c>
+      <c r="W101" s="38">
+        <f>VLOOKUP(B101,country_opex,5,FALSE)</f>
+        <v/>
+      </c>
+      <c r="X101" s="38">
+        <f>maint</f>
+        <v/>
+      </c>
+      <c r="Y101" s="38">
+        <f>VLOOKUP(B101,country_opex,7,FALSE)*ins_pct</f>
+        <v/>
+      </c>
+      <c r="Z101" s="38">
+        <f>charge_berth</f>
+        <v/>
+      </c>
+      <c r="AA101" s="38">
+        <f>U101+V101+W101+X101+Y101+Z101</f>
+        <v/>
+      </c>
+      <c r="AB101" s="38">
+        <f>VLOOKUP(B101,country_opex,7,FALSE)/dep_years</f>
+        <v/>
+      </c>
+      <c r="AC101" s="38">
+        <f>T101-AA101</f>
+        <v/>
+      </c>
+      <c r="AD101" s="35">
+        <f>IF(T101=0,"",AC101/T101)</f>
+        <v/>
+      </c>
+      <c r="AE101" s="36">
+        <f>IF(AC101&lt;=0,"",VLOOKUP(B101,country_opex,7,FALSE)/AC101)</f>
+        <v/>
+      </c>
+      <c r="AF101" s="33">
+        <f>((D101*O101/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D101*O101*VLOOKUP(B101,country_opex,4,FALSE))/1000</f>
+        <v/>
+      </c>
+      <c r="AG101" s="31" t="n">
+        <v>5000</v>
+      </c>
+      <c r="AH101" s="32" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="AI101" s="32" t="inlineStr">
+        <is>
+          <t>med-low</t>
+        </is>
+      </c>
+      <c r="AJ101" s="39" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AK101" s="34">
+        <f>IF(AG101="","",AG101*AJ101)</f>
+        <v/>
+      </c>
+      <c r="AL101" s="34">
+        <f>IF(OR(AG101="",R101=0),"",MIN(IF(AS101="",9.9E+99,AS101),FLOOR(AK101/R101,1)))</f>
+        <v/>
+      </c>
+      <c r="AM101" s="38">
+        <f>IF(AL101="","",AL101*T101)</f>
+        <v/>
+      </c>
+      <c r="AN101" s="36">
+        <f>IF(OR(AG101="",R101=0),"",MIN(IF(AS101="",9.9E+99,AS101),AK101/R101))</f>
+        <v/>
+      </c>
+      <c r="AO101" s="38">
+        <f>IF(AN101="","",AN101*T101)</f>
+        <v/>
+      </c>
+      <c r="AP101" s="40" t="n"/>
+      <c r="AQ101" s="41" t="n"/>
+      <c r="AR101" s="41" t="n"/>
+      <c r="AS101" s="42" t="n"/>
+      <c r="AT101" s="43">
+        <f>IF(((S101*pax_cap*load_thin*ROUND(K101*L101*revleg_thin,0))-(((battery/range_nm)*D101*ROUND(K101*L101*revleg_thin,0)*VLOOKUP(B101,country_opex,3,FALSE))+V101+W101+X101+Y101+Z101))&lt;=0,"",VLOOKUP(B101,country_opex,7,FALSE)/((S101*pax_cap*load_thin*ROUND(K101*L101*revleg_thin,0))-(((battery/range_nm)*D101*ROUND(K101*L101*revleg_thin,0)*VLOOKUP(B101,country_opex,3,FALSE))+V101+W101+X101+Y101+Z101)))</f>
+        <v/>
+      </c>
+      <c r="AU101" s="43">
+        <f>IF(((S101*pax_cap*load_mid*ROUND(K101*L101*revleg_mid,0))-(((battery/range_nm)*D101*ROUND(K101*L101*revleg_mid,0)*VLOOKUP(B101,country_opex,3,FALSE))+V101+W101+X101+Y101+Z101))&lt;=0,"",VLOOKUP(B101,country_opex,7,FALSE)/((S101*pax_cap*load_mid*ROUND(K101*L101*revleg_mid,0))-(((battery/range_nm)*D101*ROUND(K101*L101*revleg_mid,0)*VLOOKUP(B101,country_opex,3,FALSE))+V101+W101+X101+Y101+Z101)))</f>
+        <v/>
+      </c>
+      <c r="AV101" s="43">
+        <f>IF(((S101*pax_cap*load_full*ROUND(K101*L101*revleg_full,0))-(((battery/range_nm)*D101*ROUND(K101*L101*revleg_full,0)*VLOOKUP(B101,country_opex,3,FALSE))+V101+W101+X101+Y101+Z101))&lt;=0,"",VLOOKUP(B101,country_opex,7,FALSE)/((S101*pax_cap*load_full*ROUND(K101*L101*revleg_full,0))-(((battery/range_nm)*D101*ROUND(K101*L101*revleg_full,0)*VLOOKUP(B101,country_opex,3,FALSE))+V101+W101+X101+Y101+Z101)))</f>
+        <v/>
+      </c>
+      <c r="AW101" s="44" t="inlineStr">
+        <is>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
+        </is>
+      </c>
+      <c r="AX101" s="44" t="inlineStr">
+        <is>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
+        </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="25" t="inlineStr">
-        <is>
-          <t>Ola Mumbai</t>
-        </is>
-      </c>
-      <c r="B102" s="13" t="inlineStr">
-        <is>
-          <t>per_corridor_floor</t>
-        </is>
-      </c>
-      <c r="C102" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D102" s="49">
-        <f>SUMIFS(AL4:AL96,A4:A96,"Ola Mumbai",AP4:AP96,"=",AQ4:AQ96,"=",AR4:AR96,"=")</f>
-        <v/>
-      </c>
-      <c r="E102" s="50">
-        <f>SUMIFS(AM4:AM96,A4:A96,"Ola Mumbai",AP4:AP96,"=",AQ4:AQ96,"=",AR4:AR96,"=")</f>
-        <v/>
+      <c r="A102" s="29" t="inlineStr">
+        <is>
+          <t>India Andaman Ola</t>
+        </is>
+      </c>
+      <c r="B102" s="29" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C102" s="30" t="inlineStr">
+        <is>
+          <t>Andaman → APARUPA SANDS MARINA</t>
+        </is>
+      </c>
+      <c r="D102" s="31" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="E102" s="26" t="n">
+        <v>22</v>
+      </c>
+      <c r="F102" s="32" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="G102" s="32" t="inlineStr">
+        <is>
+          <t>med-low</t>
+        </is>
+      </c>
+      <c r="H102" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I102" s="33">
+        <f>60*D102/cruise_kt</f>
+        <v/>
+      </c>
+      <c r="J102" s="33">
+        <f>I102+turn_min+dwell_min</f>
+        <v/>
+      </c>
+      <c r="K102" s="34">
+        <f>MIN(10,FLOOR(60*service_hr/J102,1))</f>
+        <v/>
+      </c>
+      <c r="L102" s="34">
+        <f>ROUND(365*mech_uptime*H102,0)</f>
+        <v/>
+      </c>
+      <c r="M102" s="35">
+        <f>mech_uptime</f>
+        <v/>
+      </c>
+      <c r="N102" s="35">
+        <f>revleg_sel</f>
+        <v/>
+      </c>
+      <c r="O102" s="34">
+        <f>ROUND(K102*L102*revleg_sel,0)</f>
+        <v/>
+      </c>
+      <c r="P102" s="36">
+        <f>load_sel</f>
+        <v/>
+      </c>
+      <c r="Q102" s="36">
+        <f>pax_cap*P102</f>
+        <v/>
+      </c>
+      <c r="R102" s="34">
+        <f>Q102*O102</f>
+        <v/>
+      </c>
+      <c r="S102" s="37">
+        <f>E102*discount</f>
+        <v/>
+      </c>
+      <c r="T102" s="38">
+        <f>S102*R102</f>
+        <v/>
+      </c>
+      <c r="U102" s="38">
+        <f>(battery/range_nm)*D102*O102*VLOOKUP(B102,country_opex,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="V102" s="38">
+        <f>VLOOKUP(B102,country_opex,2,FALSE)*crew_factor</f>
+        <v/>
+      </c>
+      <c r="W102" s="38">
+        <f>VLOOKUP(B102,country_opex,5,FALSE)</f>
+        <v/>
+      </c>
+      <c r="X102" s="38">
+        <f>maint</f>
+        <v/>
+      </c>
+      <c r="Y102" s="38">
+        <f>VLOOKUP(B102,country_opex,7,FALSE)*ins_pct</f>
+        <v/>
+      </c>
+      <c r="Z102" s="38">
+        <f>charge_berth</f>
+        <v/>
+      </c>
+      <c r="AA102" s="38">
+        <f>U102+V102+W102+X102+Y102+Z102</f>
+        <v/>
+      </c>
+      <c r="AB102" s="38">
+        <f>VLOOKUP(B102,country_opex,7,FALSE)/dep_years</f>
+        <v/>
+      </c>
+      <c r="AC102" s="38">
+        <f>T102-AA102</f>
+        <v/>
+      </c>
+      <c r="AD102" s="35">
+        <f>IF(T102=0,"",AC102/T102)</f>
+        <v/>
+      </c>
+      <c r="AE102" s="36">
+        <f>IF(AC102&lt;=0,"",VLOOKUP(B102,country_opex,7,FALSE)/AC102)</f>
+        <v/>
+      </c>
+      <c r="AF102" s="33">
+        <f>((D102*O102/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D102*O102*VLOOKUP(B102,country_opex,4,FALSE))/1000</f>
+        <v/>
+      </c>
+      <c r="AG102" s="31" t="n">
+        <v>5000</v>
+      </c>
+      <c r="AH102" s="32" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="AI102" s="32" t="inlineStr">
+        <is>
+          <t>med-low</t>
+        </is>
+      </c>
+      <c r="AJ102" s="39" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AK102" s="34">
+        <f>IF(AG102="","",AG102*AJ102)</f>
+        <v/>
+      </c>
+      <c r="AL102" s="34">
+        <f>IF(OR(AG102="",R102=0),"",MIN(IF(AS102="",9.9E+99,AS102),FLOOR(AK102/R102,1)))</f>
+        <v/>
+      </c>
+      <c r="AM102" s="38">
+        <f>IF(AL102="","",AL102*T102)</f>
+        <v/>
+      </c>
+      <c r="AN102" s="36">
+        <f>IF(OR(AG102="",R102=0),"",MIN(IF(AS102="",9.9E+99,AS102),AK102/R102))</f>
+        <v/>
+      </c>
+      <c r="AO102" s="38">
+        <f>IF(AN102="","",AN102*T102)</f>
+        <v/>
+      </c>
+      <c r="AP102" s="40" t="n"/>
+      <c r="AQ102" s="41" t="n"/>
+      <c r="AR102" s="41" t="n"/>
+      <c r="AS102" s="42" t="n"/>
+      <c r="AT102" s="43">
+        <f>IF(((S102*pax_cap*load_thin*ROUND(K102*L102*revleg_thin,0))-(((battery/range_nm)*D102*ROUND(K102*L102*revleg_thin,0)*VLOOKUP(B102,country_opex,3,FALSE))+V102+W102+X102+Y102+Z102))&lt;=0,"",VLOOKUP(B102,country_opex,7,FALSE)/((S102*pax_cap*load_thin*ROUND(K102*L102*revleg_thin,0))-(((battery/range_nm)*D102*ROUND(K102*L102*revleg_thin,0)*VLOOKUP(B102,country_opex,3,FALSE))+V102+W102+X102+Y102+Z102)))</f>
+        <v/>
+      </c>
+      <c r="AU102" s="43">
+        <f>IF(((S102*pax_cap*load_mid*ROUND(K102*L102*revleg_mid,0))-(((battery/range_nm)*D102*ROUND(K102*L102*revleg_mid,0)*VLOOKUP(B102,country_opex,3,FALSE))+V102+W102+X102+Y102+Z102))&lt;=0,"",VLOOKUP(B102,country_opex,7,FALSE)/((S102*pax_cap*load_mid*ROUND(K102*L102*revleg_mid,0))-(((battery/range_nm)*D102*ROUND(K102*L102*revleg_mid,0)*VLOOKUP(B102,country_opex,3,FALSE))+V102+W102+X102+Y102+Z102)))</f>
+        <v/>
+      </c>
+      <c r="AV102" s="43">
+        <f>IF(((S102*pax_cap*load_full*ROUND(K102*L102*revleg_full,0))-(((battery/range_nm)*D102*ROUND(K102*L102*revleg_full,0)*VLOOKUP(B102,country_opex,3,FALSE))+V102+W102+X102+Y102+Z102))&lt;=0,"",VLOOKUP(B102,country_opex,7,FALSE)/((S102*pax_cap*load_full*ROUND(K102*L102*revleg_full,0))-(((battery/range_nm)*D102*ROUND(K102*L102*revleg_full,0)*VLOOKUP(B102,country_opex,3,FALSE))+V102+W102+X102+Y102+Z102)))</f>
+        <v/>
+      </c>
+      <c r="AW102" s="44" t="inlineStr">
+        <is>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
+        </is>
+      </c>
+      <c r="AX102" s="44" t="inlineStr">
+        <is>
+          <t>handoff/INDIA-ECONOMICS-SIDECAR-V0-2026-06-20.json (andaman)</t>
+        </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="25" t="inlineStr">
-        <is>
-          <t>India Goa Ola</t>
-        </is>
-      </c>
-      <c r="B103" s="13" t="inlineStr">
-        <is>
-          <t>network_sum / ceil</t>
-        </is>
-      </c>
-      <c r="C103" s="23">
-        <f>SUMIFS(AN4:AN96,A4:A96,"India Goa Ola",AP4:AP96,"=",AQ4:AQ96,"=",AR4:AR96,"=")</f>
-        <v/>
-      </c>
-      <c r="D103" s="49">
-        <f>IF(C103=0,0,CEILING(C103,1))</f>
-        <v/>
-      </c>
-      <c r="E103" s="50">
-        <f>SUMIFS(AO4:AO96,A4:A96,"India Goa Ola",AP4:AP96,"=",AQ4:AQ96,"=",AR4:AR96,"=")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="25" t="inlineStr">
-        <is>
-          <t>India Kerala Ola</t>
-        </is>
-      </c>
-      <c r="B104" s="13" t="inlineStr">
-        <is>
-          <t>network_sum / ceil</t>
-        </is>
-      </c>
-      <c r="C104" s="23">
-        <f>SUMIFS(AN4:AN96,A4:A96,"India Kerala Ola",AP4:AP96,"=",AQ4:AQ96,"=",AR4:AR96,"=")</f>
-        <v/>
-      </c>
-      <c r="D104" s="49">
-        <f>IF(C104=0,0,CEILING(C104,1))</f>
-        <v/>
-      </c>
-      <c r="E104" s="50">
-        <f>SUMIFS(AO4:AO96,A4:A96,"India Kerala Ola",AP4:AP96,"=",AQ4:AQ96,"=",AR4:AR96,"=")</f>
+      <c r="A103" s="45" t="inlineStr">
+        <is>
+          <t>TOTAL / median</t>
+        </is>
+      </c>
+      <c r="T103" s="46">
+        <f>SUM(T4:T102)</f>
+        <v/>
+      </c>
+      <c r="AC103" s="46">
+        <f>SUM(AC4:AC102)</f>
+        <v/>
+      </c>
+      <c r="AD103" s="47">
+        <f>IF(T103=0,"",AC103/T103)</f>
+        <v/>
+      </c>
+      <c r="AL103" s="48">
+        <f>SUM(AL4:AL102)</f>
+        <v/>
+      </c>
+      <c r="AM103" s="46">
+        <f>SUM(AM4:AM102)</f>
         <v/>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="25" t="inlineStr">
-        <is>
-          <t>India Mumbai Ola</t>
-        </is>
-      </c>
-      <c r="B105" s="13" t="inlineStr">
-        <is>
-          <t>network_sum / ceil</t>
-        </is>
-      </c>
-      <c r="C105" s="23">
-        <f>SUMIFS(AN4:AN96,A4:A96,"India Mumbai Ola",AP4:AP96,"=",AQ4:AQ96,"=",AR4:AR96,"=")</f>
-        <v/>
-      </c>
-      <c r="D105" s="49">
-        <f>IF(C105=0,0,CEILING(C105,1))</f>
-        <v/>
-      </c>
-      <c r="E105" s="50">
-        <f>SUMIFS(AO4:AO96,A4:A96,"India Mumbai Ola",AP4:AP96,"=",AQ4:AQ96,"=",AR4:AR96,"=")</f>
-        <v/>
+      <c r="A105" s="8" t="inlineStr">
+        <is>
+          <t>Market fleet build-up — grounded floor (network-sum of raw vessel fractions per market, rounded once; subset slices excluded; legacy per-corridor-floor totals above kept for reference)</t>
+        </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="45" t="inlineStr">
-        <is>
-          <t>GROUNDED FLOOR (PUBLISHED)</t>
-        </is>
-      </c>
-      <c r="D106" s="48">
-        <f>SUM(D101:D105)</f>
-        <v/>
-      </c>
-      <c r="E106" s="46">
-        <f>SUM(E101:E105)</f>
-        <v/>
+      <c r="A106" s="24" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B106" s="24" t="inlineStr">
+        <is>
+          <t>Fleet basis</t>
+        </is>
+      </c>
+      <c r="C106" s="24" t="inlineStr">
+        <is>
+          <t>Raw vessels (sum)</t>
+        </is>
+      </c>
+      <c r="D106" s="24" t="inlineStr">
+        <is>
+          <t>Fleet (rounded once)</t>
+        </is>
+      </c>
+      <c r="E106" s="24" t="inlineStr">
+        <is>
+          <t>Market rev/yr (raw sum)</t>
+        </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="20" t="inlineStr">
-        <is>
-          <t>ESTIMATED UPSIDE (LB-99 modal-shift / experience-upside tiers; held OUT of grounded floor)</t>
-        </is>
-      </c>
-      <c r="D107" s="51">
-        <f>SUMIF(AR4:AR96,"&lt;&gt;",AL4:AL96)</f>
-        <v/>
-      </c>
-      <c r="E107" s="52">
-        <f>SUMIF(AR4:AR96,"&lt;&gt;",AM4:AM96)</f>
+      <c r="A107" s="25" t="inlineStr">
+        <is>
+          <t>India Andaman Ola</t>
+        </is>
+      </c>
+      <c r="B107" s="13" t="inlineStr">
+        <is>
+          <t>network_sum / ceil</t>
+        </is>
+      </c>
+      <c r="C107" s="23">
+        <f>SUMIFS(AN4:AN102,A4:A102,"India Andaman Ola",AP4:AP102,"=",AQ4:AQ102,"=",AR4:AR102,"=")</f>
+        <v/>
+      </c>
+      <c r="D107" s="49">
+        <f>IF(C107=0,0,CEILING(C107,1))</f>
+        <v/>
+      </c>
+      <c r="E107" s="50">
+        <f>SUMIFS(AO4:AO102,A4:A102,"India Andaman Ola",AP4:AP102,"=",AQ4:AQ102,"=",AR4:AR102,"=")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="25" t="inlineStr">
+        <is>
+          <t>India Kolkata Ola</t>
+        </is>
+      </c>
+      <c r="B108" s="13" t="inlineStr">
+        <is>
+          <t>network_sum</t>
+        </is>
+      </c>
+      <c r="C108" s="23">
+        <f>SUMIFS(AN4:AN102,A4:A102,"India Kolkata Ola",AP4:AP102,"=",AQ4:AQ102,"=",AR4:AR102,"=")</f>
+        <v/>
+      </c>
+      <c r="D108" s="49">
+        <f>ROUND(C108,0)</f>
+        <v/>
+      </c>
+      <c r="E108" s="50">
+        <f>SUMIFS(AO4:AO102,A4:A102,"India Kolkata Ola",AP4:AP102,"=",AQ4:AQ102,"=",AR4:AR102,"=")</f>
         <v/>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="53" t="inlineStr">
+      <c r="A109" s="25" t="inlineStr">
+        <is>
+          <t>Ola Mumbai</t>
+        </is>
+      </c>
+      <c r="B109" s="13" t="inlineStr">
+        <is>
+          <t>per_corridor_floor</t>
+        </is>
+      </c>
+      <c r="C109" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D109" s="49">
+        <f>SUMIFS(AL4:AL102,A4:A102,"Ola Mumbai",AP4:AP102,"=",AQ4:AQ102,"=",AR4:AR102,"=")</f>
+        <v/>
+      </c>
+      <c r="E109" s="50">
+        <f>SUMIFS(AM4:AM102,A4:A102,"Ola Mumbai",AP4:AP102,"=",AQ4:AQ102,"=",AR4:AR102,"=")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="25" t="inlineStr">
+        <is>
+          <t>India Goa Ola</t>
+        </is>
+      </c>
+      <c r="B110" s="13" t="inlineStr">
+        <is>
+          <t>network_sum / ceil</t>
+        </is>
+      </c>
+      <c r="C110" s="23">
+        <f>SUMIFS(AN4:AN102,A4:A102,"India Goa Ola",AP4:AP102,"=",AQ4:AQ102,"=",AR4:AR102,"=")</f>
+        <v/>
+      </c>
+      <c r="D110" s="49">
+        <f>IF(C110=0,0,CEILING(C110,1))</f>
+        <v/>
+      </c>
+      <c r="E110" s="50">
+        <f>SUMIFS(AO4:AO102,A4:A102,"India Goa Ola",AP4:AP102,"=",AQ4:AQ102,"=",AR4:AR102,"=")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="25" t="inlineStr">
+        <is>
+          <t>India Kerala Ola</t>
+        </is>
+      </c>
+      <c r="B111" s="13" t="inlineStr">
+        <is>
+          <t>network_sum / ceil</t>
+        </is>
+      </c>
+      <c r="C111" s="23">
+        <f>SUMIFS(AN4:AN102,A4:A102,"India Kerala Ola",AP4:AP102,"=",AQ4:AQ102,"=",AR4:AR102,"=")</f>
+        <v/>
+      </c>
+      <c r="D111" s="49">
+        <f>IF(C111=0,0,CEILING(C111,1))</f>
+        <v/>
+      </c>
+      <c r="E111" s="50">
+        <f>SUMIFS(AO4:AO102,A4:A102,"India Kerala Ola",AP4:AP102,"=",AQ4:AQ102,"=",AR4:AR102,"=")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="25" t="inlineStr">
+        <is>
+          <t>India Mumbai Ola</t>
+        </is>
+      </c>
+      <c r="B112" s="13" t="inlineStr">
+        <is>
+          <t>network_sum / ceil</t>
+        </is>
+      </c>
+      <c r="C112" s="23">
+        <f>SUMIFS(AN4:AN102,A4:A102,"India Mumbai Ola",AP4:AP102,"=",AQ4:AQ102,"=",AR4:AR102,"=")</f>
+        <v/>
+      </c>
+      <c r="D112" s="49">
+        <f>IF(C112=0,0,CEILING(C112,1))</f>
+        <v/>
+      </c>
+      <c r="E112" s="50">
+        <f>SUMIFS(AO4:AO102,A4:A102,"India Mumbai Ola",AP4:AP102,"=",AQ4:AQ102,"=",AR4:AR102,"=")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="25" t="inlineStr">
+        <is>
+          <t>India Chennai Ola</t>
+        </is>
+      </c>
+      <c r="B113" s="13" t="inlineStr">
+        <is>
+          <t>network_sum</t>
+        </is>
+      </c>
+      <c r="C113" s="23">
+        <f>SUMIFS(AN4:AN102,A4:A102,"India Chennai Ola",AP4:AP102,"=",AQ4:AQ102,"=",AR4:AR102,"=")</f>
+        <v/>
+      </c>
+      <c r="D113" s="49">
+        <f>ROUND(C113,0)</f>
+        <v/>
+      </c>
+      <c r="E113" s="50">
+        <f>SUMIFS(AO4:AO102,A4:A102,"India Chennai Ola",AP4:AP102,"=",AQ4:AQ102,"=",AR4:AR102,"=")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="45" t="inlineStr">
+        <is>
+          <t>GROUNDED FLOOR (PUBLISHED)</t>
+        </is>
+      </c>
+      <c r="D114" s="48">
+        <f>SUM(D107:D113)</f>
+        <v/>
+      </c>
+      <c r="E114" s="46">
+        <f>SUM(E107:E113)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="20" t="inlineStr">
+        <is>
+          <t>ESTIMATED UPSIDE (LB-99 modal-shift / experience-upside tiers; held OUT of grounded floor)</t>
+        </is>
+      </c>
+      <c r="D115" s="51">
+        <f>SUMIF(AR4:AR102,"&lt;&gt;",AL4:AL102)</f>
+        <v/>
+      </c>
+      <c r="E115" s="52">
+        <f>SUMIF(AR4:AR102,"&lt;&gt;",AM4:AM102)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="53" t="inlineStr">
         <is>
           <t>Held for Quanta-LR (&gt;70nm, roadmap H2 2026+):</t>
         </is>
       </c>
-      <c r="C109" s="54" t="inlineStr">
+      <c r="C117" s="54" t="inlineStr">
         <is>
           <t>Goa → Mumbai (213.3nm)</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="C118" s="54" t="inlineStr">
+        <is>
+          <t>Chennai Port WQIV Cruise Terminal → Cuddalore Port (90.0nm)</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="C119" s="54" t="inlineStr">
+        <is>
+          <t>Chennai Port WQIV Cruise Terminal → Puducherry Port (76.6nm)</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A99:L99"/>
+    <mergeCell ref="A105:L105"/>
     <mergeCell ref="A1:L1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/finance/_refresh_ola.xlsx
+++ b/finance/_refresh_ola.xlsx
@@ -1313,7 +1313,7 @@
         </is>
       </c>
       <c r="B19" s="12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C19" s="13" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
       </c>
       <c r="F19" s="14" t="inlineStr">
         <is>
-          <t>Cap on revenue sailings/day — ~1 sailing/70min in a 12h window; a believable on-demand premium duty cycle, not capacity-max (Jaideep 2026-06-19).</t>
+          <t>Cap on revenue sailings/day — MID headline duty cycle; thin=12 / full=18 bookends in _utilization_scenarios (Jaideep 2026-06-21).</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
         <v>0.45</v>
       </c>
       <c r="C31" s="19" t="n">
-        <v>0.45</v>
+        <v>0.55</v>
       </c>
       <c r="F31" s="14" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         <v>0.55</v>
       </c>
       <c r="C32" s="19" t="n">
-        <v>0.55</v>
+        <v>0.65</v>
       </c>
       <c r="F32" s="14" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>0.7</v>
       </c>
       <c r="C33" s="19" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="F33" s="14" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         <v/>
       </c>
       <c r="K4" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J4,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J4,1))</f>
         <v/>
       </c>
       <c r="L4" s="34">
@@ -2386,7 +2386,7 @@
         <v/>
       </c>
       <c r="K5" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J5,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J5,1))</f>
         <v/>
       </c>
       <c r="L5" s="34">
@@ -2572,7 +2572,7 @@
         <v/>
       </c>
       <c r="K6" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J6,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J6,1))</f>
         <v/>
       </c>
       <c r="L6" s="34">
@@ -2754,7 +2754,7 @@
         <v/>
       </c>
       <c r="K7" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J7,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J7,1))</f>
         <v/>
       </c>
       <c r="L7" s="34">
@@ -2948,7 +2948,7 @@
         <v/>
       </c>
       <c r="K8" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J8,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J8,1))</f>
         <v/>
       </c>
       <c r="L8" s="34">
@@ -3134,7 +3134,7 @@
         <v/>
       </c>
       <c r="K9" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J9,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J9,1))</f>
         <v/>
       </c>
       <c r="L9" s="34">
@@ -3316,7 +3316,7 @@
         <v/>
       </c>
       <c r="K10" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J10,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J10,1))</f>
         <v/>
       </c>
       <c r="L10" s="34">
@@ -3502,7 +3502,7 @@
         <v/>
       </c>
       <c r="K11" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J11,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J11,1))</f>
         <v/>
       </c>
       <c r="L11" s="34">
@@ -3684,7 +3684,7 @@
         <v/>
       </c>
       <c r="K12" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J12,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J12,1))</f>
         <v/>
       </c>
       <c r="L12" s="34">
@@ -3878,7 +3878,7 @@
         <v/>
       </c>
       <c r="K13" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J13,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J13,1))</f>
         <v/>
       </c>
       <c r="L13" s="34">
@@ -4064,7 +4064,7 @@
         <v/>
       </c>
       <c r="K14" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J14,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J14,1))</f>
         <v/>
       </c>
       <c r="L14" s="34">
@@ -4246,7 +4246,7 @@
         <v/>
       </c>
       <c r="K15" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J15,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J15,1))</f>
         <v/>
       </c>
       <c r="L15" s="34">
@@ -4440,7 +4440,7 @@
         <v/>
       </c>
       <c r="K16" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J16,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J16,1))</f>
         <v/>
       </c>
       <c r="L16" s="34">
@@ -4634,7 +4634,7 @@
         <v/>
       </c>
       <c r="K17" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J17,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J17,1))</f>
         <v/>
       </c>
       <c r="L17" s="34">
@@ -4826,7 +4826,7 @@
         <v/>
       </c>
       <c r="K18" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J18,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J18,1))</f>
         <v/>
       </c>
       <c r="L18" s="34">
@@ -5024,7 +5024,7 @@
         <v/>
       </c>
       <c r="K19" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J19,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J19,1))</f>
         <v/>
       </c>
       <c r="L19" s="34">
@@ -5218,7 +5218,7 @@
         <v/>
       </c>
       <c r="K20" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J20,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J20,1))</f>
         <v/>
       </c>
       <c r="L20" s="34">
@@ -5412,7 +5412,7 @@
         <v/>
       </c>
       <c r="K21" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J21,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J21,1))</f>
         <v/>
       </c>
       <c r="L21" s="34">
@@ -5606,7 +5606,7 @@
         <v/>
       </c>
       <c r="K22" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J22,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J22,1))</f>
         <v/>
       </c>
       <c r="L22" s="34">
@@ -5800,7 +5800,7 @@
         <v/>
       </c>
       <c r="K23" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J23,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J23,1))</f>
         <v/>
       </c>
       <c r="L23" s="34">
@@ -5994,7 +5994,7 @@
         <v/>
       </c>
       <c r="K24" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J24,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J24,1))</f>
         <v/>
       </c>
       <c r="L24" s="34">
@@ -6188,7 +6188,7 @@
         <v/>
       </c>
       <c r="K25" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J25,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J25,1))</f>
         <v/>
       </c>
       <c r="L25" s="34">
@@ -6382,7 +6382,7 @@
         <v/>
       </c>
       <c r="K26" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J26,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J26,1))</f>
         <v/>
       </c>
       <c r="L26" s="34">
@@ -6576,7 +6576,7 @@
         <v/>
       </c>
       <c r="K27" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J27,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J27,1))</f>
         <v/>
       </c>
       <c r="L27" s="34">
@@ -6770,7 +6770,7 @@
         <v/>
       </c>
       <c r="K28" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J28,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J28,1))</f>
         <v/>
       </c>
       <c r="L28" s="34">
@@ -6964,7 +6964,7 @@
         <v/>
       </c>
       <c r="K29" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J29,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J29,1))</f>
         <v/>
       </c>
       <c r="L29" s="34">
@@ -7158,7 +7158,7 @@
         <v/>
       </c>
       <c r="K30" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J30,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J30,1))</f>
         <v/>
       </c>
       <c r="L30" s="34">
@@ -7352,7 +7352,7 @@
         <v/>
       </c>
       <c r="K31" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J31,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J31,1))</f>
         <v/>
       </c>
       <c r="L31" s="34">
@@ -7546,7 +7546,7 @@
         <v/>
       </c>
       <c r="K32" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J32,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J32,1))</f>
         <v/>
       </c>
       <c r="L32" s="34">
@@ -7740,7 +7740,7 @@
         <v/>
       </c>
       <c r="K33" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J33,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J33,1))</f>
         <v/>
       </c>
       <c r="L33" s="34">
@@ -7934,7 +7934,7 @@
         <v/>
       </c>
       <c r="K34" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J34,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J34,1))</f>
         <v/>
       </c>
       <c r="L34" s="34">
@@ -8128,7 +8128,7 @@
         <v/>
       </c>
       <c r="K35" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J35,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J35,1))</f>
         <v/>
       </c>
       <c r="L35" s="34">
@@ -8322,7 +8322,7 @@
         <v/>
       </c>
       <c r="K36" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J36,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J36,1))</f>
         <v/>
       </c>
       <c r="L36" s="34">
@@ -8516,7 +8516,7 @@
         <v/>
       </c>
       <c r="K37" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J37,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J37,1))</f>
         <v/>
       </c>
       <c r="L37" s="34">
@@ -8710,7 +8710,7 @@
         <v/>
       </c>
       <c r="K38" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J38,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J38,1))</f>
         <v/>
       </c>
       <c r="L38" s="34">
@@ -8904,7 +8904,7 @@
         <v/>
       </c>
       <c r="K39" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J39,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J39,1))</f>
         <v/>
       </c>
       <c r="L39" s="34">
@@ -9098,7 +9098,7 @@
         <v/>
       </c>
       <c r="K40" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J40,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J40,1))</f>
         <v/>
       </c>
       <c r="L40" s="34">
@@ -9292,7 +9292,7 @@
         <v/>
       </c>
       <c r="K41" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J41,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J41,1))</f>
         <v/>
       </c>
       <c r="L41" s="34">
@@ -9486,7 +9486,7 @@
         <v/>
       </c>
       <c r="K42" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J42,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J42,1))</f>
         <v/>
       </c>
       <c r="L42" s="34">
@@ -9680,7 +9680,7 @@
         <v/>
       </c>
       <c r="K43" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J43,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J43,1))</f>
         <v/>
       </c>
       <c r="L43" s="34">
@@ -9874,7 +9874,7 @@
         <v/>
       </c>
       <c r="K44" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J44,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J44,1))</f>
         <v/>
       </c>
       <c r="L44" s="34">
@@ -10068,7 +10068,7 @@
         <v/>
       </c>
       <c r="K45" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J45,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J45,1))</f>
         <v/>
       </c>
       <c r="L45" s="34">
@@ -10262,7 +10262,7 @@
         <v/>
       </c>
       <c r="K46" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J46,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J46,1))</f>
         <v/>
       </c>
       <c r="L46" s="34">
@@ -10456,7 +10456,7 @@
         <v/>
       </c>
       <c r="K47" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J47,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J47,1))</f>
         <v/>
       </c>
       <c r="L47" s="34">
@@ -10650,7 +10650,7 @@
         <v/>
       </c>
       <c r="K48" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J48,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J48,1))</f>
         <v/>
       </c>
       <c r="L48" s="34">
@@ -10844,7 +10844,7 @@
         <v/>
       </c>
       <c r="K49" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J49,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J49,1))</f>
         <v/>
       </c>
       <c r="L49" s="34">
@@ -11038,7 +11038,7 @@
         <v/>
       </c>
       <c r="K50" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J50,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J50,1))</f>
         <v/>
       </c>
       <c r="L50" s="34">
@@ -11232,7 +11232,7 @@
         <v/>
       </c>
       <c r="K51" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J51,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J51,1))</f>
         <v/>
       </c>
       <c r="L51" s="34">
@@ -11426,7 +11426,7 @@
         <v/>
       </c>
       <c r="K52" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J52,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J52,1))</f>
         <v/>
       </c>
       <c r="L52" s="34">
@@ -11620,7 +11620,7 @@
         <v/>
       </c>
       <c r="K53" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J53,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J53,1))</f>
         <v/>
       </c>
       <c r="L53" s="34">
@@ -11814,7 +11814,7 @@
         <v/>
       </c>
       <c r="K54" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J54,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J54,1))</f>
         <v/>
       </c>
       <c r="L54" s="34">
@@ -12008,7 +12008,7 @@
         <v/>
       </c>
       <c r="K55" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J55,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J55,1))</f>
         <v/>
       </c>
       <c r="L55" s="34">
@@ -12202,7 +12202,7 @@
         <v/>
       </c>
       <c r="K56" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J56,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J56,1))</f>
         <v/>
       </c>
       <c r="L56" s="34">
@@ -12396,7 +12396,7 @@
         <v/>
       </c>
       <c r="K57" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J57,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J57,1))</f>
         <v/>
       </c>
       <c r="L57" s="34">
@@ -12590,7 +12590,7 @@
         <v/>
       </c>
       <c r="K58" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J58,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J58,1))</f>
         <v/>
       </c>
       <c r="L58" s="34">
@@ -12784,7 +12784,7 @@
         <v/>
       </c>
       <c r="K59" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J59,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J59,1))</f>
         <v/>
       </c>
       <c r="L59" s="34">
@@ -12978,7 +12978,7 @@
         <v/>
       </c>
       <c r="K60" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J60,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J60,1))</f>
         <v/>
       </c>
       <c r="L60" s="34">
@@ -13172,7 +13172,7 @@
         <v/>
       </c>
       <c r="K61" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J61,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J61,1))</f>
         <v/>
       </c>
       <c r="L61" s="34">
@@ -13366,7 +13366,7 @@
         <v/>
       </c>
       <c r="K62" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J62,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J62,1))</f>
         <v/>
       </c>
       <c r="L62" s="34">
@@ -13560,7 +13560,7 @@
         <v/>
       </c>
       <c r="K63" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J63,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J63,1))</f>
         <v/>
       </c>
       <c r="L63" s="34">
@@ -13746,7 +13746,7 @@
         <v/>
       </c>
       <c r="K64" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J64,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J64,1))</f>
         <v/>
       </c>
       <c r="L64" s="34">
@@ -13924,7 +13924,7 @@
         <v/>
       </c>
       <c r="K65" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J65,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J65,1))</f>
         <v/>
       </c>
       <c r="L65" s="34">
@@ -14118,7 +14118,7 @@
         <v/>
       </c>
       <c r="K66" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J66,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J66,1))</f>
         <v/>
       </c>
       <c r="L66" s="34">
@@ -14312,7 +14312,7 @@
         <v/>
       </c>
       <c r="K67" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J67,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J67,1))</f>
         <v/>
       </c>
       <c r="L67" s="34">
@@ -14504,7 +14504,7 @@
         <v/>
       </c>
       <c r="K68" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J68,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J68,1))</f>
         <v/>
       </c>
       <c r="L68" s="34">
@@ -14702,7 +14702,7 @@
         <v/>
       </c>
       <c r="K69" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J69,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J69,1))</f>
         <v/>
       </c>
       <c r="L69" s="34">
@@ -14894,7 +14894,7 @@
         <v/>
       </c>
       <c r="K70" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J70,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J70,1))</f>
         <v/>
       </c>
       <c r="L70" s="34">
@@ -15092,7 +15092,7 @@
         <v/>
       </c>
       <c r="K71" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J71,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J71,1))</f>
         <v/>
       </c>
       <c r="L71" s="34">
@@ -15286,7 +15286,7 @@
         <v/>
       </c>
       <c r="K72" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J72,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J72,1))</f>
         <v/>
       </c>
       <c r="L72" s="34">
@@ -15480,7 +15480,7 @@
         <v/>
       </c>
       <c r="K73" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J73,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J73,1))</f>
         <v/>
       </c>
       <c r="L73" s="34">
@@ -15674,7 +15674,7 @@
         <v/>
       </c>
       <c r="K74" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J74,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J74,1))</f>
         <v/>
       </c>
       <c r="L74" s="34">
@@ -15868,7 +15868,7 @@
         <v/>
       </c>
       <c r="K75" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J75,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J75,1))</f>
         <v/>
       </c>
       <c r="L75" s="34">
@@ -16060,7 +16060,7 @@
         <v/>
       </c>
       <c r="K76" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J76,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J76,1))</f>
         <v/>
       </c>
       <c r="L76" s="34">
@@ -16256,7 +16256,7 @@
         <v/>
       </c>
       <c r="K77" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J77,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J77,1))</f>
         <v/>
       </c>
       <c r="L77" s="34">
@@ -16454,7 +16454,7 @@
         <v/>
       </c>
       <c r="K78" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J78,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J78,1))</f>
         <v/>
       </c>
       <c r="L78" s="34">
@@ -16648,7 +16648,7 @@
         <v/>
       </c>
       <c r="K79" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J79,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J79,1))</f>
         <v/>
       </c>
       <c r="L79" s="34">
@@ -16840,7 +16840,7 @@
         <v/>
       </c>
       <c r="K80" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J80,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J80,1))</f>
         <v/>
       </c>
       <c r="L80" s="34">
@@ -17038,7 +17038,7 @@
         <v/>
       </c>
       <c r="K81" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J81,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J81,1))</f>
         <v/>
       </c>
       <c r="L81" s="34">
@@ -17232,7 +17232,7 @@
         <v/>
       </c>
       <c r="K82" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J82,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J82,1))</f>
         <v/>
       </c>
       <c r="L82" s="34">
@@ -17424,7 +17424,7 @@
         <v/>
       </c>
       <c r="K83" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J83,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J83,1))</f>
         <v/>
       </c>
       <c r="L83" s="34">
@@ -17622,7 +17622,7 @@
         <v/>
       </c>
       <c r="K84" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J84,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J84,1))</f>
         <v/>
       </c>
       <c r="L84" s="34">
@@ -17814,7 +17814,7 @@
         <v/>
       </c>
       <c r="K85" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J85,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J85,1))</f>
         <v/>
       </c>
       <c r="L85" s="34">
@@ -18012,7 +18012,7 @@
         <v/>
       </c>
       <c r="K86" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J86,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J86,1))</f>
         <v/>
       </c>
       <c r="L86" s="34">
@@ -18206,7 +18206,7 @@
         <v/>
       </c>
       <c r="K87" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J87,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J87,1))</f>
         <v/>
       </c>
       <c r="L87" s="34">
@@ -18400,7 +18400,7 @@
         <v/>
       </c>
       <c r="K88" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J88,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J88,1))</f>
         <v/>
       </c>
       <c r="L88" s="34">
@@ -18594,7 +18594,7 @@
         <v/>
       </c>
       <c r="K89" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J89,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J89,1))</f>
         <v/>
       </c>
       <c r="L89" s="34">
@@ -18786,7 +18786,7 @@
         <v/>
       </c>
       <c r="K90" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J90,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J90,1))</f>
         <v/>
       </c>
       <c r="L90" s="34">
@@ -18982,7 +18982,7 @@
         <v/>
       </c>
       <c r="K91" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J91,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J91,1))</f>
         <v/>
       </c>
       <c r="L91" s="34">
@@ -19180,7 +19180,7 @@
         <v/>
       </c>
       <c r="K92" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J92,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J92,1))</f>
         <v/>
       </c>
       <c r="L92" s="34">
@@ -19374,7 +19374,7 @@
         <v/>
       </c>
       <c r="K93" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J93,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J93,1))</f>
         <v/>
       </c>
       <c r="L93" s="34">
@@ -19566,7 +19566,7 @@
         <v/>
       </c>
       <c r="K94" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J94,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J94,1))</f>
         <v/>
       </c>
       <c r="L94" s="34">
@@ -19764,7 +19764,7 @@
         <v/>
       </c>
       <c r="K95" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J95,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J95,1))</f>
         <v/>
       </c>
       <c r="L95" s="34">
@@ -19958,7 +19958,7 @@
         <v/>
       </c>
       <c r="K96" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J96,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J96,1))</f>
         <v/>
       </c>
       <c r="L96" s="34">
@@ -20152,7 +20152,7 @@
         <v/>
       </c>
       <c r="K97" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J97,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J97,1))</f>
         <v/>
       </c>
       <c r="L97" s="34">
@@ -20346,7 +20346,7 @@
         <v/>
       </c>
       <c r="K98" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J98,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J98,1))</f>
         <v/>
       </c>
       <c r="L98" s="34">
@@ -20532,7 +20532,7 @@
         <v/>
       </c>
       <c r="K99" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J99,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J99,1))</f>
         <v/>
       </c>
       <c r="L99" s="34">
@@ -20714,7 +20714,7 @@
         <v/>
       </c>
       <c r="K100" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J100,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J100,1))</f>
         <v/>
       </c>
       <c r="L100" s="34">
@@ -20908,7 +20908,7 @@
         <v/>
       </c>
       <c r="K101" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J101,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J101,1))</f>
         <v/>
       </c>
       <c r="L101" s="34">
@@ -21102,7 +21102,7 @@
         <v/>
       </c>
       <c r="K102" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J102,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J102,1))</f>
         <v/>
       </c>
       <c r="L102" s="34">

--- a/finance/_refresh_ola.xlsx
+++ b/finance/_refresh_ola.xlsx
@@ -1332,7 +1332,7 @@
       </c>
       <c r="F19" s="14" t="inlineStr">
         <is>
-          <t>Cap on revenue sailings/day — MID headline duty cycle; thin=12 / full=18 bookends in _utilization_scenarios (Jaideep 2026-06-21).</t>
+          <t>Cap on revenue sailings/day — 15 across thin/mid/full scenarios (Jaideep 2026-06-21).</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
         <v>0.7</v>
       </c>
       <c r="C33" s="19" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="F33" s="14" t="inlineStr">
         <is>

--- a/finance/_refresh_ola.xlsx
+++ b/finance/_refresh_ola.xlsx
@@ -27,23 +27,23 @@
     <definedName name="dwell_min">'Assumptions'!$B$18</definedName>
     <definedName name="max_tpd">'Assumptions'!$B$19</definedName>
     <definedName name="crew_factor">'Assumptions'!$B$20</definedName>
-    <definedName name="ins_pct">'Assumptions'!$B$21</definedName>
-    <definedName name="charge_berth">'Assumptions'!$B$22</definedName>
-    <definedName name="mech_uptime">'Assumptions'!$B$23</definedName>
-    <definedName name="capture">'Assumptions'!$B$24</definedName>
-    <definedName name="capture_captive">'Assumptions'!$B$25</definedName>
-    <definedName name="discount">'Assumptions'!$B$26</definedName>
-    <definedName name="diesel_co2pg">'Assumptions'!$B$27</definedName>
-    <definedName name="load_thin">'Assumptions'!$B$31</definedName>
-    <definedName name="revleg_thin">'Assumptions'!$C$31</definedName>
-    <definedName name="load_mid">'Assumptions'!$B$32</definedName>
-    <definedName name="revleg_mid">'Assumptions'!$C$32</definedName>
-    <definedName name="load_full">'Assumptions'!$B$33</definedName>
-    <definedName name="revleg_full">'Assumptions'!$C$33</definedName>
-    <definedName name="band_tbl">'Assumptions'!$A$31:$C$33</definedName>
-    <definedName name="scenario">'Assumptions'!$B$35</definedName>
-    <definedName name="load_sel">'Assumptions'!$B$36</definedName>
-    <definedName name="revleg_sel">'Assumptions'!$B$37</definedName>
+    <definedName name="mech_uptime">'Assumptions'!$B$21</definedName>
+    <definedName name="capture">'Assumptions'!$B$22</definedName>
+    <definedName name="capture_captive">'Assumptions'!$B$23</definedName>
+    <definedName name="discount">'Assumptions'!$B$24</definedName>
+    <definedName name="diesel_co2pg">'Assumptions'!$B$25</definedName>
+    <definedName name="ins_pct">'Assumptions'!$B$29</definedName>
+    <definedName name="charge_berth">'Assumptions'!$B$30</definedName>
+    <definedName name="load_thin">'Assumptions'!$B$34</definedName>
+    <definedName name="revleg_thin">'Assumptions'!$C$34</definedName>
+    <definedName name="load_mid">'Assumptions'!$B$35</definedName>
+    <definedName name="revleg_mid">'Assumptions'!$C$35</definedName>
+    <definedName name="load_full">'Assumptions'!$B$36</definedName>
+    <definedName name="revleg_full">'Assumptions'!$C$36</definedName>
+    <definedName name="band_tbl">'Assumptions'!$A$34:$C$36</definedName>
+    <definedName name="scenario">'Assumptions'!$B$38</definedName>
+    <definedName name="load_sel">'Assumptions'!$B$39</definedName>
+    <definedName name="revleg_sel">'Assumptions'!$B$40</definedName>
     <definedName name="country_opex">'Country opex'!$A$4:$G$4</definedName>
     <definedName name="som_floor_fleet">'Corridor economics'!$D$114</definedName>
     <definedName name="som_floor_rev">'Corridor economics'!$E$114</definedName>
@@ -707,7 +707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B27"/>
+  <dimension ref="B2:B36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -786,84 +786,143 @@
     <row r="14">
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>EBITDA  = REVENUE − OPEX   (energy + captain + marina/overhead + maintenance)</t>
+          <t>EBITDA  = REVENUE − OPEX</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>PAYBACK = vessel CAPEX ÷ EBITDA</t>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    OPEX = energy + crew + berth/port admin + maintenance + vessel insurance + fast-charge berth</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="2" t="inlineStr"/>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>PAYBACK = vessel CAPEX ÷ EBITDA</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>From demand pool to fleet &amp; market size</t>
-        </is>
-      </c>
+      <c r="B17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>Navier serviceable rides/yr = corridor demand pool × capture rate (10% on contested corridors; ~90% on captive sole-operator transfer legs — see the per-row Capture % column)</t>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>OPEX lines (per boat, per year — no double-counting)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Vessels supported = FLOOR(Navier rides/yr ÷ pax/yr per boat);  Market rev = vessels × rev/boat. The 'Market sizing' tab rolls these up into the SOM → SAM → TAM ladder.</t>
+          <t>Energy — variable propulsion cost: kWh on revenue sailings × local $/kWh (Country opex tab). Excludes utility demand charges.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Crew — fully-loaded captain + relief: local captain wage × crew FTE factor (Country opex + Assumptions).</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>The scenario toggle (what we flex)</t>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Berth &amp; port admin — fixed annual berth, port fees, and local marine admin (Country opex tab). Excludes vessel H&amp;M+P&amp;I and fast-charge infrastructure.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>'Corridor economics' has a SCENARIO cell = THIN / MID / FULL. It flexes two levers: load factor (how full the boat is) and revenue-leg factor (how many legs earn full fare). MID is the headline. Change that one cell and the whole model recomputes. The right-hand Payback THIN/MID/FULL columns always show all three at once.</t>
+          <t>Maintenance — vessel annual maintenance reserve (Assumptions tab).</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Vessel insurance — commercial H&amp;M + P&amp;I as % of regional CAPEX (Assumptions % × Country opex CAPEX column).</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Colour &amp; provenance legend</t>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Fast-charge berth — dedicated fast-charge berth slot + utility demand charges (Assumptions default; overridable per market). Separate from per-kWh energy and berth/port admin.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Yellow = INPUTS you can change (fare, distance, demand, weather).</t>
-        </is>
-      </c>
+      <c r="B25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Green  = COMPUTED by formula.</t>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>From demand pool to fleet &amp; market size</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Navier serviceable rides/yr = corridor demand pool × capture rate (10% on contested corridors; ~90% on captive sole-operator transfer legs — see the per-row Capture % column)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Vessels supported = FLOOR(Navier rides/yr ÷ pax/yr per boat);  Market rev = vessels × rev/boat. The 'Market sizing' tab rolls these up into the SOM → SAM → TAM ladder.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>The scenario toggle (what we flex)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>'Corridor economics' has a SCENARIO cell = THIN / MID / FULL. It flexes load factor (occupancy) and revenue-leg factor (share of legs that earn full fare). Max trips/day is fixed across all three bands (see Assumptions). MID is the headline. Change SCENARIO and the whole model recomputes. Payback THIN/MID/FULL columns always show all three at once.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Colour &amp; provenance legend</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Yellow = INPUTS you can change (fare, distance, demand, weather).</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Green  = COMPUTED by formula.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">   Every fare &amp; demand figure carries a Source tier (T1 official → T5 modeled) + Confidence (high/med/low). Null beats a wrong number: no published pool → blank, not a guess.</t>
         </is>
@@ -880,7 +939,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1369,11 +1428,11 @@
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>Insurance (% of capex/yr)</t>
+          <t>Mechanical uptime</t>
         </is>
       </c>
       <c r="B21" s="17" t="n">
-        <v>0.025</v>
+        <v>0.75</v>
       </c>
       <c r="C21" s="13" t="inlineStr">
         <is>
@@ -1382,7 +1441,7 @@
       </c>
       <c r="D21" s="13" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
@@ -1392,29 +1451,25 @@
       </c>
       <c r="F21" s="14" t="inlineStr">
         <is>
-          <t>H&amp;M + P&amp;I for a commercial passenger vessel ~2.5%/yr of capex; scales with regional capex overrides (Jaideep 2026-06-19).</t>
+          <t>Blade luxury aviation ~75-80% reliability uptime</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>Charging &amp; berth (additional to marina+energy)</t>
-        </is>
-      </c>
-      <c r="B22" s="15" t="n">
-        <v>18000</v>
+          <t>Navier capture rate</t>
+        </is>
+      </c>
+      <c r="B22" s="17" t="n">
+        <v>0.1</v>
       </c>
       <c r="C22" s="13" t="inlineStr">
         <is>
-          <t>USD/yr</t>
-        </is>
-      </c>
-      <c r="D22" s="13" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
+          <t>frac</t>
+        </is>
+      </c>
+      <c r="D22" s="13" t="inlineStr"/>
       <c r="E22" s="13" t="inlineStr">
         <is>
           <t>med</t>
@@ -1422,29 +1477,25 @@
       </c>
       <c r="F22" s="14" t="inlineStr">
         <is>
-          <t>Dedicated fast-charge berth + demand charges, ADDITIONAL to marina overhead and energy (Jaideep 2026-06-19). L3-overridable.</t>
+          <t>Navier wins ~10% of a CONTESTED corridor demand pool (locked). Captive sole-operator transfer legs (captive:true / luxury_charter / hospitality archetypes) carry the captive rate instead — see per-row Capture %.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>Mechanical uptime</t>
+          <t>Captive capture rate (A′ corridors)</t>
         </is>
       </c>
       <c r="B23" s="17" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="C23" s="13" t="inlineStr">
         <is>
           <t>frac</t>
         </is>
       </c>
-      <c r="D23" s="13" t="inlineStr">
-        <is>
-          <t>T4</t>
-        </is>
-      </c>
+      <c r="D23" s="13" t="inlineStr"/>
       <c r="E23" s="13" t="inlineStr">
         <is>
           <t>med</t>
@@ -1452,255 +1503,303 @@
       </c>
       <c r="F23" s="14" t="inlineStr">
         <is>
-          <t>Blade luxury aviation ~75-80% reliability uptime</t>
+          <t>Sole-operator water-access-only transfer legs (captive:true or luxury_charter/hospitality archetype): Navier IS the transfer fleet — capture ~90%. Applied per-row in the Capture % column.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>Navier capture rate</t>
-        </is>
-      </c>
-      <c r="B24" s="17" t="n">
-        <v>0.1</v>
+          <t>Discount factor (vs comparable fare)</t>
+        </is>
+      </c>
+      <c r="B24" s="16" t="n">
+        <v>1</v>
       </c>
       <c r="C24" s="13" t="inlineStr">
         <is>
           <t>frac</t>
         </is>
       </c>
-      <c r="D24" s="13" t="inlineStr"/>
+      <c r="D24" s="13" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
-          <t>med</t>
+          <t>high</t>
         </is>
       </c>
       <c r="F24" s="14" t="inlineStr">
         <is>
-          <t>Navier wins ~10% of a CONTESTED corridor demand pool (locked). Captive sole-operator transfer legs (captive:true / luxury_charter / hospitality archetypes) carry the captive rate instead — see per-row Capture %.</t>
+          <t>Market parity — better product, not cheaper (locked).</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>Captive capture rate (A′ corridors)</t>
-        </is>
-      </c>
-      <c r="B25" s="17" t="n">
-        <v>0.9</v>
+          <t>Diesel CO₂ per gallon</t>
+        </is>
+      </c>
+      <c r="B25" s="16" t="n">
+        <v>10.21</v>
       </c>
       <c r="C25" s="13" t="inlineStr">
         <is>
-          <t>frac</t>
-        </is>
-      </c>
-      <c r="D25" s="13" t="inlineStr"/>
+          <t>kg/gal</t>
+        </is>
+      </c>
+      <c r="D25" s="13" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
       <c r="E25" s="13" t="inlineStr">
         <is>
-          <t>med</t>
+          <t>high</t>
         </is>
       </c>
       <c r="F25" s="14" t="inlineStr">
         <is>
-          <t>Sole-operator water-access-only transfer legs (captive:true or luxury_charter/hospitality archetype): Navier IS the transfer fleet — capture ~90%. Applied per-row in the Capture % column.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="11" t="inlineStr">
-        <is>
-          <t>Discount factor (vs comparable fare)</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C26" s="13" t="inlineStr">
-        <is>
-          <t>frac</t>
-        </is>
-      </c>
-      <c r="D26" s="13" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="E26" s="13" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="F26" s="14" t="inlineStr">
-        <is>
-          <t>Market parity — better product, not cheaper (locked).</t>
+          <t>US EPA: 10.21 kg CO2 per gallon marine/diesel</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="11" t="inlineStr">
-        <is>
-          <t>Diesel CO₂ per gallon</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="n">
-        <v>10.21</v>
-      </c>
-      <c r="C27" s="13" t="inlineStr">
-        <is>
-          <t>kg/gal</t>
-        </is>
-      </c>
-      <c r="D27" s="13" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="E27" s="13" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="F27" s="14" t="inlineStr">
-        <is>
-          <t>US EPA: 10.21 kg CO2 per gallon marine/diesel</t>
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>OPEX defaults  (global fallbacks — localized energy, crew, berth admin on Country opex tab)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>Parameter</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="inlineStr">
+        <is>
+          <t>Tier</t>
+        </is>
+      </c>
+      <c r="E28" s="10" t="inlineStr">
+        <is>
+          <t>Conf.</t>
+        </is>
+      </c>
+      <c r="F28" s="10" t="inlineStr">
+        <is>
+          <t>Source / note</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="9" t="inlineStr">
-        <is>
-          <t>Utilization scenarios  (the two levers we flex)</t>
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>Vessel insurance — H&amp;M + P&amp;I (% of CAPEX/yr)</t>
+        </is>
+      </c>
+      <c r="B29" s="17" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="C29" s="13" t="inlineStr">
+        <is>
+          <t>frac</t>
+        </is>
+      </c>
+      <c r="D29" s="13" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="E29" s="13" t="inlineStr">
+        <is>
+          <t>med</t>
+        </is>
+      </c>
+      <c r="F29" s="14" t="inlineStr">
+        <is>
+          <t>Commercial vessel H&amp;M + P&amp;I ~2.5%/yr of regional CAPEX. Separate from berth/port admin in Country opex (Jaideep 2026-06-19).. Multiplied by regional CAPEX (Country opex col G). Not included in berth/port admin.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="10" t="inlineStr">
-        <is>
-          <t>Scenario</t>
-        </is>
-      </c>
-      <c r="B30" s="10" t="inlineStr">
-        <is>
-          <t>Load factor</t>
-        </is>
-      </c>
-      <c r="C30" s="10" t="inlineStr">
-        <is>
-          <t>Rev-leg factor</t>
-        </is>
-      </c>
-      <c r="D30" s="10" t="inlineStr"/>
-      <c r="E30" s="10" t="inlineStr"/>
-      <c r="F30" s="10" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="18" t="inlineStr">
-        <is>
-          <t>THIN</t>
-        </is>
-      </c>
-      <c r="B31" s="19" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="C31" s="19" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="F31" s="14" t="inlineStr">
-        <is>
-          <t>thin/one-way/seasonal corridor — conservative floor</t>
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>Fast-charge berth &amp; demand charges (global default)</t>
+        </is>
+      </c>
+      <c r="B30" s="15" t="n">
+        <v>18000</v>
+      </c>
+      <c r="C30" s="13" t="inlineStr">
+        <is>
+          <t>USD/yr</t>
+        </is>
+      </c>
+      <c r="D30" s="13" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="E30" s="13" t="inlineStr">
+        <is>
+          <t>med</t>
+        </is>
+      </c>
+      <c r="F30" s="14" t="inlineStr">
+        <is>
+          <t>Dedicated fast-charge berth slot + utility demand charges. Excludes per-kWh propulsion energy and berth/port admin (Jaideep 2026-06-19). L3-overridable per market.. Dedicated charge berth + utility demand charges. Excludes per-kWh propulsion energy and berth/port admin. L3-overridable per market.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="18" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="B32" s="19" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="C32" s="19" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="F32" s="14" t="inlineStr">
-        <is>
-          <t>HEADLINE — realistic busy two-way corridor</t>
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>Utilization scenarios  (load factor + revenue-leg factor)</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="18" t="inlineStr">
-        <is>
-          <t>FULL</t>
-        </is>
-      </c>
-      <c r="B33" s="19" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="C33" s="19" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="F33" s="14" t="inlineStr">
-        <is>
-          <t>mature/dense corridor — optimistic ceiling</t>
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>Load factor</t>
+        </is>
+      </c>
+      <c r="C33" s="10" t="inlineStr">
+        <is>
+          <t>Rev-leg factor</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="inlineStr"/>
+      <c r="E33" s="10" t="inlineStr"/>
+      <c r="F33" s="10" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="18" t="inlineStr">
+        <is>
+          <t>THIN</t>
+        </is>
+      </c>
+      <c r="B34" s="19" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="C34" s="19" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="F34" s="14" t="inlineStr">
+        <is>
+          <t>thin/one-way/seasonal corridor — conservative floor</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="20" t="inlineStr">
-        <is>
-          <t>SCENARIO (toggle me)</t>
-        </is>
-      </c>
-      <c r="B35" s="21" t="inlineStr">
+      <c r="A35" s="18" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="C35" s="22" t="inlineStr">
-        <is>
-          <t>← set THIN / MID / FULL</t>
+      <c r="B35" s="19" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="C35" s="19" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="F35" s="14" t="inlineStr">
+        <is>
+          <t>HEADLINE — realistic busy two-way corridor</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="11" t="inlineStr">
+      <c r="A36" s="18" t="inlineStr">
+        <is>
+          <t>FULL</t>
+        </is>
+      </c>
+      <c r="B36" s="19" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C36" s="19" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F36" s="14" t="inlineStr">
+        <is>
+          <t>mature/dense corridor — optimistic ceiling</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="20" t="inlineStr">
+        <is>
+          <t>SCENARIO (toggle me)</t>
+        </is>
+      </c>
+      <c r="B38" s="21" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="C38" s="22" t="inlineStr">
+        <is>
+          <t>← set THIN / MID / FULL</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="11" t="inlineStr">
         <is>
           <t>Selected load factor</t>
         </is>
       </c>
-      <c r="B36" s="23">
-        <f>VLOOKUP(scenario,'Assumptions'!$A$31:$C$33,2,FALSE)</f>
+      <c r="B39" s="23">
+        <f>VLOOKUP(scenario,'Assumptions'!$A$34:$C$36,2,FALSE)</f>
         <v/>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="11" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="11" t="inlineStr">
         <is>
           <t>Selected rev-leg factor</t>
         </is>
       </c>
-      <c r="B37" s="23">
-        <f>VLOOKUP(scenario,'Assumptions'!$A$31:$C$33,3,FALSE)</f>
+      <c r="B40" s="23">
+        <f>VLOOKUP(scenario,'Assumptions'!$A$34:$C$36,3,FALSE)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A3:F3"/>
+  <mergeCells count="5">
     <mergeCell ref="A14:F14"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A29:F29"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A3:F3"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="B35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="B38" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"THIN,MID,FULL"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1730,7 +1829,7 @@
     <row r="1">
       <c r="A1" s="8" t="inlineStr">
         <is>
-          <t>Country opex — L3 localized layer (VLOOKUP target for the engine)</t>
+          <t>Country opex — localized inputs (crew, energy, berth admin, CAPEX)</t>
         </is>
       </c>
     </row>
@@ -1757,7 +1856,7 @@
       </c>
       <c r="E3" s="24" t="inlineStr">
         <is>
-          <t>Marina $/yr</t>
+          <t>Berth &amp; port admin $/yr</t>
         </is>
       </c>
       <c r="F3" s="24" t="inlineStr">
@@ -1772,7 +1871,7 @@
       </c>
       <c r="H3" s="24" t="inlineStr">
         <is>
-          <t>Source notes (captain | energy | marina)</t>
+          <t>Source notes (crew | energy | berth admin)</t>
         </is>
       </c>
     </row>
@@ -1845,10 +1944,10 @@
     <col width="11" customWidth="1" min="20" max="20"/>
     <col width="10" customWidth="1" min="21" max="21"/>
     <col width="10" customWidth="1" min="22" max="22"/>
-    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
     <col width="9" customWidth="1" min="24" max="24"/>
-    <col width="10" customWidth="1" min="25" max="25"/>
-    <col width="11" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
     <col width="11" customWidth="1" min="27" max="27"/>
     <col width="10" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
@@ -2009,7 +2108,7 @@
       </c>
       <c r="W3" s="24" t="inlineStr">
         <is>
-          <t>Marina/yr</t>
+          <t>Berth &amp; port admin/yr</t>
         </is>
       </c>
       <c r="X3" s="24" t="inlineStr">
@@ -2019,12 +2118,12 @@
       </c>
       <c r="Y3" s="24" t="inlineStr">
         <is>
-          <t>Insurance/yr</t>
+          <t>Vessel insurance/yr</t>
         </is>
       </c>
       <c r="Z3" s="24" t="inlineStr">
         <is>
-          <t>Charge+berth/yr</t>
+          <t>Fast-charge berth/yr</t>
         </is>
       </c>
       <c r="AA3" s="24" t="inlineStr">
